--- a/Gastos_Mensuales.xlsx
+++ b/Gastos_Mensuales.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3050" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3038" uniqueCount="389">
   <si>
     <t xml:space="preserve">Mes</t>
   </si>
@@ -450,12 +450,6 @@
     <t xml:space="preserve">Seguro auto Jay (cargo adicional)</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Culligan (agua)</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-07-20</t>
   </si>
   <si>
@@ -510,10 +504,10 @@
     <t xml:space="preserve">2026-07-15</t>
   </si>
   <si>
-    <t xml:space="preserve">Pearson (curso online Guada)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Viajes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pearson (curso online Guada, gasto del viaje)</t>
   </si>
   <si>
     <t xml:space="preserve">2026-06-23</t>
@@ -7222,10 +7216,10 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C232" s="3"/>
       <c r="D232" s="3" t="s">
@@ -7238,21 +7232,23 @@
         <v>18</v>
       </c>
       <c r="G232" s="4" t="n">
-        <v>250000</v>
+        <v>161568</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I232" s="3"/>
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B233" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C233" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C233" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D233" s="3" t="s">
         <v>144</v>
       </c>
@@ -7260,10 +7256,10 @@
         <v>145</v>
       </c>
       <c r="F233" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G233" s="4" t="n">
-        <v>161568</v>
+        <v>1492000</v>
       </c>
       <c r="H233" s="3" t="s">
         <v>31</v>
@@ -7278,19 +7274,19 @@
         <v>65</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D234" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E234" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E234" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="F234" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G234" s="4" t="n">
-        <v>1492000</v>
+        <v>30000</v>
       </c>
       <c r="H234" s="3" t="s">
         <v>31</v>
@@ -7305,10 +7301,10 @@
         <v>65</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>148</v>
@@ -7317,7 +7313,7 @@
         <v>12</v>
       </c>
       <c r="G235" s="4" t="n">
-        <v>30000</v>
+        <v>108850</v>
       </c>
       <c r="H235" s="3" t="s">
         <v>31</v>
@@ -7332,19 +7328,19 @@
         <v>65</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D236" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E236" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E236" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="F236" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G236" s="4" t="n">
-        <v>108850</v>
+        <v>90000</v>
       </c>
       <c r="H236" s="3" t="s">
         <v>31</v>
@@ -7359,19 +7355,19 @@
         <v>65</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>151</v>
+        <v>94</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G237" s="4" t="n">
-        <v>90000</v>
+        <v>61000</v>
       </c>
       <c r="H237" s="3" t="s">
         <v>31</v>
@@ -7386,19 +7382,19 @@
         <v>65</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G238" s="4" t="n">
-        <v>61000</v>
+        <v>20000</v>
       </c>
       <c r="H238" s="3" t="s">
         <v>31</v>
@@ -7407,25 +7403,23 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C239" s="3" t="s">
-        <v>69</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C239" s="3"/>
       <c r="D239" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E239" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E239" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="F239" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G239" s="4" t="n">
-        <v>20000</v>
+        <v>6733</v>
       </c>
       <c r="H239" s="3" t="s">
         <v>31</v>
@@ -7434,50 +7428,52 @@
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C240" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C240" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D240" s="3" t="s">
         <v>153</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>154</v>
+        <v>68</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G240" s="4" t="n">
-        <v>6733</v>
+        <v>134000</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I240" s="3"/>
     </row>
     <row r="241" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D241" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E241" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E241" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="F241" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G241" s="4" t="n">
-        <v>134000</v>
+        <v>519563</v>
       </c>
       <c r="H241" s="3" t="s">
         <v>13</v>
@@ -7504,7 +7500,7 @@
         <v>12</v>
       </c>
       <c r="G242" s="4" t="n">
-        <v>519563</v>
+        <v>135000</v>
       </c>
       <c r="H242" s="3" t="s">
         <v>13</v>
@@ -7519,19 +7515,19 @@
         <v>65</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G243" s="4" t="n">
-        <v>135000</v>
+        <v>269500</v>
       </c>
       <c r="H243" s="3" t="s">
         <v>13</v>
@@ -7546,19 +7542,19 @@
         <v>65</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D244" s="3" t="s">
         <v>158</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G244" s="4" t="n">
-        <v>269500</v>
+        <v>708266</v>
       </c>
       <c r="H244" s="3" t="s">
         <v>13</v>
@@ -7576,16 +7572,16 @@
         <v>79</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G245" s="4" t="n">
-        <v>708266</v>
+        <v>-141653</v>
       </c>
       <c r="H245" s="3" t="s">
         <v>13</v>
@@ -7597,22 +7593,20 @@
         <v>32</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C246" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C246" s="3"/>
       <c r="D246" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G246" s="4" t="n">
-        <v>-141653</v>
+        <v>124699</v>
       </c>
       <c r="H246" s="3" t="s">
         <v>13</v>
@@ -7621,26 +7615,26 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B247" s="3" t="s">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="C247" s="3"/>
       <c r="D247" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="E247" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E247" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="F247" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G247" s="4" t="n">
-        <v>124699</v>
+        <v>4724610</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="I247" s="3"/>
     </row>
@@ -7649,20 +7643,20 @@
         <v>42</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>19</v>
+        <v>160</v>
       </c>
       <c r="C248" s="3"/>
       <c r="D248" s="3" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G248" s="4" t="n">
-        <v>4724610</v>
+        <v>1545000</v>
       </c>
       <c r="H248" s="3" t="s">
         <v>64</v>
@@ -7674,20 +7668,20 @@
         <v>42</v>
       </c>
       <c r="B249" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C249" s="3"/>
       <c r="D249" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E249" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E249" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="F249" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G249" s="4" t="n">
-        <v>1545000</v>
+        <v>2161949</v>
       </c>
       <c r="H249" s="3" t="s">
         <v>64</v>
@@ -7699,20 +7693,20 @@
         <v>42</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C250" s="3"/>
       <c r="D250" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G250" s="4" t="n">
-        <v>2161949</v>
+        <v>7869921</v>
       </c>
       <c r="H250" s="3" t="s">
         <v>64</v>
@@ -7724,14 +7718,14 @@
         <v>42</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C251" s="3"/>
       <c r="D251" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>12</v>
@@ -7749,20 +7743,22 @@
         <v>42</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C252" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C252" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="D252" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G252" s="4" t="n">
-        <v>7869921</v>
+        <v>171000</v>
       </c>
       <c r="H252" s="3" t="s">
         <v>64</v>
@@ -7777,19 +7773,19 @@
         <v>65</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>170</v>
+        <v>79</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G253" s="4" t="n">
-        <v>171000</v>
+        <v>745373</v>
       </c>
       <c r="H253" s="3" t="s">
         <v>64</v>
@@ -7807,7 +7803,7 @@
         <v>79</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>79</v>
@@ -7816,7 +7812,7 @@
         <v>12</v>
       </c>
       <c r="G254" s="4" t="n">
-        <v>745373</v>
+        <v>136317</v>
       </c>
       <c r="H254" s="3" t="s">
         <v>64</v>
@@ -7831,19 +7827,19 @@
         <v>65</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G255" s="4" t="n">
-        <v>136317</v>
+        <v>167775</v>
       </c>
       <c r="H255" s="3" t="s">
         <v>64</v>
@@ -7852,16 +7848,16 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>168</v>
+        <v>69</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E256" s="3" t="s">
         <v>171</v>
@@ -7870,7 +7866,7 @@
         <v>12</v>
       </c>
       <c r="G256" s="4" t="n">
-        <v>167775</v>
+        <v>158000</v>
       </c>
       <c r="H256" s="3" t="s">
         <v>64</v>
@@ -7885,7 +7881,7 @@
         <v>65</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D257" s="3" t="s">
         <v>172</v>
@@ -7897,7 +7893,7 @@
         <v>12</v>
       </c>
       <c r="G257" s="4" t="n">
-        <v>158000</v>
+        <v>303784</v>
       </c>
       <c r="H257" s="3" t="s">
         <v>64</v>
@@ -7906,25 +7902,25 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>175</v>
+        <v>116</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G258" s="4" t="n">
-        <v>303784</v>
+        <v>-223612</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>64</v>
@@ -7942,7 +7938,7 @@
         <v>79</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>116</v>
@@ -7951,7 +7947,7 @@
         <v>12</v>
       </c>
       <c r="G259" s="4" t="n">
-        <v>-223612</v>
+        <v>-40895</v>
       </c>
       <c r="H259" s="3" t="s">
         <v>64</v>
@@ -7960,28 +7956,28 @@
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="E260" s="3" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G260" s="4" t="n">
-        <v>-40895</v>
+        <v>12193</v>
       </c>
       <c r="H260" s="3" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="I260" s="3"/>
     </row>
@@ -7996,7 +7992,7 @@
         <v>82</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>92</v>
@@ -8005,7 +8001,7 @@
         <v>12</v>
       </c>
       <c r="G261" s="4" t="n">
-        <v>12193</v>
+        <v>16142</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>31</v>
@@ -8023,7 +8019,7 @@
         <v>82</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>92</v>
@@ -8032,7 +8028,7 @@
         <v>12</v>
       </c>
       <c r="G262" s="4" t="n">
-        <v>16142</v>
+        <v>18263</v>
       </c>
       <c r="H262" s="3" t="s">
         <v>31</v>
@@ -8050,7 +8046,7 @@
         <v>82</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>92</v>
@@ -8059,7 +8055,7 @@
         <v>12</v>
       </c>
       <c r="G263" s="4" t="n">
-        <v>18263</v>
+        <v>17217</v>
       </c>
       <c r="H263" s="3" t="s">
         <v>31</v>
@@ -8077,7 +8073,7 @@
         <v>82</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>92</v>
@@ -8086,7 +8082,7 @@
         <v>12</v>
       </c>
       <c r="G264" s="4" t="n">
-        <v>17217</v>
+        <v>18237</v>
       </c>
       <c r="H264" s="3" t="s">
         <v>31</v>
@@ -8104,7 +8100,7 @@
         <v>82</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>92</v>
@@ -8113,7 +8109,7 @@
         <v>12</v>
       </c>
       <c r="G265" s="4" t="n">
-        <v>18237</v>
+        <v>17289</v>
       </c>
       <c r="H265" s="3" t="s">
         <v>31</v>
@@ -8131,7 +8127,7 @@
         <v>82</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E266" s="3" t="s">
         <v>92</v>
@@ -8140,7 +8136,7 @@
         <v>12</v>
       </c>
       <c r="G266" s="4" t="n">
-        <v>17289</v>
+        <v>18306</v>
       </c>
       <c r="H266" s="3" t="s">
         <v>31</v>
@@ -8155,19 +8151,19 @@
         <v>65</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G267" s="4" t="n">
-        <v>18306</v>
+        <v>125000</v>
       </c>
       <c r="H267" s="3" t="s">
         <v>31</v>
@@ -8182,19 +8178,19 @@
         <v>65</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>168</v>
+        <v>69</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G268" s="4" t="n">
-        <v>125000</v>
+        <v>400000</v>
       </c>
       <c r="H268" s="3" t="s">
         <v>31</v>
@@ -8206,22 +8202,20 @@
         <v>36</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C269" s="3" t="s">
-        <v>69</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C269" s="3"/>
       <c r="D269" s="3" t="s">
         <v>177</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G269" s="4" t="n">
-        <v>400000</v>
+        <v>10097</v>
       </c>
       <c r="H269" s="3" t="s">
         <v>31</v>
@@ -8230,23 +8224,23 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C270" s="3"/>
       <c r="D270" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>154</v>
+        <v>181</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G270" s="4" t="n">
-        <v>10097</v>
+        <v>137500</v>
       </c>
       <c r="H270" s="3" t="s">
         <v>31</v>
@@ -8271,7 +8265,7 @@
         <v>18</v>
       </c>
       <c r="G271" s="4" t="n">
-        <v>137500</v>
+        <v>33825</v>
       </c>
       <c r="H271" s="3" t="s">
         <v>31</v>
@@ -8283,20 +8277,22 @@
         <v>41</v>
       </c>
       <c r="B272" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C272" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D272" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E272" s="3" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G272" s="4" t="n">
-        <v>33825</v>
+        <v>133900</v>
       </c>
       <c r="H272" s="3" t="s">
         <v>31</v>
@@ -8314,7 +8310,7 @@
         <v>66</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E273" s="3" t="s">
         <v>68</v>
@@ -8323,7 +8319,7 @@
         <v>12</v>
       </c>
       <c r="G273" s="4" t="n">
-        <v>133900</v>
+        <v>158000</v>
       </c>
       <c r="H273" s="3" t="s">
         <v>31</v>
@@ -8338,19 +8334,19 @@
         <v>65</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="D274" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E274" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E274" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="F274" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G274" s="4" t="n">
-        <v>158000</v>
+        <v>77000</v>
       </c>
       <c r="H274" s="3" t="s">
         <v>31</v>
@@ -8365,19 +8361,19 @@
         <v>65</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>168</v>
+        <v>66</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>188</v>
+        <v>68</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G275" s="4" t="n">
-        <v>77000</v>
+        <v>214000</v>
       </c>
       <c r="H275" s="3" t="s">
         <v>31</v>
@@ -8386,28 +8382,28 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>68</v>
+        <v>188</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G276" s="4" t="n">
-        <v>214000</v>
+        <v>160000</v>
       </c>
       <c r="H276" s="3" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I276" s="3"/>
     </row>
@@ -8425,13 +8421,13 @@
         <v>189</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G277" s="4" t="n">
-        <v>160000</v>
+        <v>495727</v>
       </c>
       <c r="H277" s="3" t="s">
         <v>13</v>
@@ -8443,22 +8439,20 @@
         <v>42</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C278" s="3" t="s">
-        <v>69</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C278" s="3"/>
       <c r="D278" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G278" s="4" t="n">
-        <v>495727</v>
+        <v>40451</v>
       </c>
       <c r="H278" s="3" t="s">
         <v>13</v>
@@ -8470,23 +8464,25 @@
         <v>42</v>
       </c>
       <c r="B279" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C279" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C279" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="D279" s="3" t="s">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G279" s="4" t="n">
-        <v>40451</v>
+        <v>338074</v>
       </c>
       <c r="H279" s="3" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="I279" s="3"/>
     </row>
@@ -8498,19 +8494,19 @@
         <v>65</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G280" s="4" t="n">
-        <v>338074</v>
+        <v>53700</v>
       </c>
       <c r="H280" s="3" t="s">
         <v>64</v>
@@ -8525,19 +8521,19 @@
         <v>65</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G281" s="4" t="n">
-        <v>53700</v>
+        <v>-50711</v>
       </c>
       <c r="H281" s="3" t="s">
         <v>64</v>
@@ -8546,16 +8542,16 @@
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="E282" s="3" t="s">
         <v>194</v>
@@ -8564,10 +8560,10 @@
         <v>12</v>
       </c>
       <c r="G282" s="4" t="n">
-        <v>-50711</v>
+        <v>147440</v>
       </c>
       <c r="H282" s="3" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="I282" s="3"/>
     </row>
@@ -8579,7 +8575,7 @@
         <v>65</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>168</v>
+        <v>69</v>
       </c>
       <c r="D283" s="3" t="s">
         <v>195</v>
@@ -8591,7 +8587,7 @@
         <v>12</v>
       </c>
       <c r="G283" s="4" t="n">
-        <v>147440</v>
+        <v>106000</v>
       </c>
       <c r="H283" s="3" t="s">
         <v>31</v>
@@ -8606,7 +8602,7 @@
         <v>65</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D284" s="3" t="s">
         <v>197</v>
@@ -8618,7 +8614,7 @@
         <v>12</v>
       </c>
       <c r="G284" s="4" t="n">
-        <v>106000</v>
+        <v>788596</v>
       </c>
       <c r="H284" s="3" t="s">
         <v>31</v>
@@ -8633,19 +8629,19 @@
         <v>65</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D285" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="E285" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E285" s="3" t="s">
-        <v>200</v>
-      </c>
       <c r="F285" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G285" s="4" t="n">
-        <v>788596</v>
+        <v>171000</v>
       </c>
       <c r="H285" s="3" t="s">
         <v>31</v>
@@ -8660,19 +8656,19 @@
         <v>65</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>201</v>
+        <v>68</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G286" s="4" t="n">
-        <v>171000</v>
+        <v>266500</v>
       </c>
       <c r="H286" s="3" t="s">
         <v>31</v>
@@ -8681,25 +8677,25 @@
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="D287" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E287" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E287" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="F287" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G287" s="4" t="n">
-        <v>266500</v>
+        <v>1260000</v>
       </c>
       <c r="H287" s="3" t="s">
         <v>31</v>
@@ -8708,25 +8704,25 @@
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G288" s="4" t="n">
-        <v>1260000</v>
+        <v>-157719</v>
       </c>
       <c r="H288" s="3" t="s">
         <v>31</v>
@@ -8735,25 +8731,23 @@
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C289" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C289" s="3"/>
       <c r="D289" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G289" s="4" t="n">
-        <v>-157719</v>
+        <v>28885</v>
       </c>
       <c r="H289" s="3" t="s">
         <v>31</v>
@@ -8762,23 +8756,25 @@
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C290" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C290" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="D290" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E290" s="3" t="s">
-        <v>154</v>
+        <v>92</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G290" s="4" t="n">
-        <v>28885</v>
+        <v>16128</v>
       </c>
       <c r="H290" s="3" t="s">
         <v>31</v>
@@ -8796,7 +8792,7 @@
         <v>82</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E291" s="3" t="s">
         <v>92</v>
@@ -8805,7 +8801,7 @@
         <v>12</v>
       </c>
       <c r="G291" s="4" t="n">
-        <v>16128</v>
+        <v>20280</v>
       </c>
       <c r="H291" s="3" t="s">
         <v>31</v>
@@ -8823,7 +8819,7 @@
         <v>82</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E292" s="3" t="s">
         <v>92</v>
@@ -8832,7 +8828,7 @@
         <v>12</v>
       </c>
       <c r="G292" s="4" t="n">
-        <v>20280</v>
+        <v>18252</v>
       </c>
       <c r="H292" s="3" t="s">
         <v>31</v>
@@ -8850,7 +8846,7 @@
         <v>82</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E293" s="3" t="s">
         <v>92</v>
@@ -8859,7 +8855,7 @@
         <v>12</v>
       </c>
       <c r="G293" s="4" t="n">
-        <v>18252</v>
+        <v>17238</v>
       </c>
       <c r="H293" s="3" t="s">
         <v>31</v>
@@ -8877,7 +8873,7 @@
         <v>82</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E294" s="3" t="s">
         <v>92</v>
@@ -8886,7 +8882,7 @@
         <v>12</v>
       </c>
       <c r="G294" s="4" t="n">
-        <v>17238</v>
+        <v>18252</v>
       </c>
       <c r="H294" s="3" t="s">
         <v>31</v>
@@ -8904,7 +8900,7 @@
         <v>82</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E295" s="3" t="s">
         <v>92</v>
@@ -8913,7 +8909,7 @@
         <v>12</v>
       </c>
       <c r="G295" s="4" t="n">
-        <v>18252</v>
+        <v>16136</v>
       </c>
       <c r="H295" s="3" t="s">
         <v>31</v>
@@ -8931,7 +8927,7 @@
         <v>82</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E296" s="3" t="s">
         <v>92</v>
@@ -8940,7 +8936,7 @@
         <v>12</v>
       </c>
       <c r="G296" s="4" t="n">
-        <v>16136</v>
+        <v>26510</v>
       </c>
       <c r="H296" s="3" t="s">
         <v>31</v>
@@ -8958,16 +8954,16 @@
         <v>82</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>92</v>
+        <v>208</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G297" s="4" t="n">
-        <v>26510</v>
+        <v>688000</v>
       </c>
       <c r="H297" s="3" t="s">
         <v>31</v>
@@ -8982,19 +8978,19 @@
         <v>65</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G298" s="4" t="n">
-        <v>688000</v>
+        <v>48000</v>
       </c>
       <c r="H298" s="3" t="s">
         <v>31</v>
@@ -9012,16 +9008,16 @@
         <v>69</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G299" s="4" t="n">
-        <v>48000</v>
+        <v>473000</v>
       </c>
       <c r="H299" s="3" t="s">
         <v>31</v>
@@ -9036,19 +9032,19 @@
         <v>65</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G300" s="4" t="n">
-        <v>473000</v>
+        <v>229200</v>
       </c>
       <c r="H300" s="3" t="s">
         <v>31</v>
@@ -9063,19 +9059,19 @@
         <v>65</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G301" s="4" t="n">
-        <v>229200</v>
+        <v>190002</v>
       </c>
       <c r="H301" s="3" t="s">
         <v>31</v>
@@ -9084,25 +9080,25 @@
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="D302" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E302" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E302" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="F302" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G302" s="4" t="n">
-        <v>190002</v>
+        <v>999056</v>
       </c>
       <c r="H302" s="3" t="s">
         <v>31</v>
@@ -9117,19 +9113,19 @@
         <v>65</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="D303" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E303" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E303" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="F303" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G303" s="4" t="n">
-        <v>999056</v>
+        <v>195000</v>
       </c>
       <c r="H303" s="3" t="s">
         <v>31</v>
@@ -9147,16 +9143,16 @@
         <v>69</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>217</v>
+        <v>146</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G304" s="4" t="n">
-        <v>195000</v>
+        <v>70000</v>
       </c>
       <c r="H304" s="3" t="s">
         <v>31</v>
@@ -9168,22 +9164,20 @@
         <v>38</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C305" s="3" t="s">
-        <v>69</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C305" s="3"/>
       <c r="D305" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G305" s="4" t="n">
-        <v>70000</v>
+        <v>10381</v>
       </c>
       <c r="H305" s="3" t="s">
         <v>31</v>
@@ -9192,23 +9186,25 @@
     </row>
     <row r="306" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C306" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C306" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D306" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>154</v>
+        <v>68</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G306" s="4" t="n">
-        <v>10381</v>
+        <v>117500</v>
       </c>
       <c r="H306" s="3" t="s">
         <v>31</v>
@@ -9226,16 +9222,16 @@
         <v>66</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>68</v>
+        <v>218</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G307" s="4" t="n">
-        <v>117500</v>
+        <v>6000</v>
       </c>
       <c r="H307" s="3" t="s">
         <v>31</v>
@@ -9250,19 +9246,19 @@
         <v>65</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D308" s="3" t="s">
         <v>219</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G308" s="4" t="n">
-        <v>6000</v>
+        <v>80000</v>
       </c>
       <c r="H308" s="3" t="s">
         <v>31</v>
@@ -9280,16 +9276,16 @@
         <v>69</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G309" s="4" t="n">
-        <v>80000</v>
+        <v>280000</v>
       </c>
       <c r="H309" s="3" t="s">
         <v>31</v>
@@ -9307,16 +9303,16 @@
         <v>69</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G310" s="4" t="n">
-        <v>280000</v>
+        <v>100000</v>
       </c>
       <c r="H310" s="3" t="s">
         <v>31</v>
@@ -9334,16 +9330,16 @@
         <v>69</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G311" s="4" t="n">
-        <v>100000</v>
+        <v>140800</v>
       </c>
       <c r="H311" s="3" t="s">
         <v>31</v>
@@ -9352,7 +9348,7 @@
     </row>
     <row r="312" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>65</v>
@@ -9361,16 +9357,16 @@
         <v>69</v>
       </c>
       <c r="D312" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E312" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E312" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="F312" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G312" s="4" t="n">
-        <v>140800</v>
+        <v>51200</v>
       </c>
       <c r="H312" s="3" t="s">
         <v>31</v>
@@ -9385,19 +9381,19 @@
         <v>65</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D313" s="3" t="s">
         <v>224</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>225</v>
+        <v>198</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G313" s="4" t="n">
-        <v>51200</v>
+        <v>564697</v>
       </c>
       <c r="H313" s="3" t="s">
         <v>31</v>
@@ -9415,16 +9411,16 @@
         <v>79</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>200</v>
+        <v>116</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G314" s="4" t="n">
-        <v>564697</v>
+        <v>-112939</v>
       </c>
       <c r="H314" s="3" t="s">
         <v>31</v>
@@ -9436,22 +9432,20 @@
         <v>40</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C315" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C315" s="3"/>
       <c r="D315" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="F315" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G315" s="4" t="n">
-        <v>-112939</v>
+        <v>25752</v>
       </c>
       <c r="H315" s="3" t="s">
         <v>31</v>
@@ -9460,26 +9454,26 @@
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C316" s="3"/>
       <c r="D316" s="3" t="s">
-        <v>227</v>
+        <v>90</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G316" s="4" t="n">
-        <v>25752</v>
+        <v>119526</v>
       </c>
       <c r="H316" s="3" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I316" s="3"/>
     </row>
@@ -9488,20 +9482,22 @@
         <v>9</v>
       </c>
       <c r="B317" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C317" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C317" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="D317" s="3" t="s">
-        <v>90</v>
+        <v>226</v>
       </c>
       <c r="E317" s="3" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="F317" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G317" s="4" t="n">
-        <v>119526</v>
+        <v>25528</v>
       </c>
       <c r="H317" s="3" t="s">
         <v>13</v>
@@ -9519,7 +9515,7 @@
         <v>82</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>228</v>
+        <v>101</v>
       </c>
       <c r="E318" s="3" t="s">
         <v>92</v>
@@ -9528,7 +9524,7 @@
         <v>12</v>
       </c>
       <c r="G318" s="4" t="n">
-        <v>25528</v>
+        <v>23457</v>
       </c>
       <c r="H318" s="3" t="s">
         <v>13</v>
@@ -9546,7 +9542,7 @@
         <v>82</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="E319" s="3" t="s">
         <v>92</v>
@@ -9555,7 +9551,7 @@
         <v>12</v>
       </c>
       <c r="G319" s="4" t="n">
-        <v>23457</v>
+        <v>13154</v>
       </c>
       <c r="H319" s="3" t="s">
         <v>13</v>
@@ -9564,25 +9560,25 @@
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>92</v>
+        <v>155</v>
       </c>
       <c r="F320" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G320" s="4" t="n">
-        <v>13154</v>
+        <v>831231</v>
       </c>
       <c r="H320" s="3" t="s">
         <v>13</v>
@@ -9597,19 +9593,19 @@
         <v>65</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>144</v>
+        <v>227</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="F321" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G321" s="4" t="n">
-        <v>831231</v>
+        <v>46150</v>
       </c>
       <c r="H321" s="3" t="s">
         <v>13</v>
@@ -9627,16 +9623,16 @@
         <v>79</v>
       </c>
       <c r="D322" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E322" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E322" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="F322" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G322" s="4" t="n">
-        <v>46150</v>
+        <v>265505</v>
       </c>
       <c r="H322" s="3" t="s">
         <v>13</v>
@@ -9651,19 +9647,19 @@
         <v>65</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>231</v>
+        <v>155</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G323" s="4" t="n">
-        <v>265505</v>
+        <v>193766</v>
       </c>
       <c r="H323" s="3" t="s">
         <v>13</v>
@@ -9678,19 +9674,19 @@
         <v>65</v>
       </c>
       <c r="C324" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G324" s="4" t="n">
-        <v>193766</v>
+        <v>48350</v>
       </c>
       <c r="H324" s="3" t="s">
         <v>13</v>
@@ -9699,7 +9695,7 @@
     </row>
     <row r="325" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>65</v>
@@ -9708,16 +9704,16 @@
         <v>79</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G325" s="4" t="n">
-        <v>48350</v>
+        <v>29150</v>
       </c>
       <c r="H325" s="3" t="s">
         <v>13</v>
@@ -9732,19 +9728,19 @@
         <v>65</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G326" s="4" t="n">
-        <v>29150</v>
+        <v>37600</v>
       </c>
       <c r="H326" s="3" t="s">
         <v>13</v>
@@ -9756,20 +9752,22 @@
         <v>9</v>
       </c>
       <c r="B327" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C327" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C327" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D327" s="3" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="E327" s="3" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="F327" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G327" s="4" t="n">
-        <v>250000</v>
+        <v>74710</v>
       </c>
       <c r="H327" s="3" t="s">
         <v>13</v>
@@ -9784,19 +9782,19 @@
         <v>65</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G328" s="4" t="n">
-        <v>37600</v>
+        <v>27111</v>
       </c>
       <c r="H328" s="3" t="s">
         <v>13</v>
@@ -9805,7 +9803,7 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>65</v>
@@ -9814,16 +9812,16 @@
         <v>79</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>119</v>
+        <v>228</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>193</v>
+        <v>116</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G329" s="4" t="n">
-        <v>74710</v>
+        <v>-53101</v>
       </c>
       <c r="H329" s="3" t="s">
         <v>13</v>
@@ -9838,19 +9836,19 @@
         <v>65</v>
       </c>
       <c r="C330" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>119</v>
+        <v>226</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G330" s="4" t="n">
-        <v>27111</v>
+        <v>-7520</v>
       </c>
       <c r="H330" s="3" t="s">
         <v>13</v>
@@ -9859,25 +9857,23 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C331" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C331" s="3"/>
       <c r="D331" s="3" t="s">
-        <v>230</v>
+        <v>122</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G331" s="4" t="n">
-        <v>-53101</v>
+        <v>79835</v>
       </c>
       <c r="H331" s="3" t="s">
         <v>13</v>
@@ -9886,28 +9882,28 @@
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C332" s="3" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="D332" s="3" t="s">
         <v>228</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G332" s="4" t="n">
-        <v>-7520</v>
+        <v>771571</v>
       </c>
       <c r="H332" s="3" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="I332" s="3"/>
     </row>
@@ -9916,38 +9912,40 @@
         <v>9</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C333" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C333" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="D333" s="3" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>154</v>
+        <v>232</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G333" s="4" t="n">
-        <v>79835</v>
+        <v>159800</v>
       </c>
       <c r="H333" s="3" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="I333" s="3"/>
     </row>
     <row r="334" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C334" s="3" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>230</v>
+        <v>78</v>
       </c>
       <c r="E334" s="3" t="s">
         <v>233</v>
@@ -9956,7 +9954,7 @@
         <v>12</v>
       </c>
       <c r="G334" s="4" t="n">
-        <v>771571</v>
+        <v>142500</v>
       </c>
       <c r="H334" s="3" t="s">
         <v>64</v>
@@ -9971,10 +9969,10 @@
         <v>65</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E335" s="3" t="s">
         <v>234</v>
@@ -9983,7 +9981,7 @@
         <v>12</v>
       </c>
       <c r="G335" s="4" t="n">
-        <v>159800</v>
+        <v>60000</v>
       </c>
       <c r="H335" s="3" t="s">
         <v>64</v>
@@ -9998,19 +9996,19 @@
         <v>65</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G336" s="4" t="n">
-        <v>142500</v>
+        <v>95339</v>
       </c>
       <c r="H336" s="3" t="s">
         <v>64</v>
@@ -10025,19 +10023,19 @@
         <v>65</v>
       </c>
       <c r="C337" s="3" t="s">
-        <v>168</v>
+        <v>105</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>84</v>
+        <v>235</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G337" s="4" t="n">
-        <v>60000</v>
+        <v>174680</v>
       </c>
       <c r="H337" s="3" t="s">
         <v>64</v>
@@ -10052,19 +10050,19 @@
         <v>65</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>101</v>
+        <v>235</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G338" s="4" t="n">
-        <v>95339</v>
+        <v>477300</v>
       </c>
       <c r="H338" s="3" t="s">
         <v>64</v>
@@ -10079,35 +10077,33 @@
         <v>65</v>
       </c>
       <c r="C339" s="3" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>237</v>
+        <v>130</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="F339" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G339" s="4" t="n">
-        <v>174680</v>
+        <v>116250</v>
       </c>
       <c r="H339" s="3" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="I339" s="3"/>
     </row>
     <row r="340" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C340" s="3" t="s">
-        <v>105</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C340" s="3"/>
       <c r="D340" s="3" t="s">
         <v>237</v>
       </c>
@@ -10115,37 +10111,33 @@
         <v>238</v>
       </c>
       <c r="F340" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G340" s="4" t="n">
-        <v>477300</v>
+        <v>356000</v>
       </c>
       <c r="H340" s="3" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="I340" s="3"/>
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C341" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D341" s="3" t="s">
-        <v>130</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C341" s="3"/>
+      <c r="D341" s="3"/>
       <c r="E341" s="3" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="F341" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G341" s="4" t="n">
-        <v>116250</v>
+        <v>2833</v>
       </c>
       <c r="H341" s="3" t="s">
         <v>13</v>
@@ -10154,32 +10146,30 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B342" s="3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C342" s="3"/>
-      <c r="D342" s="3" t="s">
+      <c r="D342" s="3"/>
+      <c r="E342" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E342" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="F342" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G342" s="4" t="n">
-        <v>356000</v>
+        <v>3425</v>
       </c>
       <c r="H342" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I342" s="3"/>
     </row>
-    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>10</v>
@@ -10187,22 +10177,22 @@
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
       <c r="E343" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F343" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G343" s="4" t="n">
-        <v>2833</v>
+        <v>3866</v>
       </c>
       <c r="H343" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I343" s="3"/>
     </row>
-    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>10</v>
@@ -10210,22 +10200,22 @@
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
       <c r="E344" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F344" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G344" s="4" t="n">
-        <v>3425</v>
+        <v>4150</v>
       </c>
       <c r="H344" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I344" s="3"/>
     </row>
-    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>10</v>
@@ -10233,22 +10223,22 @@
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
       <c r="E345" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F345" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G345" s="4" t="n">
-        <v>3866</v>
+        <v>3625</v>
       </c>
       <c r="H345" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I345" s="3"/>
     </row>
-    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>10</v>
@@ -10256,22 +10246,22 @@
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
       <c r="E346" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F346" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G346" s="4" t="n">
-        <v>4150</v>
+        <v>2707</v>
       </c>
       <c r="H346" s="3" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="I346" s="3"/>
     </row>
-    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>10</v>
@@ -10279,214 +10269,222 @@
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
       <c r="E347" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G347" s="4" t="n">
-        <v>3625</v>
+        <v>2697</v>
       </c>
       <c r="H347" s="3" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="I347" s="3"/>
     </row>
-    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
       <c r="E348" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F348" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G348" s="4" t="n">
-        <v>2707</v>
+        <v>373520</v>
       </c>
       <c r="H348" s="3" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="I348" s="3"/>
     </row>
-    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
       <c r="E349" s="3" t="s">
-        <v>241</v>
+        <v>34</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G349" s="4" t="n">
-        <v>2697</v>
+        <v>60101</v>
       </c>
       <c r="H349" s="3" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="I349" s="3"/>
     </row>
-    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C350" s="3"/>
-      <c r="D350" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D350" s="3" t="s">
+        <v>237</v>
+      </c>
       <c r="E350" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G350" s="4" t="n">
-        <v>373520</v>
+        <v>294383</v>
       </c>
       <c r="H350" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I350" s="3"/>
     </row>
-    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C351" s="3"/>
-      <c r="D351" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C351" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D351" s="3" t="s">
+        <v>242</v>
+      </c>
       <c r="E351" s="3" t="s">
-        <v>34</v>
+        <v>243</v>
       </c>
       <c r="F351" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G351" s="4" t="n">
-        <v>60101</v>
+        <v>168000</v>
       </c>
       <c r="H351" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I351" s="3"/>
     </row>
-    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C352" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D352" s="3" t="s">
-        <v>239</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C352" s="3"/>
+      <c r="D352" s="3"/>
       <c r="E352" s="3" t="s">
-        <v>243</v>
+        <v>127</v>
       </c>
       <c r="F352" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G352" s="4" t="n">
-        <v>294383</v>
+        <v>134466</v>
       </c>
       <c r="H352" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I352" s="3"/>
     </row>
-    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C353" s="3" t="s">
-        <v>66</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C353" s="3"/>
       <c r="D353" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E353" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="E353" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="F353" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G353" s="4" t="n">
-        <v>168000</v>
+        <v>50982</v>
       </c>
       <c r="H353" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I353" s="3"/>
     </row>
-    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C354" s="3"/>
-      <c r="D354" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D354" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="E354" s="3" t="s">
-        <v>127</v>
+        <v>245</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G354" s="4" t="n">
-        <v>134466</v>
+        <v>936617</v>
       </c>
       <c r="H354" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I354" s="3"/>
     </row>
-    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C355" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C355" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D355" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>246</v>
+        <v>198</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G355" s="4" t="n">
-        <v>50982</v>
+        <v>207824</v>
       </c>
       <c r="H355" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I355" s="3"/>
     </row>
-    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="s">
         <v>36</v>
       </c>
@@ -10494,85 +10492,77 @@
         <v>65</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>177</v>
+        <v>246</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G356" s="4" t="n">
-        <v>936617</v>
+        <v>150000</v>
       </c>
       <c r="H356" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I356" s="3"/>
     </row>
-    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C357" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D357" s="3" t="s">
-        <v>178</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C357" s="3"/>
+      <c r="D357" s="3"/>
       <c r="E357" s="3" t="s">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="F357" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G357" s="4" t="n">
-        <v>207824</v>
+        <v>5603</v>
       </c>
       <c r="H357" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I357" s="3"/>
     </row>
-    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C358" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D358" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C358" s="3"/>
+      <c r="D358" s="3"/>
+      <c r="E358" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="E358" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="F358" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G358" s="4" t="n">
-        <v>150000</v>
+        <v>22727</v>
       </c>
       <c r="H358" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I358" s="3"/>
     </row>
-    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="C359" s="3"/>
       <c r="D359" s="3"/>
@@ -10583,60 +10573,68 @@
         <v>12</v>
       </c>
       <c r="G359" s="4" t="n">
-        <v>5603</v>
+        <v>373520</v>
       </c>
       <c r="H359" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I359" s="3"/>
     </row>
-    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C360" s="3"/>
-      <c r="D360" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C360" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D360" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="E360" s="3" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F360" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G360" s="4" t="n">
-        <v>22727</v>
+        <v>137000</v>
       </c>
       <c r="H360" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I360" s="3"/>
     </row>
-    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C361" s="3"/>
-      <c r="D361" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C361" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D361" s="3" t="s">
+        <v>207</v>
+      </c>
       <c r="E361" s="3" t="s">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G361" s="4" t="n">
-        <v>373520</v>
+        <v>395852</v>
       </c>
       <c r="H361" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I361" s="3"/>
     </row>
-    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="s">
         <v>36</v>
       </c>
@@ -10644,26 +10642,26 @@
         <v>65</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>208</v>
+        <v>250</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F362" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G362" s="4" t="n">
-        <v>137000</v>
+        <v>273847</v>
       </c>
       <c r="H362" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I362" s="3"/>
     </row>
-    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="s">
         <v>36</v>
       </c>
@@ -10671,26 +10669,26 @@
         <v>65</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G363" s="4" t="n">
-        <v>395852</v>
+        <v>195000</v>
       </c>
       <c r="H363" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I363" s="3"/>
     </row>
-    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="s">
         <v>36</v>
       </c>
@@ -10698,7 +10696,7 @@
         <v>65</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D364" s="3" t="s">
         <v>252</v>
@@ -10710,14 +10708,14 @@
         <v>12</v>
       </c>
       <c r="G364" s="4" t="n">
-        <v>273847</v>
+        <v>134486</v>
       </c>
       <c r="H364" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I364" s="3"/>
     </row>
-    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="s">
         <v>36</v>
       </c>
@@ -10725,26 +10723,26 @@
         <v>65</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G365" s="4" t="n">
-        <v>195000</v>
+        <v>48000</v>
       </c>
       <c r="H365" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I365" s="3"/>
     </row>
-    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="s">
         <v>36</v>
       </c>
@@ -10755,100 +10753,100 @@
         <v>79</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>255</v>
+        <v>198</v>
       </c>
       <c r="F366" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G366" s="4" t="n">
-        <v>134486</v>
+        <v>517066</v>
       </c>
       <c r="H366" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I366" s="3"/>
     </row>
-    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C367" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D367" s="3" t="s">
-        <v>256</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C367" s="3"/>
+      <c r="D367" s="3"/>
       <c r="E367" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F367" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G367" s="4" t="n">
+        <v>59589</v>
+      </c>
+      <c r="H367" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I367" s="3"/>
+    </row>
+    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A368" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B368" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C368" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D368" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="F367" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G367" s="4" t="n">
-        <v>48000</v>
-      </c>
-      <c r="H367" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I367" s="3"/>
-    </row>
-    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A368" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B368" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C368" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D368" s="3" t="s">
+      <c r="E368" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F368" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G368" s="4" t="n">
+        <v>127000</v>
+      </c>
+      <c r="H368" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I368" s="3"/>
+    </row>
+    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A369" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B369" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C369" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D369" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E368" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F368" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G368" s="4" t="n">
-        <v>517066</v>
-      </c>
-      <c r="H368" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I368" s="3"/>
-    </row>
-    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A369" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B369" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C369" s="3"/>
-      <c r="D369" s="3"/>
       <c r="E369" s="3" t="s">
-        <v>34</v>
+        <v>243</v>
       </c>
       <c r="F369" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G369" s="4" t="n">
-        <v>59589</v>
+        <v>112000</v>
       </c>
       <c r="H369" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I369" s="3"/>
     </row>
-    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="s">
         <v>38</v>
       </c>
@@ -10856,26 +10854,26 @@
         <v>65</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G370" s="4" t="n">
-        <v>127000</v>
+        <v>259730</v>
       </c>
       <c r="H370" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I370" s="3"/>
     </row>
-    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="s">
         <v>38</v>
       </c>
@@ -10883,10 +10881,10 @@
         <v>65</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>245</v>
@@ -10895,41 +10893,37 @@
         <v>12</v>
       </c>
       <c r="G371" s="4" t="n">
-        <v>112000</v>
+        <v>139453</v>
       </c>
       <c r="H371" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I371" s="3"/>
     </row>
-    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C372" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D372" s="3" t="s">
-        <v>260</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C372" s="3"/>
+      <c r="D372" s="3"/>
       <c r="E372" s="3" t="s">
-        <v>253</v>
+        <v>127</v>
       </c>
       <c r="F372" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G372" s="4" t="n">
-        <v>259730</v>
+        <v>132793</v>
       </c>
       <c r="H372" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I372" s="3"/>
     </row>
-    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="3" t="s">
         <v>38</v>
       </c>
@@ -10937,49 +10931,53 @@
         <v>65</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G373" s="4" t="n">
-        <v>139453</v>
+        <v>407000</v>
       </c>
       <c r="H373" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I373" s="3"/>
     </row>
-    <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C374" s="3"/>
-      <c r="D374" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C374" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D374" s="3" t="s">
+        <v>261</v>
+      </c>
       <c r="E374" s="3" t="s">
-        <v>127</v>
+        <v>245</v>
       </c>
       <c r="F374" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G374" s="4" t="n">
-        <v>132793</v>
+        <v>929706</v>
       </c>
       <c r="H374" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I374" s="3"/>
     </row>
-    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="3" t="s">
         <v>38</v>
       </c>
@@ -10987,26 +10985,26 @@
         <v>65</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="D375" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E375" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E375" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="F375" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G375" s="4" t="n">
-        <v>407000</v>
+        <v>878500</v>
       </c>
       <c r="H375" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I375" s="3"/>
     </row>
-    <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="3" t="s">
         <v>38</v>
       </c>
@@ -11017,23 +11015,23 @@
         <v>79</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>263</v>
+        <v>216</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>247</v>
+        <v>198</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G376" s="4" t="n">
-        <v>929706</v>
+        <v>328125</v>
       </c>
       <c r="H376" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I376" s="3"/>
     </row>
-    <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="3" t="s">
         <v>38</v>
       </c>
@@ -11041,26 +11039,26 @@
         <v>65</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>168</v>
+        <v>66</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G377" s="4" t="n">
-        <v>878500</v>
+        <v>166000</v>
       </c>
       <c r="H377" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I377" s="3"/>
     </row>
-    <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="3" t="s">
         <v>38</v>
       </c>
@@ -11068,149 +11066,149 @@
         <v>65</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D378" s="3" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="E378" s="3" t="s">
-        <v>200</v>
+        <v>251</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G378" s="4" t="n">
-        <v>328125</v>
+        <v>270622</v>
       </c>
       <c r="H378" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I378" s="3"/>
     </row>
-    <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C379" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D379" s="3" t="s">
-        <v>265</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C379" s="3"/>
+      <c r="D379" s="3"/>
       <c r="E379" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G379" s="4" t="n">
-        <v>166000</v>
+        <v>11516</v>
       </c>
       <c r="H379" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I379" s="3"/>
     </row>
-    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C380" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D380" s="3" t="s">
-        <v>266</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C380" s="3"/>
+      <c r="D380" s="3"/>
       <c r="E380" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G380" s="4" t="n">
-        <v>270622</v>
+        <v>22727</v>
       </c>
       <c r="H380" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I380" s="3"/>
     </row>
-    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
       <c r="E381" s="3" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G381" s="4" t="n">
-        <v>11516</v>
+        <v>373520</v>
       </c>
       <c r="H381" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I381" s="3"/>
     </row>
-    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="3" t="s">
         <v>38</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C382" s="3"/>
-      <c r="D382" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C382" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D382" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="E382" s="3" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F382" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G382" s="4" t="n">
-        <v>22727</v>
+        <v>181000</v>
       </c>
       <c r="H382" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I382" s="3"/>
     </row>
-    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C383" s="3"/>
-      <c r="D383" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C383" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D383" s="3" t="s">
+        <v>267</v>
+      </c>
       <c r="E383" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G383" s="4" t="n">
-        <v>373520</v>
+        <v>78400</v>
       </c>
       <c r="H383" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I383" s="3"/>
     </row>
-    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="3" t="s">
         <v>38</v>
       </c>
@@ -11218,26 +11216,26 @@
         <v>65</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G384" s="4" t="n">
-        <v>181000</v>
+        <v>440300</v>
       </c>
       <c r="H384" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I384" s="3"/>
     </row>
-    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="3" t="s">
         <v>38</v>
       </c>
@@ -11245,26 +11243,26 @@
         <v>65</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G385" s="4" t="n">
-        <v>78400</v>
+        <v>265341</v>
       </c>
       <c r="H385" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I385" s="3"/>
     </row>
-    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="3" t="s">
         <v>38</v>
       </c>
@@ -11272,26 +11270,26 @@
         <v>65</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D386" s="3" t="s">
         <v>271</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G386" s="4" t="n">
-        <v>440300</v>
+        <v>243191</v>
       </c>
       <c r="H386" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I386" s="3"/>
     </row>
-    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="3" t="s">
         <v>38</v>
       </c>
@@ -11299,26 +11297,26 @@
         <v>65</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>273</v>
+        <v>147</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G387" s="4" t="n">
-        <v>265341</v>
+        <v>239000</v>
       </c>
       <c r="H387" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I387" s="3"/>
     </row>
-    <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="3" t="s">
         <v>38</v>
       </c>
@@ -11326,26 +11324,26 @@
         <v>65</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>273</v>
+        <v>147</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G388" s="4" t="n">
-        <v>243191</v>
+        <v>261384</v>
       </c>
       <c r="H388" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I388" s="3"/>
     </row>
-    <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="3" t="s">
         <v>38</v>
       </c>
@@ -11353,80 +11351,76 @@
         <v>65</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>245</v>
+        <v>198</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G389" s="4" t="n">
-        <v>239000</v>
+        <v>387502</v>
       </c>
       <c r="H389" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I389" s="3"/>
     </row>
-    <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D390" s="3" t="s">
-        <v>149</v>
+        <v>274</v>
       </c>
       <c r="E390" s="3" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G390" s="4" t="n">
-        <v>261384</v>
+        <v>260955</v>
       </c>
       <c r="H390" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I390" s="3"/>
     </row>
-    <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C391" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D391" s="3" t="s">
-        <v>152</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C391" s="3"/>
+      <c r="D391" s="3"/>
       <c r="E391" s="3" t="s">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="F391" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G391" s="4" t="n">
-        <v>387502</v>
+        <v>57831</v>
       </c>
       <c r="H391" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I391" s="3"/>
     </row>
-    <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="3" t="s">
         <v>39</v>
       </c>
@@ -11434,49 +11428,53 @@
         <v>65</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D392" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G392" s="4" t="n">
-        <v>260955</v>
+        <v>178000</v>
       </c>
       <c r="H392" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I392" s="3"/>
     </row>
-    <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C393" s="3"/>
-      <c r="D393" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C393" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D393" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E393" s="3" t="s">
-        <v>34</v>
+        <v>276</v>
       </c>
       <c r="F393" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G393" s="4" t="n">
-        <v>57831</v>
+        <v>122000</v>
       </c>
       <c r="H393" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I393" s="3"/>
     </row>
-    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="3" t="s">
         <v>39</v>
       </c>
@@ -11484,10 +11482,10 @@
         <v>65</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E394" s="3" t="s">
         <v>277</v>
@@ -11496,14 +11494,14 @@
         <v>12</v>
       </c>
       <c r="G394" s="4" t="n">
-        <v>178000</v>
+        <v>233052</v>
       </c>
       <c r="H394" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I394" s="3"/>
     </row>
-    <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="3" t="s">
         <v>39</v>
       </c>
@@ -11511,153 +11509,153 @@
         <v>65</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D395" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E395" s="3" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G395" s="4" t="n">
-        <v>122000</v>
+        <v>535511</v>
       </c>
       <c r="H395" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I395" s="3"/>
     </row>
-    <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C396" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D396" s="3" t="s">
-        <v>276</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C396" s="3"/>
+      <c r="D396" s="3"/>
       <c r="E396" s="3" t="s">
-        <v>279</v>
+        <v>127</v>
       </c>
       <c r="F396" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G396" s="4" t="n">
-        <v>233052</v>
+        <v>131201</v>
       </c>
       <c r="H396" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I396" s="3"/>
     </row>
-    <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C397" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C397" s="3"/>
       <c r="D397" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E397" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="E397" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="F397" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G397" s="4" t="n">
-        <v>535511</v>
+        <v>41329</v>
       </c>
       <c r="H397" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I397" s="3"/>
     </row>
-    <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="398" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C398" s="3"/>
-      <c r="D398" s="3"/>
+      <c r="D398" s="3" t="s">
+        <v>279</v>
+      </c>
       <c r="E398" s="3" t="s">
-        <v>127</v>
+        <v>280</v>
       </c>
       <c r="F398" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G398" s="4" t="n">
-        <v>131201</v>
+        <v>111000</v>
       </c>
       <c r="H398" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I398" s="3"/>
     </row>
-    <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C399" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C399" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D399" s="3" t="s">
         <v>281</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G399" s="4" t="n">
-        <v>41329</v>
+        <v>183000</v>
       </c>
       <c r="H399" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I399" s="3"/>
     </row>
-    <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C400" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C400" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="D400" s="3" t="s">
         <v>281</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>282</v>
+        <v>251</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G400" s="4" t="n">
-        <v>111000</v>
+        <v>274095</v>
       </c>
       <c r="H400" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I400" s="3"/>
     </row>
-    <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="3" t="s">
         <v>39</v>
       </c>
@@ -11665,26 +11663,26 @@
         <v>65</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G401" s="4" t="n">
-        <v>183000</v>
+        <v>67482</v>
       </c>
       <c r="H401" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I401" s="3"/>
     </row>
-    <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="402" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="3" t="s">
         <v>39</v>
       </c>
@@ -11692,26 +11690,26 @@
         <v>65</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="D402" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E402" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="E402" s="3" t="s">
-        <v>253</v>
-      </c>
       <c r="F402" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G402" s="4" t="n">
-        <v>274095</v>
+        <v>135896</v>
       </c>
       <c r="H402" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I402" s="3"/>
     </row>
-    <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="3" t="s">
         <v>39</v>
       </c>
@@ -11719,26 +11717,26 @@
         <v>65</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="D403" s="3" t="s">
         <v>284</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="F403" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G403" s="4" t="n">
-        <v>67482</v>
+        <v>172000</v>
       </c>
       <c r="H403" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I403" s="3"/>
     </row>
-    <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="3" t="s">
         <v>39</v>
       </c>
@@ -11746,26 +11744,26 @@
         <v>65</v>
       </c>
       <c r="C404" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="F404" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G404" s="4" t="n">
-        <v>135896</v>
+        <v>216568</v>
       </c>
       <c r="H404" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I404" s="3"/>
     </row>
-    <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="3" t="s">
         <v>39</v>
       </c>
@@ -11773,26 +11771,26 @@
         <v>65</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="D405" s="3" t="s">
         <v>286</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>287</v>
+        <v>243</v>
       </c>
       <c r="F405" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G405" s="4" t="n">
-        <v>172000</v>
+        <v>252000</v>
       </c>
       <c r="H405" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I405" s="3"/>
     </row>
-    <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="3" t="s">
         <v>39</v>
       </c>
@@ -11800,26 +11798,26 @@
         <v>65</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="F406" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G406" s="4" t="n">
-        <v>216568</v>
+        <v>200000</v>
       </c>
       <c r="H406" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I406" s="3"/>
     </row>
-    <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="3" t="s">
         <v>39</v>
       </c>
@@ -11827,26 +11825,26 @@
         <v>65</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="F407" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G407" s="4" t="n">
-        <v>252000</v>
+        <v>307699</v>
       </c>
       <c r="H407" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I407" s="3"/>
     </row>
-    <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="3" t="s">
         <v>39</v>
       </c>
@@ -11854,26 +11852,26 @@
         <v>65</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F408" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G408" s="4" t="n">
-        <v>200000</v>
+        <v>70384</v>
       </c>
       <c r="H408" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I408" s="3"/>
     </row>
-    <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="3" t="s">
         <v>39</v>
       </c>
@@ -11884,23 +11882,23 @@
         <v>79</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="F409" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G409" s="4" t="n">
-        <v>307699</v>
+        <v>815782</v>
       </c>
       <c r="H409" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I409" s="3"/>
     </row>
-    <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="3" t="s">
         <v>39</v>
       </c>
@@ -11908,26 +11906,26 @@
         <v>65</v>
       </c>
       <c r="C410" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>292</v>
+        <v>151</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>293</v>
+        <v>251</v>
       </c>
       <c r="F410" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G410" s="4" t="n">
-        <v>70384</v>
+        <v>291772</v>
       </c>
       <c r="H410" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I410" s="3"/>
     </row>
-    <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="3" t="s">
         <v>39</v>
       </c>
@@ -11935,26 +11933,26 @@
         <v>65</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="F411" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G411" s="4" t="n">
-        <v>815782</v>
+        <v>103000</v>
       </c>
       <c r="H411" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I411" s="3"/>
     </row>
-    <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="3" t="s">
         <v>39</v>
       </c>
@@ -11962,53 +11960,49 @@
         <v>65</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>153</v>
+        <v>292</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="F412" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G412" s="4" t="n">
-        <v>291772</v>
+        <v>175000</v>
       </c>
       <c r="H412" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I412" s="3"/>
     </row>
-    <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C413" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D413" s="3" t="s">
-        <v>294</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C413" s="3"/>
+      <c r="D413" s="3"/>
       <c r="E413" s="3" t="s">
-        <v>295</v>
+        <v>248</v>
       </c>
       <c r="F413" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G413" s="4" t="n">
-        <v>103000</v>
+        <v>22727</v>
       </c>
       <c r="H413" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I413" s="3"/>
     </row>
-    <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="3" t="s">
         <v>39</v>
       </c>
@@ -12016,159 +12010,163 @@
         <v>65</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D414" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E414" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="E414" s="3" t="s">
-        <v>245</v>
-      </c>
       <c r="F414" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G414" s="4" t="n">
-        <v>175000</v>
+        <v>115276</v>
       </c>
       <c r="H414" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I414" s="3"/>
     </row>
-    <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C415" s="3"/>
       <c r="D415" s="3"/>
       <c r="E415" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F415" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G415" s="4" t="n">
-        <v>22727</v>
+        <v>15928</v>
       </c>
       <c r="H415" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I415" s="3"/>
     </row>
-    <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C416" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C416" s="3"/>
       <c r="D416" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E416" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F416" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G416" s="4" t="n">
+        <v>139920</v>
+      </c>
+      <c r="H416" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I416" s="3"/>
+    </row>
+    <row r="417" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A417" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B417" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C417" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D417" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E417" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="F416" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G416" s="4" t="n">
-        <v>115276</v>
-      </c>
-      <c r="H416" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I416" s="3"/>
-    </row>
-    <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A417" s="3" t="s">
+      <c r="F417" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G417" s="4" t="n">
+        <v>440300</v>
+      </c>
+      <c r="H417" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I417" s="3"/>
+    </row>
+    <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A418" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B418" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C418" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D418" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E418" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F418" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G418" s="4" t="n">
+        <v>172000</v>
+      </c>
+      <c r="H418" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I418" s="3"/>
+    </row>
+    <row r="419" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A419" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B417" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C417" s="3"/>
-      <c r="D417" s="3"/>
-      <c r="E417" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F417" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G417" s="4" t="n">
-        <v>15928</v>
-      </c>
-      <c r="H417" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I417" s="3"/>
-    </row>
-    <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A418" s="3" t="s">
+      <c r="B419" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C419" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D419" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E419" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F419" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G419" s="4" t="n">
+        <v>65806</v>
+      </c>
+      <c r="H419" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I419" s="3"/>
+    </row>
+    <row r="420" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A420" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B418" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C418" s="3"/>
-      <c r="D418" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="E418" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="F418" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G418" s="4" t="n">
-        <v>139920</v>
-      </c>
-      <c r="H418" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I418" s="3"/>
-    </row>
-    <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A419" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B419" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C419" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D419" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E419" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F419" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G419" s="4" t="n">
-        <v>440300</v>
-      </c>
-      <c r="H419" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I419" s="3"/>
-    </row>
-    <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A420" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="B420" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D420" s="3" t="s">
         <v>299</v>
@@ -12180,14 +12178,14 @@
         <v>12</v>
       </c>
       <c r="G420" s="4" t="n">
-        <v>172000</v>
+        <v>-65860</v>
       </c>
       <c r="H420" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I420" s="3"/>
     </row>
-    <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="421" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="3" t="s">
         <v>39</v>
       </c>
@@ -12195,53 +12193,49 @@
         <v>65</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>222</v>
+        <v>135</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="F421" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G421" s="4" t="n">
-        <v>65806</v>
+        <v>305000</v>
       </c>
       <c r="H421" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I421" s="3"/>
     </row>
-    <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="422" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C422" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D422" s="3" t="s">
-        <v>301</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C422" s="3"/>
+      <c r="D422" s="3"/>
       <c r="E422" s="3" t="s">
-        <v>302</v>
+        <v>34</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G422" s="4" t="n">
-        <v>-65860</v>
+        <v>58534</v>
       </c>
       <c r="H422" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I422" s="3"/>
     </row>
-    <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="s">
         <v>39</v>
       </c>
@@ -12249,76 +12243,80 @@
         <v>65</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>135</v>
+        <v>302</v>
       </c>
       <c r="E423" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="F423" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G423" s="4" t="n">
+        <v>93993</v>
+      </c>
+      <c r="H423" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I423" s="3"/>
+    </row>
+    <row r="424" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A424" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B424" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C424" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D424" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="F423" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G423" s="4" t="n">
-        <v>305000</v>
-      </c>
-      <c r="H423" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I423" s="3"/>
-    </row>
-    <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A424" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B424" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C424" s="3"/>
-      <c r="D424" s="3"/>
       <c r="E424" s="3" t="s">
-        <v>34</v>
+        <v>245</v>
       </c>
       <c r="F424" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G424" s="4" t="n">
-        <v>58534</v>
+        <v>163150</v>
       </c>
       <c r="H424" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I424" s="3"/>
     </row>
-    <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="D425" s="3" t="s">
         <v>304</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>293</v>
+        <v>171</v>
       </c>
       <c r="F425" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G425" s="4" t="n">
-        <v>93993</v>
+        <v>360000</v>
       </c>
       <c r="H425" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I425" s="3"/>
     </row>
-    <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="3" t="s">
         <v>40</v>
       </c>
@@ -12329,23 +12327,23 @@
         <v>79</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="F426" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G426" s="4" t="n">
-        <v>163150</v>
+        <v>52150</v>
       </c>
       <c r="H426" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I426" s="3"/>
     </row>
-    <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="3" t="s">
         <v>40</v>
       </c>
@@ -12353,26 +12351,26 @@
         <v>65</v>
       </c>
       <c r="C427" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D427" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>173</v>
+        <v>305</v>
       </c>
       <c r="F427" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G427" s="4" t="n">
-        <v>360000</v>
+        <v>84900</v>
       </c>
       <c r="H427" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I427" s="3"/>
     </row>
-    <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="428" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="3" t="s">
         <v>40</v>
       </c>
@@ -12383,23 +12381,23 @@
         <v>79</v>
       </c>
       <c r="D428" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E428" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="E428" s="3" t="s">
-        <v>296</v>
-      </c>
       <c r="F428" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G428" s="4" t="n">
-        <v>52150</v>
+        <v>648804</v>
       </c>
       <c r="H428" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I428" s="3"/>
     </row>
-    <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="3" t="s">
         <v>40</v>
       </c>
@@ -12410,50 +12408,46 @@
         <v>79</v>
       </c>
       <c r="D429" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E429" s="3" t="s">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="F429" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G429" s="4" t="n">
-        <v>84900</v>
+        <v>781672</v>
       </c>
       <c r="H429" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I429" s="3"/>
     </row>
-    <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C430" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D430" s="3" t="s">
-        <v>306</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C430" s="3"/>
+      <c r="D430" s="3"/>
       <c r="E430" s="3" t="s">
-        <v>308</v>
+        <v>127</v>
       </c>
       <c r="F430" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G430" s="4" t="n">
-        <v>648804</v>
+        <v>132190</v>
       </c>
       <c r="H430" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I430" s="3"/>
     </row>
-    <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="3" t="s">
         <v>40</v>
       </c>
@@ -12461,49 +12455,53 @@
         <v>65</v>
       </c>
       <c r="C431" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D431" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>247</v>
+        <v>308</v>
       </c>
       <c r="F431" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G431" s="4" t="n">
-        <v>781672</v>
+        <v>140000</v>
       </c>
       <c r="H431" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I431" s="3"/>
     </row>
-    <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C432" s="3"/>
-      <c r="D432" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C432" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D432" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="E432" s="3" t="s">
-        <v>127</v>
+        <v>309</v>
       </c>
       <c r="F432" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G432" s="4" t="n">
-        <v>132190</v>
+        <v>30000</v>
       </c>
       <c r="H432" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I432" s="3"/>
     </row>
-    <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="3" t="s">
         <v>40</v>
       </c>
@@ -12511,26 +12509,26 @@
         <v>65</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>309</v>
+        <v>224</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>310</v>
+        <v>243</v>
       </c>
       <c r="F433" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G433" s="4" t="n">
-        <v>140000</v>
+        <v>82000</v>
       </c>
       <c r="H433" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I433" s="3"/>
     </row>
-    <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="3" t="s">
         <v>40</v>
       </c>
@@ -12538,26 +12536,26 @@
         <v>65</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="D434" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="F434" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G434" s="4" t="n">
-        <v>30000</v>
+        <v>312133</v>
       </c>
       <c r="H434" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I434" s="3"/>
     </row>
-    <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="3" t="s">
         <v>40</v>
       </c>
@@ -12565,53 +12563,51 @@
         <v>65</v>
       </c>
       <c r="C435" s="3" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>226</v>
+        <v>310</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>245</v>
+        <v>311</v>
       </c>
       <c r="F435" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G435" s="4" t="n">
-        <v>82000</v>
+        <v>261000</v>
       </c>
       <c r="H435" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I435" s="3"/>
     </row>
-    <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C436" s="3" t="s">
-        <v>94</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C436" s="3"/>
       <c r="D436" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E436" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="E436" s="3" t="s">
-        <v>303</v>
-      </c>
       <c r="F436" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G436" s="4" t="n">
-        <v>312133</v>
+        <v>2392425</v>
       </c>
       <c r="H436" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I436" s="3"/>
     </row>
-    <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="3" t="s">
         <v>40</v>
       </c>
@@ -12619,51 +12615,53 @@
         <v>65</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>168</v>
+        <v>66</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>313</v>
+        <v>243</v>
       </c>
       <c r="F437" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G437" s="4" t="n">
-        <v>261000</v>
+        <v>143000</v>
       </c>
       <c r="H437" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I437" s="3"/>
     </row>
-    <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B438" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C438" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C438" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D438" s="3" t="s">
-        <v>227</v>
+        <v>295</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>314</v>
+        <v>272</v>
       </c>
       <c r="F438" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G438" s="4" t="n">
-        <v>2392425</v>
+        <v>364400</v>
       </c>
       <c r="H438" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I438" s="3"/>
     </row>
-    <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="3" t="s">
         <v>40</v>
       </c>
@@ -12671,255 +12669,253 @@
         <v>65</v>
       </c>
       <c r="C439" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D439" s="3" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="E439" s="3" t="s">
-        <v>245</v>
+        <v>294</v>
       </c>
       <c r="F439" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G439" s="4" t="n">
-        <v>143000</v>
+        <v>74761</v>
       </c>
       <c r="H439" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I439" s="3"/>
     </row>
-    <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C440" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D440" s="3" t="s">
-        <v>297</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C440" s="3"/>
+      <c r="D440" s="3"/>
       <c r="E440" s="3" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G440" s="4" t="n">
-        <v>364400</v>
+        <v>22727</v>
       </c>
       <c r="H440" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I440" s="3"/>
     </row>
-    <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="s">
         <v>40</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C441" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D441" s="3" t="s">
-        <v>297</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C441" s="3"/>
+      <c r="D441" s="3"/>
       <c r="E441" s="3" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F441" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G441" s="4" t="n">
-        <v>74761</v>
+        <v>18773</v>
       </c>
       <c r="H441" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I441" s="3"/>
     </row>
-    <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B442" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C442" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D442" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E442" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="F442" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G442" s="4" t="n">
+        <v>440300</v>
+      </c>
+      <c r="H442" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I442" s="3"/>
+    </row>
+    <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A443" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B443" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C443" s="3"/>
+      <c r="D443" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E443" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="F443" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G443" s="4" t="n">
+        <v>2392425</v>
+      </c>
+      <c r="H443" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I443" s="3"/>
+    </row>
+    <row r="444" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A444" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B442" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C442" s="3"/>
-      <c r="D442" s="3"/>
-      <c r="E442" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F442" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G442" s="4" t="n">
-        <v>22727</v>
-      </c>
-      <c r="H442" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I442" s="3"/>
-    </row>
-    <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A443" s="3" t="s">
+      <c r="B444" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C444" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D444" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E444" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F444" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G444" s="4" t="n">
+        <v>243000</v>
+      </c>
+      <c r="H444" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I444" s="3"/>
+    </row>
+    <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A445" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B443" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C443" s="3"/>
-      <c r="D443" s="3"/>
-      <c r="E443" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F443" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G443" s="4" t="n">
-        <v>18773</v>
-      </c>
-      <c r="H443" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I443" s="3"/>
-    </row>
-    <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A444" s="3" t="s">
+      <c r="B445" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C445" s="3"/>
+      <c r="D445" s="3"/>
+      <c r="E445" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F445" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G445" s="4" t="n">
+        <v>55994</v>
+      </c>
+      <c r="H445" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I445" s="3"/>
+    </row>
+    <row r="446" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A446" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B444" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C444" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D444" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="E444" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F444" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G444" s="4" t="n">
-        <v>440300</v>
-      </c>
-      <c r="H444" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I444" s="3"/>
-    </row>
-    <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A445" s="3" t="s">
+      <c r="B446" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C446" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D446" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E446" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F446" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G446" s="4" t="n">
+        <v>308968</v>
+      </c>
+      <c r="H446" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I446" s="3"/>
+    </row>
+    <row r="447" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A447" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B445" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C445" s="3"/>
-      <c r="D445" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="E445" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="F445" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G445" s="4" t="n">
-        <v>2392425</v>
-      </c>
-      <c r="H445" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I445" s="3"/>
-    </row>
-    <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A446" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B446" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C446" s="3" t="s">
+      <c r="B447" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C447" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D446" s="3" t="s">
+      <c r="D447" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="E446" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F446" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G446" s="4" t="n">
-        <v>243000</v>
-      </c>
-      <c r="H446" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I446" s="3"/>
-    </row>
-    <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A447" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B447" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C447" s="3"/>
-      <c r="D447" s="3"/>
       <c r="E447" s="3" t="s">
-        <v>34</v>
+        <v>243</v>
       </c>
       <c r="F447" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G447" s="4" t="n">
-        <v>55994</v>
+        <v>107000</v>
       </c>
       <c r="H447" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I447" s="3"/>
     </row>
-    <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C448" s="3" t="s">
-        <v>94</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C448" s="3"/>
       <c r="D448" s="3" t="s">
         <v>321</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>253</v>
+        <v>322</v>
       </c>
       <c r="F448" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G448" s="4" t="n">
-        <v>308968</v>
+        <v>50000</v>
       </c>
       <c r="H448" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I448" s="3"/>
     </row>
-    <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="3" t="s">
         <v>41</v>
       </c>
@@ -12927,51 +12923,49 @@
         <v>65</v>
       </c>
       <c r="C449" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>245</v>
+        <v>323</v>
       </c>
       <c r="F449" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G449" s="4" t="n">
-        <v>107000</v>
+        <v>435994</v>
       </c>
       <c r="H449" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I449" s="3"/>
     </row>
-    <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C450" s="3"/>
-      <c r="D450" s="3" t="s">
-        <v>323</v>
-      </c>
+      <c r="D450" s="3"/>
       <c r="E450" s="3" t="s">
-        <v>324</v>
+        <v>127</v>
       </c>
       <c r="F450" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G450" s="4" t="n">
-        <v>50000</v>
+        <v>121469</v>
       </c>
       <c r="H450" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I450" s="3"/>
     </row>
-    <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="3" t="s">
         <v>41</v>
       </c>
@@ -12979,49 +12973,53 @@
         <v>65</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>323</v>
+        <v>201</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="F451" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G451" s="4" t="n">
-        <v>435994</v>
+        <v>73327</v>
       </c>
       <c r="H451" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I451" s="3"/>
     </row>
-    <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="452" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B452" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C452" s="3"/>
-      <c r="D452" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C452" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D452" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="E452" s="3" t="s">
-        <v>127</v>
+        <v>243</v>
       </c>
       <c r="F452" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G452" s="4" t="n">
-        <v>121469</v>
+        <v>214000</v>
       </c>
       <c r="H452" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I452" s="3"/>
     </row>
-    <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="453" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="3" t="s">
         <v>41</v>
       </c>
@@ -13029,130 +13027,130 @@
         <v>65</v>
       </c>
       <c r="C453" s="3" t="s">
-        <v>95</v>
+        <v>166</v>
       </c>
       <c r="D453" s="3" t="s">
-        <v>203</v>
+        <v>324</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>293</v>
+        <v>325</v>
       </c>
       <c r="F453" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G453" s="4" t="n">
-        <v>73327</v>
+        <v>56000</v>
       </c>
       <c r="H453" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I453" s="3"/>
     </row>
-    <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B454" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C454" s="3" t="s">
-        <v>66</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C454" s="3"/>
       <c r="D454" s="3" t="s">
         <v>326</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>245</v>
+        <v>327</v>
       </c>
       <c r="F454" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G454" s="4" t="n">
-        <v>214000</v>
+        <v>425242</v>
       </c>
       <c r="H454" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I454" s="3"/>
     </row>
-    <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C455" s="3" t="s">
-        <v>168</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C455" s="3"/>
       <c r="D455" s="3" t="s">
-        <v>326</v>
+        <v>203</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F455" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G455" s="4" t="n">
-        <v>56000</v>
+        <v>296076</v>
       </c>
       <c r="H455" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I455" s="3"/>
     </row>
-    <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B456" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C456" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C456" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D456" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>329</v>
+        <v>245</v>
       </c>
       <c r="F456" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G456" s="4" t="n">
-        <v>425242</v>
+        <v>619681</v>
       </c>
       <c r="H456" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I456" s="3"/>
     </row>
-    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B457" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C457" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C457" s="3" t="s">
+        <v>94</v>
+      </c>
       <c r="D457" s="3" t="s">
-        <v>205</v>
+        <v>330</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="F457" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G457" s="4" t="n">
-        <v>296076</v>
+        <v>295000</v>
       </c>
       <c r="H457" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I457" s="3"/>
     </row>
-    <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="458" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="3" t="s">
         <v>41</v>
       </c>
@@ -13160,53 +13158,51 @@
         <v>65</v>
       </c>
       <c r="C458" s="3" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D458" s="3" t="s">
         <v>331</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="F458" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G458" s="4" t="n">
-        <v>619681</v>
+        <v>61717</v>
       </c>
       <c r="H458" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I458" s="3"/>
     </row>
-    <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="459" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C459" s="3" t="s">
-        <v>94</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C459" s="3"/>
       <c r="D459" s="3" t="s">
         <v>332</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="F459" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G459" s="4" t="n">
-        <v>295000</v>
+        <v>277650</v>
       </c>
       <c r="H459" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I459" s="3"/>
     </row>
-    <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="460" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="3" t="s">
         <v>41</v>
       </c>
@@ -13214,51 +13210,53 @@
         <v>65</v>
       </c>
       <c r="C460" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>293</v>
+        <v>334</v>
       </c>
       <c r="F460" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G460" s="4" t="n">
-        <v>61717</v>
+        <v>450185</v>
       </c>
       <c r="H460" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I460" s="3"/>
     </row>
-    <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="461" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B461" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C461" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C461" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D461" s="3" t="s">
-        <v>334</v>
+        <v>180</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>335</v>
+        <v>243</v>
       </c>
       <c r="F461" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G461" s="4" t="n">
-        <v>277650</v>
+        <v>112000</v>
       </c>
       <c r="H461" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I461" s="3"/>
     </row>
-    <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="462" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="3" t="s">
         <v>41</v>
       </c>
@@ -13266,176 +13264,176 @@
         <v>65</v>
       </c>
       <c r="C462" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D462" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>336</v>
+        <v>272</v>
       </c>
       <c r="F462" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G462" s="4" t="n">
-        <v>450185</v>
+        <v>332275</v>
       </c>
       <c r="H462" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I462" s="3"/>
     </row>
-    <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="463" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C463" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D463" s="3" t="s">
-        <v>182</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C463" s="3"/>
+      <c r="D463" s="3"/>
       <c r="E463" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F463" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G463" s="4" t="n">
-        <v>112000</v>
+        <v>13525</v>
       </c>
       <c r="H463" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I463" s="3"/>
     </row>
-    <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C464" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D464" s="3" t="s">
-        <v>337</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C464" s="3"/>
+      <c r="D464" s="3"/>
       <c r="E464" s="3" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G464" s="4" t="n">
-        <v>332275</v>
+        <v>22727</v>
       </c>
       <c r="H464" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I464" s="3"/>
     </row>
-    <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="465" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C465" s="3"/>
-      <c r="D465" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C465" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D465" s="3" t="s">
+        <v>184</v>
+      </c>
       <c r="E465" s="3" t="s">
-        <v>249</v>
+        <v>336</v>
       </c>
       <c r="F465" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G465" s="4" t="n">
-        <v>13525</v>
+        <v>32700</v>
       </c>
       <c r="H465" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I465" s="3"/>
     </row>
-    <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="466" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="3" t="s">
         <v>41</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C466" s="3"/>
       <c r="D466" s="3"/>
       <c r="E466" s="3" t="s">
-        <v>250</v>
+        <v>34</v>
       </c>
       <c r="F466" s="3" t="s">
         <v>18</v>
       </c>
       <c r="G466" s="4" t="n">
-        <v>22727</v>
+        <v>53965</v>
       </c>
       <c r="H466" s="3" t="s">
         <v>13</v>
       </c>
       <c r="I466" s="3"/>
     </row>
-    <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B467" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D467" s="3" t="s">
-        <v>186</v>
+        <v>337</v>
       </c>
       <c r="E467" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F467" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G467" s="4" t="n">
+        <v>280600</v>
+      </c>
+      <c r="H467" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I467" s="3"/>
+    </row>
+    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A468" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B468" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C468" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D468" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="F467" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G467" s="4" t="n">
-        <v>32700</v>
-      </c>
-      <c r="H467" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I467" s="3"/>
-    </row>
-    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A468" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B468" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C468" s="3"/>
-      <c r="D468" s="3"/>
       <c r="E468" s="3" t="s">
-        <v>34</v>
+        <v>339</v>
       </c>
       <c r="F468" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G468" s="4" t="n">
-        <v>53965</v>
+        <v>892735</v>
       </c>
       <c r="H468" s="3" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="I468" s="3"/>
     </row>
-    <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="3" t="s">
         <v>42</v>
       </c>
@@ -13443,26 +13441,26 @@
         <v>65</v>
       </c>
       <c r="C469" s="3" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D469" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E469" s="3" t="s">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="F469" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G469" s="4" t="n">
-        <v>280600</v>
+        <v>149000</v>
       </c>
       <c r="H469" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I469" s="3"/>
     </row>
-    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="3" t="s">
         <v>42</v>
       </c>
@@ -13470,26 +13468,26 @@
         <v>65</v>
       </c>
       <c r="C470" s="3" t="s">
-        <v>168</v>
+        <v>94</v>
       </c>
       <c r="D470" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E470" s="3" t="s">
-        <v>341</v>
+        <v>301</v>
       </c>
       <c r="F470" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G470" s="4" t="n">
-        <v>892735</v>
+        <v>252000</v>
       </c>
       <c r="H470" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I470" s="3"/>
     </row>
-    <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="471" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="3" t="s">
         <v>42</v>
       </c>
@@ -13503,20 +13501,20 @@
         <v>342</v>
       </c>
       <c r="E471" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F471" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G471" s="4" t="n">
-        <v>149000</v>
+        <v>198000</v>
       </c>
       <c r="H471" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I471" s="3"/>
     </row>
-    <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="3" t="s">
         <v>42</v>
       </c>
@@ -13524,26 +13522,26 @@
         <v>65</v>
       </c>
       <c r="C472" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D472" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E472" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="E472" s="3" t="s">
-        <v>303</v>
-      </c>
       <c r="F472" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G472" s="4" t="n">
-        <v>252000</v>
+        <v>20000</v>
       </c>
       <c r="H472" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I472" s="3"/>
     </row>
-    <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="473" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="3" t="s">
         <v>42</v>
       </c>
@@ -13551,26 +13549,26 @@
         <v>65</v>
       </c>
       <c r="C473" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D473" s="3" t="s">
         <v>344</v>
       </c>
       <c r="E473" s="3" t="s">
-        <v>245</v>
+        <v>345</v>
       </c>
       <c r="F473" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G473" s="4" t="n">
-        <v>198000</v>
+        <v>65000</v>
       </c>
       <c r="H473" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I473" s="3"/>
     </row>
-    <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="3" t="s">
         <v>42</v>
       </c>
@@ -13578,26 +13576,26 @@
         <v>65</v>
       </c>
       <c r="C474" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D474" s="3" t="s">
-        <v>169</v>
+        <v>344</v>
       </c>
       <c r="E474" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F474" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G474" s="4" t="n">
-        <v>20000</v>
+        <v>267128</v>
       </c>
       <c r="H474" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I474" s="3"/>
     </row>
-    <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="475" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="3" t="s">
         <v>42</v>
       </c>
@@ -13608,7 +13606,7 @@
         <v>69</v>
       </c>
       <c r="D475" s="3" t="s">
-        <v>346</v>
+        <v>162</v>
       </c>
       <c r="E475" s="3" t="s">
         <v>347</v>
@@ -13617,114 +13615,114 @@
         <v>12</v>
       </c>
       <c r="G475" s="4" t="n">
-        <v>65000</v>
+        <v>30000</v>
       </c>
       <c r="H475" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I475" s="3"/>
     </row>
-    <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C476" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D476" s="3" t="s">
-        <v>346</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C476" s="3"/>
+      <c r="D476" s="3"/>
       <c r="E476" s="3" t="s">
-        <v>348</v>
+        <v>248</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G476" s="4" t="n">
-        <v>267128</v>
+        <v>22727</v>
       </c>
       <c r="H476" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I476" s="3"/>
     </row>
-    <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C477" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D477" s="3" t="s">
-        <v>164</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C477" s="3"/>
+      <c r="D477" s="3"/>
       <c r="E477" s="3" t="s">
-        <v>349</v>
+        <v>247</v>
       </c>
       <c r="F477" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G477" s="4" t="n">
-        <v>30000</v>
+        <v>4338</v>
       </c>
       <c r="H477" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I477" s="3"/>
     </row>
-    <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="478" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C478" s="3"/>
-      <c r="D478" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C478" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D478" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="E478" s="3" t="s">
-        <v>250</v>
+        <v>349</v>
       </c>
       <c r="F478" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G478" s="4" t="n">
-        <v>22727</v>
+        <v>15165</v>
       </c>
       <c r="H478" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I478" s="3"/>
     </row>
-    <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="479" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B479" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C479" s="3"/>
-      <c r="D479" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C479" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D479" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="E479" s="3" t="s">
-        <v>249</v>
+        <v>350</v>
       </c>
       <c r="F479" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G479" s="4" t="n">
-        <v>4338</v>
+        <v>513392</v>
       </c>
       <c r="H479" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I479" s="3"/>
     </row>
-    <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="3" t="s">
         <v>42</v>
       </c>
@@ -13732,80 +13730,80 @@
         <v>65</v>
       </c>
       <c r="C480" s="3" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D480" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E480" s="3" t="s">
-        <v>351</v>
+        <v>301</v>
       </c>
       <c r="F480" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G480" s="4" t="n">
-        <v>15165</v>
+        <v>320000</v>
       </c>
       <c r="H480" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I480" s="3"/>
     </row>
-    <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B481" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C481" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D481" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E481" s="3" t="s">
-        <v>352</v>
+        <v>243</v>
       </c>
       <c r="F481" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G481" s="4" t="n">
-        <v>513392</v>
+        <v>201000</v>
       </c>
       <c r="H481" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I481" s="3"/>
     </row>
-    <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B482" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C482" s="3" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D482" s="3" t="s">
-        <v>350</v>
+        <v>158</v>
       </c>
       <c r="E482" s="3" t="s">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="F482" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G482" s="4" t="n">
-        <v>320000</v>
+        <v>253000</v>
       </c>
       <c r="H482" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I482" s="3"/>
     </row>
-    <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="3" t="s">
         <v>32</v>
       </c>
@@ -13816,23 +13814,23 @@
         <v>66</v>
       </c>
       <c r="D483" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E483" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F483" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G483" s="4" t="n">
-        <v>201000</v>
+        <v>198000</v>
       </c>
       <c r="H483" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I483" s="3"/>
     </row>
-    <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="3" t="s">
         <v>32</v>
       </c>
@@ -13843,23 +13841,23 @@
         <v>66</v>
       </c>
       <c r="D484" s="3" t="s">
-        <v>160</v>
+        <v>353</v>
       </c>
       <c r="E484" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F484" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G484" s="4" t="n">
-        <v>253000</v>
+        <v>351000</v>
       </c>
       <c r="H484" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I484" s="3"/>
     </row>
-    <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="3" t="s">
         <v>32</v>
       </c>
@@ -13867,141 +13865,89 @@
         <v>65</v>
       </c>
       <c r="C485" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D485" s="3" t="s">
         <v>354</v>
       </c>
       <c r="E485" s="3" t="s">
-        <v>245</v>
+        <v>355</v>
       </c>
       <c r="F485" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G485" s="4" t="n">
-        <v>198000</v>
+        <v>328834</v>
       </c>
       <c r="H485" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I485" s="3"/>
     </row>
-    <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B486" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C486" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D486" s="3" t="s">
-        <v>355</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C486" s="3"/>
+      <c r="D486" s="3"/>
       <c r="E486" s="3" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="F486" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G486" s="4" t="n">
-        <v>351000</v>
+        <v>22727</v>
       </c>
       <c r="H486" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I486" s="3"/>
     </row>
-    <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C487" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D487" s="3" t="s">
-        <v>356</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C487" s="3"/>
+      <c r="D487" s="3"/>
       <c r="E487" s="3" t="s">
-        <v>357</v>
+        <v>247</v>
       </c>
       <c r="F487" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G487" s="4" t="n">
-        <v>328834</v>
+        <v>4238</v>
       </c>
       <c r="H487" s="3" t="s">
         <v>93</v>
       </c>
       <c r="I487" s="3"/>
     </row>
-    <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A488" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B488" s="3" t="s">
-        <v>10</v>
-      </c>
+    <row r="488" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A488" s="3"/>
+      <c r="B488" s="3"/>
       <c r="C488" s="3"/>
       <c r="D488" s="3"/>
       <c r="E488" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F488" s="3" t="s">
-        <v>18</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="F488" s="3"/>
       <c r="G488" s="4" t="n">
-        <v>22727</v>
-      </c>
-      <c r="H488" s="3" t="s">
-        <v>93</v>
-      </c>
+        <f aca="false">SUM(G2:G487)</f>
+        <v>172338183</v>
+      </c>
+      <c r="H488" s="3"/>
       <c r="I488" s="3"/>
     </row>
-    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A489" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B489" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C489" s="3"/>
-      <c r="D489" s="3"/>
-      <c r="E489" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F489" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G489" s="4" t="n">
-        <v>4238</v>
-      </c>
-      <c r="H489" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="I489" s="3"/>
-    </row>
-    <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A490" s="3"/>
-      <c r="B490" s="3"/>
-      <c r="C490" s="3"/>
-      <c r="D490" s="3"/>
-      <c r="E490" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="F490" s="3"/>
-      <c r="G490" s="4" t="n">
-        <f aca="false">SUM(G2:G489)</f>
-        <v>172838183</v>
-      </c>
-      <c r="H490" s="3"/>
-      <c r="I490" s="3"/>
-    </row>
+    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="490" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -14026,7 +13972,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14034,32 +13980,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14067,32 +14013,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14100,27 +14046,27 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14128,22 +14074,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14151,17 +14097,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -14189,7 +14135,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14239,143 +14185,143 @@
         <v>60</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-01",Gastos!$F$2:$F$489,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$F$2:$F$487,"Fijo")</f>
         <v>3247828</v>
       </c>
       <c r="C4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-02",Gastos!$F$2:$F$489,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$F$2:$F$487,"Fijo")</f>
         <v>5318465</v>
       </c>
       <c r="D4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-03",Gastos!$F$2:$F$489,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$F$2:$F$487,"Fijo")</f>
         <v>5936170</v>
       </c>
       <c r="E4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-04",Gastos!$F$2:$F$489,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$F$2:$F$487,"Fijo")</f>
         <v>5876788</v>
       </c>
       <c r="F4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-05",Gastos!$F$2:$F$489,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$F$2:$F$487,"Fijo")</f>
         <v>6035363</v>
       </c>
       <c r="G4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-06",Gastos!$F$2:$F$489,"Fijo")</f>
-        <v>6199233</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$F$2:$F$487,"Fijo")</f>
+        <v>5949233</v>
       </c>
       <c r="H4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-07",Gastos!$F$2:$F$489,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$F$2:$F$487,"Fijo")</f>
         <v>6977171</v>
       </c>
       <c r="I4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-08",Gastos!$F$2:$F$489,"Fijo")</f>
-        <v>9047758</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$F$2:$F$487,"Fijo")</f>
+        <v>8797758</v>
       </c>
       <c r="J4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-09",Gastos!$F$2:$F$489,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$F$2:$F$487,"Fijo")</f>
         <v>6459977</v>
       </c>
       <c r="K4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-10",Gastos!$F$2:$F$489,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$F$2:$F$487,"Fijo")</f>
         <v>5665877</v>
       </c>
       <c r="L4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-11",Gastos!$F$2:$F$489,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$F$2:$F$487,"Fijo")</f>
         <v>5665877</v>
       </c>
       <c r="M4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-12",Gastos!$F$2:$F$489,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$F$2:$F$487,"Fijo")</f>
         <v>3320877</v>
       </c>
       <c r="N4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-01",Gastos!$F$2:$F$489,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$F$2:$F$487,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="O4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-02",Gastos!$F$2:$F$489,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$F$2:$F$487,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="P4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-03",Gastos!$F$2:$F$489,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$F$2:$F$487,"Fijo")</f>
         <v>0</v>
       </c>
       <c r="Q4" s="10" t="n">
         <f aca="false">SUM(B4:P4)</f>
-        <v>70763248</v>
+        <v>70263248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-01",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$F$2:$F$487,"Variable")</f>
         <v>6304755</v>
       </c>
       <c r="C5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-02",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$F$2:$F$487,"Variable")</f>
         <v>9626002</v>
       </c>
       <c r="D5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-03",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$F$2:$F$487,"Variable")</f>
         <v>8177007</v>
       </c>
       <c r="E5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-04",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$F$2:$F$487,"Variable")</f>
         <v>9970945</v>
       </c>
       <c r="F5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-05",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$F$2:$F$487,"Variable")</f>
         <v>10299475</v>
       </c>
       <c r="G5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-06",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$F$2:$F$487,"Variable")</f>
         <v>30893365</v>
       </c>
       <c r="H5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-07",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$F$2:$F$487,"Variable")</f>
         <v>6757280</v>
       </c>
       <c r="I5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-08",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$F$2:$F$487,"Variable")</f>
         <v>15886106</v>
       </c>
       <c r="J5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-09",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$F$2:$F$487,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="K5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-10",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$F$2:$F$487,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="L5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-11",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$F$2:$F$487,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="M5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-12",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$F$2:$F$487,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="N5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-01",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$F$2:$F$487,"Variable")</f>
         <v>0</v>
       </c>
       <c r="O5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-02",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$F$2:$F$487,"Variable")</f>
         <v>0</v>
       </c>
       <c r="P5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-03",Gastos!$F$2:$F$489,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$F$2:$F$487,"Variable")</f>
         <v>0</v>
       </c>
       <c r="Q5" s="10" t="n">
@@ -14385,7 +14331,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">B4+B5</f>
@@ -14409,7 +14355,7 @@
       </c>
       <c r="G6" s="9" t="n">
         <f aca="false">G4+G5</f>
-        <v>37092598</v>
+        <v>36842598</v>
       </c>
       <c r="H6" s="9" t="n">
         <f aca="false">H4+H5</f>
@@ -14417,7 +14363,7 @@
       </c>
       <c r="I6" s="9" t="n">
         <f aca="false">I4+I5</f>
-        <v>24933864</v>
+        <v>24683864</v>
       </c>
       <c r="J6" s="9" t="n">
         <f aca="false">J4+J5</f>
@@ -14449,12 +14395,12 @@
       </c>
       <c r="Q6" s="10" t="n">
         <f aca="false">Q4+Q5</f>
-        <v>172838183</v>
+        <v>172338183</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14462,68 +14408,68 @@
         <v>10</v>
       </c>
       <c r="B9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-01",Gastos!$B$2:$B$489,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Servicios")</f>
         <v>286542</v>
       </c>
       <c r="C9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-02",Gastos!$B$2:$B$489,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Servicios")</f>
         <v>883152</v>
       </c>
       <c r="D9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-03",Gastos!$B$2:$B$489,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Servicios")</f>
         <v>1048593</v>
       </c>
       <c r="E9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-04",Gastos!$B$2:$B$489,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Servicios")</f>
         <v>783677</v>
       </c>
       <c r="F9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-05",Gastos!$B$2:$B$489,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Servicios")</f>
         <v>826352</v>
       </c>
       <c r="G9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-06",Gastos!$B$2:$B$489,"Servicios")</f>
-        <v>874134</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Servicios")</f>
+        <v>624134</v>
       </c>
       <c r="H9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-07",Gastos!$B$2:$B$489,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Servicios")</f>
         <v>633304</v>
       </c>
       <c r="I9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-08",Gastos!$B$2:$B$489,"Servicios")</f>
-        <v>905440</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Servicios")</f>
+        <v>655440</v>
       </c>
       <c r="J9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-09",Gastos!$B$2:$B$489,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="K9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-10",Gastos!$B$2:$B$489,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="L9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-11",Gastos!$B$2:$B$489,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="M9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-12",Gastos!$B$2:$B$489,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="N9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-01",Gastos!$B$2:$B$489,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="O9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-02",Gastos!$B$2:$B$489,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-03",Gastos!$B$2:$B$489,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="Q9" s="9" t="n">
         <f aca="false">SUM(B9:P9)</f>
-        <v>7881194</v>
+        <v>7381194</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14531,63 +14477,63 @@
         <v>16</v>
       </c>
       <c r="B10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-01",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-02",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-03",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="E10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-04",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="F10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-05",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="G10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-06",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>262000</v>
       </c>
       <c r="H10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-07",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="I10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-08",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="J10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-09",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="K10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-10",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="L10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-11",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="M10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-12",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="N10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-01",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="O10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-02",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="P10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-03",Gastos!$B$2:$B$489,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="9" t="n">
@@ -14600,68 +14546,68 @@
         <v>19</v>
       </c>
       <c r="B11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-01",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Educación")</f>
         <v>0</v>
       </c>
       <c r="C11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-02",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Educación")</f>
         <v>2345000</v>
       </c>
       <c r="D11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-03",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="E11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-04",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="F11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-05",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="G11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-06",Gastos!$B$2:$B$489,"Educación")</f>
-        <v>8109610</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Educación")</f>
+        <v>3385000</v>
       </c>
       <c r="H11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-07",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="I11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-08",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="J11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-09",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="K11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-10",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="L11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-11",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="M11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-12",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Educación")</f>
         <v>1040000</v>
       </c>
       <c r="N11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-01",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Educación")</f>
         <v>0</v>
       </c>
       <c r="O11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-02",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Educación")</f>
         <v>0</v>
       </c>
       <c r="P11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-03",Gastos!$B$2:$B$489,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Educación")</f>
         <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
         <f aca="false">SUM(B11:P11)</f>
-        <v>38574610</v>
+        <v>33850000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14669,63 +14615,63 @@
         <v>21</v>
       </c>
       <c r="B12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-01",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="C12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-02",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="D12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-03",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Salud")</f>
         <v>1548449</v>
       </c>
       <c r="E12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-04",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="F12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-05",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Salud")</f>
         <v>1306200</v>
       </c>
       <c r="G12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-06",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="H12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-07",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="I12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-08",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="J12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-09",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="K12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-10",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="L12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-11",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="M12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-12",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="N12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-01",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Salud")</f>
         <v>0</v>
       </c>
       <c r="O12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-02",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Salud")</f>
         <v>0</v>
       </c>
       <c r="P12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-03",Gastos!$B$2:$B$489,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Salud")</f>
         <v>0</v>
       </c>
       <c r="Q12" s="9" t="n">
@@ -14738,63 +14684,63 @@
         <v>27</v>
       </c>
       <c r="B13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-01",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>1057700</v>
       </c>
       <c r="C13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-02",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>710897</v>
       </c>
       <c r="D13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-03",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>708661</v>
       </c>
       <c r="E13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-04",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>730525</v>
       </c>
       <c r="F13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-05",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>728410</v>
       </c>
       <c r="G13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-06",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>1086789</v>
       </c>
       <c r="H13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-07",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>814937</v>
       </c>
       <c r="I13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-08",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>765835</v>
       </c>
       <c r="J13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-09",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="K13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-10",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="L13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-11",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="M13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-12",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="N13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-01",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="O13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-02",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="P13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-03",Gastos!$B$2:$B$489,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="Q13" s="9" t="n">
@@ -14807,63 +14753,63 @@
         <v>29</v>
       </c>
       <c r="B14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-01",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>456901</v>
       </c>
       <c r="C14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-02",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>335538</v>
       </c>
       <c r="D14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-03",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>450311</v>
       </c>
       <c r="E14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-04",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>390929</v>
       </c>
       <c r="F14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-05",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>549504</v>
       </c>
       <c r="G14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-06",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>461374</v>
       </c>
       <c r="H14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-07",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>620062</v>
       </c>
       <c r="I14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-08",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>451349</v>
       </c>
       <c r="J14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-09",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="K14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-10",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="L14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-11",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="M14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-12",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="N14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-01",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="O14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-02",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="P14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-03",Gastos!$B$2:$B$489,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="Q14" s="9" t="n">
@@ -14876,63 +14822,63 @@
         <v>47</v>
       </c>
       <c r="B15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-01",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="C15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-02",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="D15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-03",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="E15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-04",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>470932</v>
       </c>
       <c r="F15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-05",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="G15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-06",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="H15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-07",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>1507182</v>
       </c>
       <c r="I15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-08",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>3131099</v>
       </c>
       <c r="J15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-09",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>1300032</v>
       </c>
       <c r="K15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-10",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="L15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-11",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="M15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-12",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="N15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-01",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="O15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-02",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="P15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-03",Gastos!$B$2:$B$489,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="Q15" s="9" t="n">
@@ -14945,63 +14891,63 @@
         <v>65</v>
       </c>
       <c r="B16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-01",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>5861720</v>
       </c>
       <c r="C16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-02",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>8780160</v>
       </c>
       <c r="D16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-03",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>5832711</v>
       </c>
       <c r="E16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-04",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>6178045</v>
       </c>
       <c r="F16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-05",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>5382047</v>
       </c>
       <c r="G16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-06",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>5089768</v>
       </c>
       <c r="H16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-07",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>5387766</v>
       </c>
       <c r="I16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-08",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>14520831</v>
       </c>
       <c r="J16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-09",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="K16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-10",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-11",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="M16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-12",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="N16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-01",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="O16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-02",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="P16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-03",Gastos!$B$2:$B$489,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="Q16" s="9" t="n">
@@ -15014,63 +14960,63 @@
         <v>109</v>
       </c>
       <c r="B17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-01",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="C17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-02",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-03",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-04",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="F17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-05",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="G17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-06",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-07",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="I17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-08",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"IPS")</f>
         <v>388110</v>
       </c>
       <c r="J17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-09",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="K17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-10",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-11",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="M17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-12",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="N17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-01",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="O17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-02",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="P17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-03",Gastos!$B$2:$B$489,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"IPS")</f>
         <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
@@ -15080,58 +15026,58 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-01",Gastos!$B$2:$B$489,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="C18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-02",Gastos!$B$2:$B$489,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="D18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-03",Gastos!$B$2:$B$489,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="E18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-04",Gastos!$B$2:$B$489,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Viajes")</f>
         <v>2392425</v>
       </c>
       <c r="F18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-05",Gastos!$B$2:$B$489,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Viajes")</f>
         <v>3391393</v>
       </c>
       <c r="G18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-06",Gastos!$B$2:$B$489,"Viajes")</f>
-        <v>19446791</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Viajes")</f>
+        <v>24171401</v>
       </c>
       <c r="H18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-07",Gastos!$B$2:$B$489,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-08",Gastos!$B$2:$B$489,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-09",Gastos!$B$2:$B$489,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="K18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-10",Gastos!$B$2:$B$489,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-11",Gastos!$B$2:$B$489,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="M18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2026-12",Gastos!$B$2:$B$489,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="N18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$489,Gastos!$A$2:$A$489,"2027-01",Gastos!$B$2:$B$489,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Viajes")</f>
         <v>0</v>
       </c>
     </row>

--- a/Gastos_Mensuales.xlsx
+++ b/Gastos_Mensuales.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3038" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3115" uniqueCount="396">
   <si>
     <t xml:space="preserve">Mes</t>
   </si>
@@ -1090,6 +1090,27 @@
   </si>
   <si>
     <t xml:space="preserve">Petrobras Molas Lope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Almuerzo (plato ₲350.000 + propina ₲35.000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reintegro supermercado (20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utensilios de cocina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comida oficina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bebida fútbol (Powerade + Coca Zero)</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -1628,7 +1649,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I490"/>
+  <dimension ref="A1:I499"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -13931,23 +13952,318 @@
       <c r="I487" s="3"/>
     </row>
     <row r="488" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A488" s="3"/>
-      <c r="B488" s="3"/>
-      <c r="C488" s="3"/>
-      <c r="D488" s="3"/>
+      <c r="A488" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B488" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C488" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D488" s="3" t="s">
+        <v>134</v>
+      </c>
       <c r="E488" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="F488" s="3"/>
+      <c r="F488" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G488" s="4" t="n">
-        <f aca="false">SUM(G2:G487)</f>
-        <v>172338183</v>
-      </c>
-      <c r="H488" s="3"/>
+        <v>385000</v>
+      </c>
+      <c r="H488" s="3" t="s">
+        <v>13</v>
+      </c>
       <c r="I488" s="3"/>
     </row>
-    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="490" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A489" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B489" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C489" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D489" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E489" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F489" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G489" s="4" t="n">
+        <v>67000</v>
+      </c>
+      <c r="H489" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I489" s="3"/>
+    </row>
+    <row r="490" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A490" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B490" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C490" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D490" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E490" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F490" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G490" s="4" t="n">
+        <v>830000</v>
+      </c>
+      <c r="H490" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I490" s="3"/>
+    </row>
+    <row r="491" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A491" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B491" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C491" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D491" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E491" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="F491" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G491" s="4" t="n">
+        <v>-166000</v>
+      </c>
+      <c r="H491" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I491" s="3"/>
+    </row>
+    <row r="492" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A492" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B492" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C492" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D492" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E492" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="F492" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G492" s="4" t="n">
+        <v>210000</v>
+      </c>
+      <c r="H492" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I492" s="3"/>
+    </row>
+    <row r="493" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A493" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B493" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C493" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D493" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E493" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F493" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G493" s="4" t="n">
+        <v>308000</v>
+      </c>
+      <c r="H493" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I493" s="3"/>
+    </row>
+    <row r="494" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A494" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B494" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C494" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D494" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E494" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F494" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G494" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H494" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I494" s="3"/>
+    </row>
+    <row r="495" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A495" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B495" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C495" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D495" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E495" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="F495" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G495" s="4" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H495" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I495" s="3"/>
+    </row>
+    <row r="496" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A496" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B496" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C496" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D496" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E496" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F496" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G496" s="4" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H496" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I496" s="3"/>
+    </row>
+    <row r="497" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A497" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B497" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C497" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D497" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="E497" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F497" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G497" s="4" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H497" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I497" s="3"/>
+    </row>
+    <row r="498" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A498" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B498" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C498" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D498" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E498" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="F498" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G498" s="4" t="n">
+        <v>22000</v>
+      </c>
+      <c r="H498" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I498" s="3"/>
+    </row>
+    <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A499" s="3"/>
+      <c r="B499" s="3"/>
+      <c r="C499" s="3"/>
+      <c r="D499" s="3"/>
+      <c r="E499" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="F499" s="3"/>
+      <c r="G499" s="4" t="n">
+        <f aca="false">SUM(G2:G498)</f>
+        <v>174214183</v>
+      </c>
+      <c r="H499" s="3"/>
+      <c r="I499" s="3"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13972,7 +14288,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13980,32 +14296,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14013,32 +14329,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14046,27 +14362,27 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14074,22 +14390,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14097,17 +14413,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -14135,7 +14451,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14185,74 +14501,74 @@
         <v>60</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>3247828</v>
       </c>
       <c r="C4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>5318465</v>
       </c>
       <c r="D4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>5936170</v>
       </c>
       <c r="E4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>5876788</v>
       </c>
       <c r="F4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>6035363</v>
       </c>
       <c r="G4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>5949233</v>
       </c>
       <c r="H4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>6977171</v>
       </c>
       <c r="I4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>8797758</v>
       </c>
       <c r="J4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>6459977</v>
       </c>
       <c r="K4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>5665877</v>
       </c>
       <c r="L4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>5665877</v>
       </c>
       <c r="M4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>3320877</v>
       </c>
       <c r="N4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="O4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="P4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$F$2:$F$487,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$F$2:$F$498,"Fijo")</f>
         <v>0</v>
       </c>
       <c r="Q4" s="10" t="n">
@@ -14262,76 +14578,76 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$F$2:$F$498,"Variable")</f>
         <v>6304755</v>
       </c>
       <c r="C5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$F$2:$F$498,"Variable")</f>
         <v>9626002</v>
       </c>
       <c r="D5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$F$2:$F$498,"Variable")</f>
         <v>8177007</v>
       </c>
       <c r="E5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$F$2:$F$498,"Variable")</f>
         <v>9970945</v>
       </c>
       <c r="F5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$F$2:$F$498,"Variable")</f>
         <v>10299475</v>
       </c>
       <c r="G5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$F$2:$F$498,"Variable")</f>
         <v>30893365</v>
       </c>
       <c r="H5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$F$2:$F$498,"Variable")</f>
         <v>6757280</v>
       </c>
       <c r="I5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$F$2:$F$487,"Variable")</f>
-        <v>15886106</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$F$2:$F$498,"Variable")</f>
+        <v>17762106</v>
       </c>
       <c r="J5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$F$2:$F$498,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="K5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$F$2:$F$498,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="L5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$F$2:$F$498,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="M5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$F$2:$F$498,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="N5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$F$2:$F$498,"Variable")</f>
         <v>0</v>
       </c>
       <c r="O5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$F$2:$F$498,"Variable")</f>
         <v>0</v>
       </c>
       <c r="P5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$F$2:$F$487,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$F$2:$F$498,"Variable")</f>
         <v>0</v>
       </c>
       <c r="Q5" s="10" t="n">
         <f aca="false">SUM(B5:P5)</f>
-        <v>102074935</v>
+        <v>103950935</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">B4+B5</f>
@@ -14363,7 +14679,7 @@
       </c>
       <c r="I6" s="9" t="n">
         <f aca="false">I4+I5</f>
-        <v>24683864</v>
+        <v>26559864</v>
       </c>
       <c r="J6" s="9" t="n">
         <f aca="false">J4+J5</f>
@@ -14395,12 +14711,12 @@
       </c>
       <c r="Q6" s="10" t="n">
         <f aca="false">Q4+Q5</f>
-        <v>172338183</v>
+        <v>174214183</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14408,63 +14724,63 @@
         <v>10</v>
       </c>
       <c r="B9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>286542</v>
       </c>
       <c r="C9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>883152</v>
       </c>
       <c r="D9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>1048593</v>
       </c>
       <c r="E9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>783677</v>
       </c>
       <c r="F9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>826352</v>
       </c>
       <c r="G9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>624134</v>
       </c>
       <c r="H9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>633304</v>
       </c>
       <c r="I9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>655440</v>
       </c>
       <c r="J9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="K9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="L9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="M9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="N9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="O9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="Q9" s="9" t="n">
@@ -14477,63 +14793,63 @@
         <v>16</v>
       </c>
       <c r="B10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="E10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="F10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="G10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>262000</v>
       </c>
       <c r="H10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="I10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="J10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="K10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="L10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="M10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="N10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="O10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="P10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="9" t="n">
@@ -14546,63 +14862,63 @@
         <v>19</v>
       </c>
       <c r="B11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Educación")</f>
         <v>0</v>
       </c>
       <c r="C11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Educación")</f>
         <v>2345000</v>
       </c>
       <c r="D11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="E11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="F11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="G11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="H11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="I11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="J11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="K11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="L11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="M11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Educación")</f>
         <v>1040000</v>
       </c>
       <c r="N11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Educación")</f>
         <v>0</v>
       </c>
       <c r="O11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Educación")</f>
         <v>0</v>
       </c>
       <c r="P11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Educación")</f>
         <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
@@ -14615,63 +14931,63 @@
         <v>21</v>
       </c>
       <c r="B12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="C12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="D12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Salud")</f>
         <v>1548449</v>
       </c>
       <c r="E12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="F12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Salud")</f>
         <v>1306200</v>
       </c>
       <c r="G12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="H12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="I12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="J12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="K12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="L12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="M12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="N12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Salud")</f>
         <v>0</v>
       </c>
       <c r="O12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Salud")</f>
         <v>0</v>
       </c>
       <c r="P12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Salud")</f>
         <v>0</v>
       </c>
       <c r="Q12" s="9" t="n">
@@ -14684,63 +15000,63 @@
         <v>27</v>
       </c>
       <c r="B13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>1057700</v>
       </c>
       <c r="C13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>710897</v>
       </c>
       <c r="D13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>708661</v>
       </c>
       <c r="E13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>730525</v>
       </c>
       <c r="F13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>728410</v>
       </c>
       <c r="G13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>1086789</v>
       </c>
       <c r="H13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>814937</v>
       </c>
       <c r="I13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>765835</v>
       </c>
       <c r="J13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="K13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="L13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="M13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="N13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="O13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="P13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="Q13" s="9" t="n">
@@ -14753,63 +15069,63 @@
         <v>29</v>
       </c>
       <c r="B14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>456901</v>
       </c>
       <c r="C14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>335538</v>
       </c>
       <c r="D14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>450311</v>
       </c>
       <c r="E14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>390929</v>
       </c>
       <c r="F14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>549504</v>
       </c>
       <c r="G14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>461374</v>
       </c>
       <c r="H14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>620062</v>
       </c>
       <c r="I14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>451349</v>
       </c>
       <c r="J14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="K14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="L14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="M14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="N14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="O14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="P14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="Q14" s="9" t="n">
@@ -14822,63 +15138,63 @@
         <v>47</v>
       </c>
       <c r="B15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="C15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="D15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="E15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>470932</v>
       </c>
       <c r="F15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="G15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="H15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>1507182</v>
       </c>
       <c r="I15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>3131099</v>
       </c>
       <c r="J15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>1300032</v>
       </c>
       <c r="K15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="L15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="M15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="N15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="O15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="P15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="Q15" s="9" t="n">
@@ -14891,68 +15207,68 @@
         <v>65</v>
       </c>
       <c r="B16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>5861720</v>
       </c>
       <c r="C16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>8780160</v>
       </c>
       <c r="D16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>5832711</v>
       </c>
       <c r="E16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>6178045</v>
       </c>
       <c r="F16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>5382047</v>
       </c>
       <c r="G16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>5089768</v>
       </c>
       <c r="H16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>5387766</v>
       </c>
       <c r="I16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Día a día")</f>
-        <v>14520831</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Día a día")</f>
+        <v>16396831</v>
       </c>
       <c r="J16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="K16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="M16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="N16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="O16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="P16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="Q16" s="9" t="n">
         <f aca="false">SUM(B16:P16)</f>
-        <v>57033048</v>
+        <v>58909048</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14960,63 +15276,63 @@
         <v>109</v>
       </c>
       <c r="B17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="C17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="F17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="G17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="I17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"IPS")</f>
         <v>388110</v>
       </c>
       <c r="J17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="K17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="M17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="N17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="O17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-02",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="P17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-03",Gastos!$B$2:$B$487,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"IPS")</f>
         <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
@@ -15029,55 +15345,55 @@
         <v>160</v>
       </c>
       <c r="B18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-01",Gastos!$B$2:$B$487,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="C18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-02",Gastos!$B$2:$B$487,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="D18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-03",Gastos!$B$2:$B$487,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="E18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-04",Gastos!$B$2:$B$487,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Viajes")</f>
         <v>2392425</v>
       </c>
       <c r="F18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-05",Gastos!$B$2:$B$487,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Viajes")</f>
         <v>3391393</v>
       </c>
       <c r="G18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-06",Gastos!$B$2:$B$487,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Viajes")</f>
         <v>24171401</v>
       </c>
       <c r="H18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-07",Gastos!$B$2:$B$487,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-08",Gastos!$B$2:$B$487,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-09",Gastos!$B$2:$B$487,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="K18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-10",Gastos!$B$2:$B$487,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-11",Gastos!$B$2:$B$487,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="M18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2026-12",Gastos!$B$2:$B$487,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="N18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$487,Gastos!$A$2:$A$487,"2027-01",Gastos!$B$2:$B$487,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Viajes")</f>
         <v>0</v>
       </c>
     </row>

--- a/Gastos_Mensuales.xlsx
+++ b/Gastos_Mensuales.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3115" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="400">
   <si>
     <t xml:space="preserve">Mes</t>
   </si>
@@ -1111,6 +1111,18 @@
   </si>
   <si>
     <t xml:space="preserve">Bebida fútbol (Powerade + Coca Zero)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psicóloga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reintegro nafta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remeras (2)</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -1649,7 +1661,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I499"/>
+  <dimension ref="A1:I510"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -14248,21 +14260,306 @@
       </c>
       <c r="I498" s="3"/>
     </row>
-    <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A499" s="3"/>
-      <c r="B499" s="3"/>
-      <c r="C499" s="3"/>
-      <c r="D499" s="3"/>
+    <row r="499" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A499" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B499" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C499" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D499" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="E499" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F499" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G499" s="4" t="n">
+        <v>197000</v>
+      </c>
+      <c r="H499" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I499" s="3"/>
+    </row>
+    <row r="500" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A500" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B500" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C500" s="3"/>
+      <c r="D500" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E500" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="F500" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G500" s="4" t="n">
+        <v>248714</v>
+      </c>
+      <c r="H500" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I500" s="3"/>
+    </row>
+    <row r="501" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A501" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B501" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C501" s="3"/>
+      <c r="D501" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E501" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="F499" s="3"/>
-      <c r="G499" s="4" t="n">
-        <f aca="false">SUM(G2:G498)</f>
-        <v>174214183</v>
-      </c>
-      <c r="H499" s="3"/>
-      <c r="I499" s="3"/>
+      <c r="F501" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G501" s="4" t="n">
+        <v>330000</v>
+      </c>
+      <c r="H501" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I501" s="3"/>
+    </row>
+    <row r="502" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A502" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B502" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C502" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D502" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E502" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F502" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G502" s="4" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H502" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I502" s="3"/>
+    </row>
+    <row r="503" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A503" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B503" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C503" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D503" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E503" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F503" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G503" s="4" t="n">
+        <v>319235</v>
+      </c>
+      <c r="H503" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I503" s="3"/>
+    </row>
+    <row r="504" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A504" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B504" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C504" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D504" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E504" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="F504" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G504" s="4" t="n">
+        <v>-18750</v>
+      </c>
+      <c r="H504" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I504" s="3"/>
+    </row>
+    <row r="505" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A505" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B505" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C505" s="3"/>
+      <c r="D505" s="3"/>
+      <c r="E505" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F505" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G505" s="4" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H505" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I505" s="3"/>
+    </row>
+    <row r="506" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A506" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B506" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C506" s="3"/>
+      <c r="D506" s="3"/>
+      <c r="E506" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F506" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G506" s="4" t="n">
+        <v>4675</v>
+      </c>
+      <c r="H506" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I506" s="3"/>
+    </row>
+    <row r="507" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A507" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B507" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C507" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D507" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E507" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="F507" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G507" s="4" t="n">
+        <v>159000</v>
+      </c>
+      <c r="H507" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I507" s="3"/>
+    </row>
+    <row r="508" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A508" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B508" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C508" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D508" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E508" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F508" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G508" s="4" t="n">
+        <v>145600</v>
+      </c>
+      <c r="H508" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I508" s="3"/>
+    </row>
+    <row r="509" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A509" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B509" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C509" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D509" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E509" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="F509" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G509" s="4" t="n">
+        <v>48500</v>
+      </c>
+      <c r="H509" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I509" s="3"/>
+    </row>
+    <row r="510" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A510" s="3"/>
+      <c r="B510" s="3"/>
+      <c r="C510" s="3"/>
+      <c r="D510" s="3"/>
+      <c r="E510" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="F510" s="3"/>
+      <c r="G510" s="4" t="n">
+        <f aca="false">SUM(G2:G509)</f>
+        <v>175693157</v>
+      </c>
+      <c r="H510" s="3"/>
+      <c r="I510" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -14288,7 +14585,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14296,32 +14593,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14329,32 +14626,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14362,27 +14659,27 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14390,22 +14687,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14413,17 +14710,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -14451,7 +14748,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14501,153 +14798,153 @@
         <v>60</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>3247828</v>
       </c>
       <c r="C4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>5318465</v>
       </c>
       <c r="D4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>5936170</v>
       </c>
       <c r="E4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>5876788</v>
       </c>
       <c r="F4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>6035363</v>
       </c>
       <c r="G4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>5949233</v>
       </c>
       <c r="H4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>6977171</v>
       </c>
       <c r="I4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$F$2:$F$498,"Fijo")</f>
-        <v>8797758</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$F$2:$F$509,"Fijo")</f>
+        <v>8822758</v>
       </c>
       <c r="J4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>6459977</v>
       </c>
       <c r="K4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>5665877</v>
       </c>
       <c r="L4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>5665877</v>
       </c>
       <c r="M4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>3320877</v>
       </c>
       <c r="N4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="O4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="P4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$F$2:$F$498,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$F$2:$F$509,"Fijo")</f>
         <v>0</v>
       </c>
       <c r="Q4" s="10" t="n">
         <f aca="false">SUM(B4:P4)</f>
-        <v>70263248</v>
+        <v>70288248</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$F$2:$F$509,"Variable")</f>
         <v>6304755</v>
       </c>
       <c r="C5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$F$2:$F$509,"Variable")</f>
         <v>9626002</v>
       </c>
       <c r="D5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$F$2:$F$509,"Variable")</f>
         <v>8177007</v>
       </c>
       <c r="E5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$F$2:$F$509,"Variable")</f>
         <v>9970945</v>
       </c>
       <c r="F5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$F$2:$F$509,"Variable")</f>
         <v>10299475</v>
       </c>
       <c r="G5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$F$2:$F$509,"Variable")</f>
         <v>30893365</v>
       </c>
       <c r="H5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$F$2:$F$509,"Variable")</f>
         <v>6757280</v>
       </c>
       <c r="I5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$F$2:$F$498,"Variable")</f>
-        <v>17762106</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$F$2:$F$509,"Variable")</f>
+        <v>19216080</v>
       </c>
       <c r="J5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$F$2:$F$509,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="K5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$F$2:$F$509,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="L5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$F$2:$F$509,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="M5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$F$2:$F$509,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="N5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$F$2:$F$509,"Variable")</f>
         <v>0</v>
       </c>
       <c r="O5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$F$2:$F$509,"Variable")</f>
         <v>0</v>
       </c>
       <c r="P5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$F$2:$F$498,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$F$2:$F$509,"Variable")</f>
         <v>0</v>
       </c>
       <c r="Q5" s="10" t="n">
         <f aca="false">SUM(B5:P5)</f>
-        <v>103950935</v>
+        <v>105404909</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">B4+B5</f>
@@ -14679,7 +14976,7 @@
       </c>
       <c r="I6" s="9" t="n">
         <f aca="false">I4+I5</f>
-        <v>26559864</v>
+        <v>28038838</v>
       </c>
       <c r="J6" s="9" t="n">
         <f aca="false">J4+J5</f>
@@ -14711,12 +15008,12 @@
       </c>
       <c r="Q6" s="10" t="n">
         <f aca="false">Q4+Q5</f>
-        <v>174214183</v>
+        <v>175693157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14724,68 +15021,68 @@
         <v>10</v>
       </c>
       <c r="B9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>286542</v>
       </c>
       <c r="C9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>883152</v>
       </c>
       <c r="D9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>1048593</v>
       </c>
       <c r="E9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>783677</v>
       </c>
       <c r="F9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>826352</v>
       </c>
       <c r="G9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>624134</v>
       </c>
       <c r="H9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>633304</v>
       </c>
       <c r="I9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Servicios")</f>
-        <v>655440</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Servicios")</f>
+        <v>680440</v>
       </c>
       <c r="J9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="K9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="L9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="M9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="N9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="O9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="Q9" s="9" t="n">
         <f aca="false">SUM(B9:P9)</f>
-        <v>7381194</v>
+        <v>7406194</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14793,63 +15090,63 @@
         <v>16</v>
       </c>
       <c r="B10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="E10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="F10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="G10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>262000</v>
       </c>
       <c r="H10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="I10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="J10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="K10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="L10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="M10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="N10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="O10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="P10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="9" t="n">
@@ -14862,63 +15159,63 @@
         <v>19</v>
       </c>
       <c r="B11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Educación")</f>
         <v>0</v>
       </c>
       <c r="C11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Educación")</f>
         <v>2345000</v>
       </c>
       <c r="D11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="E11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="F11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="G11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="H11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="I11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="J11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="K11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="L11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="M11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Educación")</f>
         <v>1040000</v>
       </c>
       <c r="N11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Educación")</f>
         <v>0</v>
       </c>
       <c r="O11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Educación")</f>
         <v>0</v>
       </c>
       <c r="P11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Educación")</f>
         <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
@@ -14931,68 +15228,68 @@
         <v>21</v>
       </c>
       <c r="B12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="C12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="D12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Salud")</f>
         <v>1548449</v>
       </c>
       <c r="E12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="F12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Salud")</f>
         <v>1306200</v>
       </c>
       <c r="G12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="H12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="I12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Salud")</f>
+        <v>1834914</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Salud")</f>
         <v>1256200</v>
       </c>
-      <c r="J12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Salud")</f>
+      <c r="K12" s="9" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Salud")</f>
         <v>1256200</v>
       </c>
-      <c r="K12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Salud")</f>
+      <c r="L12" s="9" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Salud")</f>
         <v>1256200</v>
       </c>
-      <c r="L12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Salud")</f>
+      <c r="M12" s="9" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Salud")</f>
         <v>1256200</v>
       </c>
-      <c r="M12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Salud")</f>
-        <v>1256200</v>
-      </c>
       <c r="N12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Salud")</f>
         <v>0</v>
       </c>
       <c r="O12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Salud")</f>
         <v>0</v>
       </c>
       <c r="P12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Salud")</f>
         <v>0</v>
       </c>
       <c r="Q12" s="9" t="n">
         <f aca="false">SUM(B12:P12)</f>
-        <v>15416649</v>
+        <v>15995363</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15000,68 +15297,68 @@
         <v>27</v>
       </c>
       <c r="B13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>1057700</v>
       </c>
       <c r="C13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>710897</v>
       </c>
       <c r="D13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>708661</v>
       </c>
       <c r="E13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>730525</v>
       </c>
       <c r="F13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>728410</v>
       </c>
       <c r="G13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>1086789</v>
       </c>
       <c r="H13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>814937</v>
       </c>
       <c r="I13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Seguros")</f>
-        <v>765835</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Seguros")</f>
+        <v>770510</v>
       </c>
       <c r="J13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="K13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="L13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="M13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="N13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="O13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="P13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="Q13" s="9" t="n">
         <f aca="false">SUM(B13:P13)</f>
-        <v>9347754</v>
+        <v>9352429</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15069,63 +15366,63 @@
         <v>29</v>
       </c>
       <c r="B14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>456901</v>
       </c>
       <c r="C14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>335538</v>
       </c>
       <c r="D14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>450311</v>
       </c>
       <c r="E14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>390929</v>
       </c>
       <c r="F14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>549504</v>
       </c>
       <c r="G14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>461374</v>
       </c>
       <c r="H14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>620062</v>
       </c>
       <c r="I14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>451349</v>
       </c>
       <c r="J14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="K14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="L14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="M14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="N14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="O14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="P14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="Q14" s="9" t="n">
@@ -15138,63 +15435,63 @@
         <v>47</v>
       </c>
       <c r="B15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="C15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="D15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="E15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>470932</v>
       </c>
       <c r="F15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="G15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="H15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>1507182</v>
       </c>
       <c r="I15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>3131099</v>
       </c>
       <c r="J15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>1300032</v>
       </c>
       <c r="K15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="L15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="M15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="N15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="O15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="P15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="Q15" s="9" t="n">
@@ -15207,68 +15504,68 @@
         <v>65</v>
       </c>
       <c r="B16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>5861720</v>
       </c>
       <c r="C16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>8780160</v>
       </c>
       <c r="D16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>5832711</v>
       </c>
       <c r="E16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>6178045</v>
       </c>
       <c r="F16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>5382047</v>
       </c>
       <c r="G16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>5089768</v>
       </c>
       <c r="H16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>5387766</v>
       </c>
       <c r="I16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Día a día")</f>
-        <v>16396831</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Día a día")</f>
+        <v>17267416</v>
       </c>
       <c r="J16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="K16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="M16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="N16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="O16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="P16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="Q16" s="9" t="n">
         <f aca="false">SUM(B16:P16)</f>
-        <v>58909048</v>
+        <v>59779633</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15276,63 +15573,63 @@
         <v>109</v>
       </c>
       <c r="B17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="C17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="F17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="G17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="I17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"IPS")</f>
         <v>388110</v>
       </c>
       <c r="J17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="K17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="M17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="N17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="O17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-02",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="P17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-03",Gastos!$B$2:$B$498,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"IPS")</f>
         <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
@@ -15345,55 +15642,55 @@
         <v>160</v>
       </c>
       <c r="B18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-01",Gastos!$B$2:$B$498,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="C18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-02",Gastos!$B$2:$B$498,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="D18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-03",Gastos!$B$2:$B$498,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="E18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-04",Gastos!$B$2:$B$498,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Viajes")</f>
         <v>2392425</v>
       </c>
       <c r="F18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-05",Gastos!$B$2:$B$498,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Viajes")</f>
         <v>3391393</v>
       </c>
       <c r="G18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-06",Gastos!$B$2:$B$498,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Viajes")</f>
         <v>24171401</v>
       </c>
       <c r="H18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-07",Gastos!$B$2:$B$498,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-08",Gastos!$B$2:$B$498,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-09",Gastos!$B$2:$B$498,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="K18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-10",Gastos!$B$2:$B$498,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-11",Gastos!$B$2:$B$498,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="M18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2026-12",Gastos!$B$2:$B$498,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="N18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$498,Gastos!$A$2:$A$498,"2027-01",Gastos!$B$2:$B$498,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Viajes")</f>
         <v>0</v>
       </c>
     </row>

--- a/Gastos_Mensuales.xlsx
+++ b/Gastos_Mensuales.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3186" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3201" uniqueCount="401">
   <si>
     <t xml:space="preserve">Mes</t>
   </si>
@@ -357,90 +357,90 @@
     <t xml:space="preserve">IPS - aporte empleada doméstica (limpieza)</t>
   </si>
   <si>
+    <t xml:space="preserve">Mantenimiento auto - cuota 2/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comida afuera en oficina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reintegro Decathlon (regalo Rufi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reintegro supermercado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desayuno oficina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pádel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asado (salida)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Airtable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arreglo lavarropas - cuota 1/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arreglo lavarropas - cuota 2/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disney+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pollera Rufi (evento colegio)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Dominios (gestión web marca)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencia (personal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PC - cuota 1/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descuento PC (Tienda Naranja)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mantenimiento auto - cuota 1/2</t>
   </si>
   <si>
-    <t xml:space="preserve">Mantenimiento auto - cuota 2/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comida afuera en oficina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reintegro Decathlon (regalo Rufi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reintegro supermercado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desayuno oficina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pádel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asado (salida)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airtable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arreglo lavarropas - cuota 1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arreglo lavarropas - cuota 2/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disney+</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pollera Rufi (evento colegio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Dominios (gestión web marca)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transferencia (personal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-03-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PC - cuota 1/12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-04-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descuento PC (Tienda Naranja)</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026-06-08</t>
   </si>
   <si>
@@ -1123,6 +1123,9 @@
   </si>
   <si>
     <t xml:space="preserve">Remeras (2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Libro (Amazon)</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -1661,7 +1664,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I510"/>
+  <dimension ref="A1:I512"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -6255,7 +6258,7 @@
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>47</v>
@@ -6269,7 +6272,7 @@
         <v>18</v>
       </c>
       <c r="G194" s="4" t="n">
-        <v>812527</v>
+        <v>794100</v>
       </c>
       <c r="H194" s="3" t="s">
         <v>51</v>
@@ -6278,24 +6281,28 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C195" s="3"/>
-      <c r="D195" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C195" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="E195" s="3" t="s">
         <v>112</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G195" s="4" t="n">
-        <v>794100</v>
+        <v>36000</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="I195" s="3"/>
     </row>
@@ -6307,22 +6314,22 @@
         <v>65</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G196" s="4" t="n">
-        <v>36000</v>
+        <v>-400000</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I196" s="3"/>
     </row>
@@ -6334,10 +6341,10 @@
         <v>65</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>115</v>
@@ -6346,7 +6353,7 @@
         <v>12</v>
       </c>
       <c r="G197" s="4" t="n">
-        <v>-400000</v>
+        <v>-169834</v>
       </c>
       <c r="H197" s="3" t="s">
         <v>13</v>
@@ -6361,19 +6368,19 @@
         <v>65</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G198" s="4" t="n">
-        <v>-169834</v>
+        <v>80000</v>
       </c>
       <c r="H198" s="3" t="s">
         <v>13</v>
@@ -6388,19 +6395,19 @@
         <v>65</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G199" s="4" t="n">
-        <v>80000</v>
+        <v>20000</v>
       </c>
       <c r="H199" s="3" t="s">
         <v>13</v>
@@ -6415,22 +6422,22 @@
         <v>65</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G200" s="4" t="n">
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="H200" s="3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I200" s="3"/>
     </row>
@@ -6442,22 +6449,22 @@
         <v>65</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D201" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E201" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E201" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="F201" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G201" s="4" t="n">
-        <v>70000</v>
+        <v>42000</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I201" s="3"/>
     </row>
@@ -6469,19 +6476,19 @@
         <v>65</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G202" s="4" t="n">
-        <v>42000</v>
+        <v>25000</v>
       </c>
       <c r="H202" s="3" t="s">
         <v>13</v>
@@ -6496,19 +6503,19 @@
         <v>65</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G203" s="4" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="H203" s="3" t="s">
         <v>13</v>
@@ -6523,19 +6530,19 @@
         <v>65</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G204" s="4" t="n">
-        <v>20000</v>
+        <v>45000</v>
       </c>
       <c r="H204" s="3" t="s">
         <v>13</v>
@@ -6550,13 +6557,13 @@
         <v>65</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D205" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E205" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="E205" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>12</v>
@@ -6577,10 +6584,10 @@
         <v>65</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E206" s="3" t="s">
         <v>120</v>
@@ -6589,7 +6596,7 @@
         <v>12</v>
       </c>
       <c r="G206" s="4" t="n">
-        <v>45000</v>
+        <v>91777</v>
       </c>
       <c r="H206" s="3" t="s">
         <v>13</v>
@@ -6607,16 +6614,16 @@
         <v>69</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>121</v>
+        <v>69</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G207" s="4" t="n">
-        <v>91777</v>
+        <v>50000</v>
       </c>
       <c r="H207" s="3" t="s">
         <v>13</v>
@@ -6631,19 +6638,19 @@
         <v>65</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G208" s="4" t="n">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="H208" s="3" t="s">
         <v>13</v>
@@ -6658,19 +6665,19 @@
         <v>65</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G209" s="4" t="n">
-        <v>25000</v>
+        <v>23050</v>
       </c>
       <c r="H209" s="3" t="s">
         <v>13</v>
@@ -6682,25 +6689,23 @@
         <v>9</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C210" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C210" s="3"/>
       <c r="D210" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E210" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E210" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="F210" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G210" s="4" t="n">
-        <v>23050</v>
+        <v>144823</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I210" s="3"/>
     </row>
@@ -6709,23 +6714,25 @@
         <v>9</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C211" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C211" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D211" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="F211" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G211" s="4" t="n">
-        <v>144823</v>
+        <v>-14942</v>
       </c>
       <c r="H211" s="3" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I211" s="3"/>
     </row>
@@ -6740,16 +6747,16 @@
         <v>79</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G212" s="4" t="n">
-        <v>-14942</v>
+        <v>-5422</v>
       </c>
       <c r="H212" s="3" t="s">
         <v>13</v>
@@ -6758,25 +6765,21 @@
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C213" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D213" s="3" t="s">
-        <v>122</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C213" s="3"/>
+      <c r="D213" s="3"/>
       <c r="E213" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F213" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G213" s="4" t="n">
-        <v>-5422</v>
+        <v>1001250</v>
       </c>
       <c r="H213" s="3" t="s">
         <v>13</v>
@@ -6785,7 +6788,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>47</v>
@@ -6808,21 +6811,23 @@
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B215" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C215" s="3"/>
-      <c r="D215" s="3"/>
+      <c r="D215" s="3" t="s">
+        <v>125</v>
+      </c>
       <c r="E215" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>18</v>
       </c>
       <c r="G215" s="4" t="n">
-        <v>1001250</v>
+        <v>121900</v>
       </c>
       <c r="H215" s="3" t="s">
         <v>13</v>
@@ -6831,26 +6836,28 @@
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B216" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C216" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="D216" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E216" s="3" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="F216" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G216" s="4" t="n">
-        <v>121900</v>
+        <v>120000</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I216" s="3"/>
     </row>
@@ -6862,22 +6869,22 @@
         <v>65</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E217" s="3" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G217" s="4" t="n">
-        <v>120000</v>
+        <v>10000</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I217" s="3"/>
     </row>
@@ -6889,19 +6896,19 @@
         <v>65</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E218" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G218" s="4" t="n">
-        <v>10000</v>
+        <v>98000</v>
       </c>
       <c r="H218" s="3" t="s">
         <v>13</v>
@@ -6916,19 +6923,19 @@
         <v>65</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G219" s="4" t="n">
-        <v>98000</v>
+        <v>201000</v>
       </c>
       <c r="H219" s="3" t="s">
         <v>13</v>
@@ -6943,22 +6950,22 @@
         <v>65</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D220" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E220" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E220" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="F220" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G220" s="4" t="n">
-        <v>201000</v>
+        <v>200000</v>
       </c>
       <c r="H220" s="3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I220" s="3"/>
     </row>
@@ -6970,22 +6977,22 @@
         <v>65</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G221" s="4" t="n">
-        <v>200000</v>
+        <v>42000</v>
       </c>
       <c r="H221" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I221" s="3"/>
     </row>
@@ -7000,7 +7007,7 @@
         <v>79</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E222" s="3" t="s">
         <v>79</v>
@@ -7009,7 +7016,7 @@
         <v>12</v>
       </c>
       <c r="G222" s="4" t="n">
-        <v>42000</v>
+        <v>162000</v>
       </c>
       <c r="H222" s="3" t="s">
         <v>13</v>
@@ -7021,25 +7028,23 @@
         <v>9</v>
       </c>
       <c r="B223" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C223" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C223" s="3"/>
       <c r="D223" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="E223" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E223" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="F223" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G223" s="4" t="n">
-        <v>162000</v>
+        <v>38000</v>
       </c>
       <c r="H223" s="3" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="I223" s="3"/>
     </row>
@@ -7048,23 +7053,25 @@
         <v>9</v>
       </c>
       <c r="B224" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C224" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C224" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="D224" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E224" s="3" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="F224" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G224" s="4" t="n">
-        <v>38000</v>
+        <v>120000</v>
       </c>
       <c r="H224" s="3" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="I224" s="3"/>
     </row>
@@ -7076,71 +7083,69 @@
         <v>65</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>133</v>
       </c>
       <c r="E225" s="3" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G225" s="4" t="n">
-        <v>120000</v>
+        <v>163000</v>
       </c>
       <c r="H225" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I225" s="3"/>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>66</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="C226" s="3"/>
       <c r="D226" s="3" t="s">
         <v>134</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G226" s="4" t="n">
-        <v>163000</v>
+        <v>505932</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I226" s="3"/>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C227" s="3"/>
       <c r="D227" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G227" s="4" t="n">
-        <v>505932</v>
+        <v>-35000</v>
       </c>
       <c r="H227" s="3" t="s">
         <v>31</v>
@@ -7149,51 +7154,51 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C228" s="3"/>
       <c r="D228" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>138</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G228" s="4" t="n">
-        <v>-35000</v>
+        <v>811390</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="I228" s="3"/>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="3" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B229" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C229" s="3"/>
       <c r="D229" s="3" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>18</v>
       </c>
       <c r="G229" s="4" t="n">
-        <v>811390</v>
+        <v>122098</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="I229" s="3"/>
     </row>
@@ -7202,20 +7207,20 @@
         <v>42</v>
       </c>
       <c r="B230" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C230" s="3"/>
       <c r="D230" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G230" s="4" t="n">
-        <v>122098</v>
+        <v>356000</v>
       </c>
       <c r="H230" s="3" t="s">
         <v>13</v>
@@ -7224,48 +7229,50 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B231" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C231" s="3"/>
       <c r="D231" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G231" s="4" t="n">
-        <v>356000</v>
+        <v>161568</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I231" s="3"/>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B232" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C232" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C232" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D232" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G232" s="4" t="n">
-        <v>161568</v>
+        <v>1492000</v>
       </c>
       <c r="H232" s="3" t="s">
         <v>31</v>
@@ -7280,19 +7287,19 @@
         <v>65</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>144</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G233" s="4" t="n">
-        <v>1492000</v>
+        <v>30000</v>
       </c>
       <c r="H233" s="3" t="s">
         <v>31</v>
@@ -7307,19 +7314,19 @@
         <v>65</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G234" s="4" t="n">
-        <v>30000</v>
+        <v>108850</v>
       </c>
       <c r="H234" s="3" t="s">
         <v>31</v>
@@ -7334,19 +7341,19 @@
         <v>65</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D235" s="3" t="s">
         <v>147</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G235" s="4" t="n">
-        <v>108850</v>
+        <v>90000</v>
       </c>
       <c r="H235" s="3" t="s">
         <v>31</v>
@@ -7361,19 +7368,19 @@
         <v>65</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G236" s="4" t="n">
-        <v>90000</v>
+        <v>61000</v>
       </c>
       <c r="H236" s="3" t="s">
         <v>31</v>
@@ -7388,19 +7395,19 @@
         <v>65</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="D237" s="3" t="s">
         <v>150</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G237" s="4" t="n">
-        <v>61000</v>
+        <v>20000</v>
       </c>
       <c r="H237" s="3" t="s">
         <v>31</v>
@@ -7409,25 +7416,23 @@
     </row>
     <row r="238" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C238" s="3" t="s">
-        <v>69</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C238" s="3"/>
       <c r="D238" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G238" s="4" t="n">
-        <v>20000</v>
+        <v>6733</v>
       </c>
       <c r="H238" s="3" t="s">
         <v>31</v>
@@ -7436,50 +7441,52 @@
     </row>
     <row r="239" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C239" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C239" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D239" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>152</v>
+        <v>68</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G239" s="4" t="n">
-        <v>6733</v>
+        <v>134000</v>
       </c>
       <c r="H239" s="3" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I239" s="3"/>
     </row>
     <row r="240" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G240" s="4" t="n">
-        <v>134000</v>
+        <v>519563</v>
       </c>
       <c r="H240" s="3" t="s">
         <v>13</v>
@@ -7497,16 +7504,16 @@
         <v>69</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G241" s="4" t="n">
-        <v>519563</v>
+        <v>135000</v>
       </c>
       <c r="H241" s="3" t="s">
         <v>13</v>
@@ -7521,19 +7528,19 @@
         <v>65</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D242" s="3" t="s">
         <v>156</v>
       </c>
       <c r="E242" s="3" t="s">
-        <v>157</v>
+        <v>68</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G242" s="4" t="n">
-        <v>135000</v>
+        <v>269500</v>
       </c>
       <c r="H242" s="3" t="s">
         <v>13</v>
@@ -7548,19 +7555,19 @@
         <v>65</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E243" s="3" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G243" s="4" t="n">
-        <v>269500</v>
+        <v>708266</v>
       </c>
       <c r="H243" s="3" t="s">
         <v>13</v>
@@ -7581,13 +7588,13 @@
         <v>158</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G244" s="4" t="n">
-        <v>708266</v>
+        <v>-141653</v>
       </c>
       <c r="H244" s="3" t="s">
         <v>13</v>
@@ -7599,22 +7606,20 @@
         <v>32</v>
       </c>
       <c r="B245" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C245" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C245" s="3"/>
       <c r="D245" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G245" s="4" t="n">
-        <v>-141653</v>
+        <v>124699</v>
       </c>
       <c r="H245" s="3" t="s">
         <v>13</v>
@@ -7623,26 +7628,26 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="C246" s="3"/>
       <c r="D246" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E246" s="3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G246" s="4" t="n">
-        <v>124699</v>
+        <v>4724610</v>
       </c>
       <c r="H246" s="3" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="I246" s="3"/>
     </row>
@@ -7655,16 +7660,16 @@
       </c>
       <c r="C247" s="3"/>
       <c r="D247" s="3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="E247" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G247" s="4" t="n">
-        <v>4724610</v>
+        <v>1545000</v>
       </c>
       <c r="H247" s="3" t="s">
         <v>64</v>
@@ -7683,13 +7688,13 @@
         <v>162</v>
       </c>
       <c r="E248" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G248" s="4" t="n">
-        <v>1545000</v>
+        <v>2161949</v>
       </c>
       <c r="H248" s="3" t="s">
         <v>64</v>
@@ -7708,13 +7713,13 @@
         <v>162</v>
       </c>
       <c r="E249" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G249" s="4" t="n">
-        <v>2161949</v>
+        <v>7869921</v>
       </c>
       <c r="H249" s="3" t="s">
         <v>64</v>
@@ -7751,20 +7756,22 @@
         <v>42</v>
       </c>
       <c r="B251" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C251" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C251" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="D251" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E251" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G251" s="4" t="n">
-        <v>7869921</v>
+        <v>171000</v>
       </c>
       <c r="H251" s="3" t="s">
         <v>64</v>
@@ -7779,19 +7786,19 @@
         <v>65</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E252" s="3" t="s">
-        <v>168</v>
+        <v>79</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G252" s="4" t="n">
-        <v>171000</v>
+        <v>745373</v>
       </c>
       <c r="H252" s="3" t="s">
         <v>64</v>
@@ -7818,7 +7825,7 @@
         <v>12</v>
       </c>
       <c r="G253" s="4" t="n">
-        <v>745373</v>
+        <v>136317</v>
       </c>
       <c r="H253" s="3" t="s">
         <v>64</v>
@@ -7833,19 +7840,19 @@
         <v>65</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="D254" s="3" t="s">
         <v>162</v>
       </c>
       <c r="E254" s="3" t="s">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G254" s="4" t="n">
-        <v>136317</v>
+        <v>167775</v>
       </c>
       <c r="H254" s="3" t="s">
         <v>64</v>
@@ -7854,25 +7861,25 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>166</v>
+        <v>69</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="E255" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G255" s="4" t="n">
-        <v>167775</v>
+        <v>158000</v>
       </c>
       <c r="H255" s="3" t="s">
         <v>64</v>
@@ -7887,19 +7894,19 @@
         <v>65</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E256" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G256" s="4" t="n">
-        <v>158000</v>
+        <v>303784</v>
       </c>
       <c r="H256" s="3" t="s">
         <v>64</v>
@@ -7908,25 +7915,25 @@
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E257" s="3" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G257" s="4" t="n">
-        <v>303784</v>
+        <v>-223612</v>
       </c>
       <c r="H257" s="3" t="s">
         <v>64</v>
@@ -7947,13 +7954,13 @@
         <v>162</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G258" s="4" t="n">
-        <v>-223612</v>
+        <v>-40895</v>
       </c>
       <c r="H258" s="3" t="s">
         <v>64</v>
@@ -7962,28 +7969,28 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="E259" s="3" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G259" s="4" t="n">
-        <v>-40895</v>
+        <v>12193</v>
       </c>
       <c r="H259" s="3" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="I259" s="3"/>
     </row>
@@ -7998,7 +8005,7 @@
         <v>82</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>92</v>
@@ -8007,7 +8014,7 @@
         <v>12</v>
       </c>
       <c r="G260" s="4" t="n">
-        <v>12193</v>
+        <v>16142</v>
       </c>
       <c r="H260" s="3" t="s">
         <v>31</v>
@@ -8034,7 +8041,7 @@
         <v>12</v>
       </c>
       <c r="G261" s="4" t="n">
-        <v>16142</v>
+        <v>18263</v>
       </c>
       <c r="H261" s="3" t="s">
         <v>31</v>
@@ -8052,7 +8059,7 @@
         <v>82</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>92</v>
@@ -8061,7 +8068,7 @@
         <v>12</v>
       </c>
       <c r="G262" s="4" t="n">
-        <v>18263</v>
+        <v>17217</v>
       </c>
       <c r="H262" s="3" t="s">
         <v>31</v>
@@ -8088,7 +8095,7 @@
         <v>12</v>
       </c>
       <c r="G263" s="4" t="n">
-        <v>17217</v>
+        <v>18237</v>
       </c>
       <c r="H263" s="3" t="s">
         <v>31</v>
@@ -8106,7 +8113,7 @@
         <v>82</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>92</v>
@@ -8115,7 +8122,7 @@
         <v>12</v>
       </c>
       <c r="G264" s="4" t="n">
-        <v>18237</v>
+        <v>17289</v>
       </c>
       <c r="H264" s="3" t="s">
         <v>31</v>
@@ -8142,7 +8149,7 @@
         <v>12</v>
       </c>
       <c r="G265" s="4" t="n">
-        <v>17289</v>
+        <v>18306</v>
       </c>
       <c r="H265" s="3" t="s">
         <v>31</v>
@@ -8157,19 +8164,19 @@
         <v>65</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>82</v>
+        <v>166</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E266" s="3" t="s">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G266" s="4" t="n">
-        <v>18306</v>
+        <v>125000</v>
       </c>
       <c r="H266" s="3" t="s">
         <v>31</v>
@@ -8184,19 +8191,19 @@
         <v>65</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>166</v>
+        <v>69</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E267" s="3" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G267" s="4" t="n">
-        <v>125000</v>
+        <v>400000</v>
       </c>
       <c r="H267" s="3" t="s">
         <v>31</v>
@@ -8208,22 +8215,20 @@
         <v>36</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C268" s="3" t="s">
-        <v>69</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C268" s="3"/>
       <c r="D268" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E268" s="3" t="s">
-        <v>179</v>
+        <v>152</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G268" s="4" t="n">
-        <v>400000</v>
+        <v>10097</v>
       </c>
       <c r="H268" s="3" t="s">
         <v>31</v>
@@ -8232,23 +8237,23 @@
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B269" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C269" s="3"/>
       <c r="D269" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E269" s="3" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G269" s="4" t="n">
-        <v>10097</v>
+        <v>137500</v>
       </c>
       <c r="H269" s="3" t="s">
         <v>31</v>
@@ -8264,16 +8269,16 @@
       </c>
       <c r="C270" s="3"/>
       <c r="D270" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E270" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>18</v>
       </c>
       <c r="G270" s="4" t="n">
-        <v>137500</v>
+        <v>33825</v>
       </c>
       <c r="H270" s="3" t="s">
         <v>31</v>
@@ -8285,20 +8290,22 @@
         <v>41</v>
       </c>
       <c r="B271" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C271" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D271" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>183</v>
+        <v>68</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G271" s="4" t="n">
-        <v>33825</v>
+        <v>133900</v>
       </c>
       <c r="H271" s="3" t="s">
         <v>31</v>
@@ -8316,7 +8323,7 @@
         <v>66</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E272" s="3" t="s">
         <v>68</v>
@@ -8325,7 +8332,7 @@
         <v>12</v>
       </c>
       <c r="G272" s="4" t="n">
-        <v>133900</v>
+        <v>158000</v>
       </c>
       <c r="H272" s="3" t="s">
         <v>31</v>
@@ -8340,19 +8347,19 @@
         <v>65</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E273" s="3" t="s">
-        <v>68</v>
+        <v>186</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G273" s="4" t="n">
-        <v>158000</v>
+        <v>77000</v>
       </c>
       <c r="H273" s="3" t="s">
         <v>31</v>
@@ -8367,19 +8374,19 @@
         <v>65</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>186</v>
+        <v>68</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G274" s="4" t="n">
-        <v>77000</v>
+        <v>214000</v>
       </c>
       <c r="H274" s="3" t="s">
         <v>31</v>
@@ -8388,28 +8395,28 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E275" s="3" t="s">
-        <v>68</v>
+        <v>188</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G275" s="4" t="n">
-        <v>214000</v>
+        <v>160000</v>
       </c>
       <c r="H275" s="3" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I275" s="3"/>
     </row>
@@ -8424,16 +8431,16 @@
         <v>69</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E276" s="3" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G276" s="4" t="n">
-        <v>160000</v>
+        <v>495727</v>
       </c>
       <c r="H276" s="3" t="s">
         <v>13</v>
@@ -8445,22 +8452,20 @@
         <v>42</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C277" s="3" t="s">
-        <v>69</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C277" s="3"/>
       <c r="D277" s="3" t="s">
         <v>189</v>
       </c>
       <c r="E277" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G277" s="4" t="n">
-        <v>495727</v>
+        <v>40451</v>
       </c>
       <c r="H277" s="3" t="s">
         <v>13</v>
@@ -8472,23 +8477,25 @@
         <v>42</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C278" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C278" s="3" t="s">
+        <v>166</v>
+      </c>
       <c r="D278" s="3" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="E278" s="3" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G278" s="4" t="n">
-        <v>40451</v>
+        <v>338074</v>
       </c>
       <c r="H278" s="3" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="I278" s="3"/>
     </row>
@@ -8500,19 +8507,19 @@
         <v>65</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="E279" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G279" s="4" t="n">
-        <v>338074</v>
+        <v>53700</v>
       </c>
       <c r="H279" s="3" t="s">
         <v>64</v>
@@ -8527,19 +8534,19 @@
         <v>65</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="E280" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G280" s="4" t="n">
-        <v>53700</v>
+        <v>-50711</v>
       </c>
       <c r="H280" s="3" t="s">
         <v>64</v>
@@ -8548,7 +8555,7 @@
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>65</v>
@@ -8557,19 +8564,19 @@
         <v>166</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="E281" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G281" s="4" t="n">
-        <v>-50711</v>
+        <v>147440</v>
       </c>
       <c r="H281" s="3" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="I281" s="3"/>
     </row>
@@ -8581,19 +8588,19 @@
         <v>65</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>166</v>
+        <v>69</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E282" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G282" s="4" t="n">
-        <v>147440</v>
+        <v>106000</v>
       </c>
       <c r="H282" s="3" t="s">
         <v>31</v>
@@ -8608,19 +8615,19 @@
         <v>65</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E283" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G283" s="4" t="n">
-        <v>106000</v>
+        <v>788596</v>
       </c>
       <c r="H283" s="3" t="s">
         <v>31</v>
@@ -8635,19 +8642,19 @@
         <v>65</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D284" s="3" t="s">
         <v>197</v>
       </c>
       <c r="E284" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G284" s="4" t="n">
-        <v>788596</v>
+        <v>171000</v>
       </c>
       <c r="H284" s="3" t="s">
         <v>31</v>
@@ -8662,19 +8669,19 @@
         <v>65</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>199</v>
+        <v>68</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G285" s="4" t="n">
-        <v>171000</v>
+        <v>266500</v>
       </c>
       <c r="H285" s="3" t="s">
         <v>31</v>
@@ -8683,25 +8690,25 @@
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E286" s="3" t="s">
-        <v>68</v>
+        <v>202</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G286" s="4" t="n">
-        <v>266500</v>
+        <v>1260000</v>
       </c>
       <c r="H286" s="3" t="s">
         <v>31</v>
@@ -8710,25 +8717,25 @@
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E287" s="3" t="s">
-        <v>202</v>
+        <v>115</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G287" s="4" t="n">
-        <v>1260000</v>
+        <v>-157719</v>
       </c>
       <c r="H287" s="3" t="s">
         <v>31</v>
@@ -8737,25 +8744,23 @@
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C288" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C288" s="3"/>
       <c r="D288" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G288" s="4" t="n">
-        <v>-157719</v>
+        <v>28885</v>
       </c>
       <c r="H288" s="3" t="s">
         <v>31</v>
@@ -8764,23 +8769,25 @@
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B289" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C289" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C289" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="D289" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>152</v>
+        <v>92</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G289" s="4" t="n">
-        <v>28885</v>
+        <v>16128</v>
       </c>
       <c r="H289" s="3" t="s">
         <v>31</v>
@@ -8798,7 +8805,7 @@
         <v>82</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E290" s="3" t="s">
         <v>92</v>
@@ -8807,7 +8814,7 @@
         <v>12</v>
       </c>
       <c r="G290" s="4" t="n">
-        <v>16128</v>
+        <v>20280</v>
       </c>
       <c r="H290" s="3" t="s">
         <v>31</v>
@@ -8834,7 +8841,7 @@
         <v>12</v>
       </c>
       <c r="G291" s="4" t="n">
-        <v>20280</v>
+        <v>18252</v>
       </c>
       <c r="H291" s="3" t="s">
         <v>31</v>
@@ -8861,7 +8868,7 @@
         <v>12</v>
       </c>
       <c r="G292" s="4" t="n">
-        <v>18252</v>
+        <v>17238</v>
       </c>
       <c r="H292" s="3" t="s">
         <v>31</v>
@@ -8888,7 +8895,7 @@
         <v>12</v>
       </c>
       <c r="G293" s="4" t="n">
-        <v>17238</v>
+        <v>18252</v>
       </c>
       <c r="H293" s="3" t="s">
         <v>31</v>
@@ -8906,7 +8913,7 @@
         <v>82</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E294" s="3" t="s">
         <v>92</v>
@@ -8915,7 +8922,7 @@
         <v>12</v>
       </c>
       <c r="G294" s="4" t="n">
-        <v>18252</v>
+        <v>16136</v>
       </c>
       <c r="H294" s="3" t="s">
         <v>31</v>
@@ -8933,7 +8940,7 @@
         <v>82</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E295" s="3" t="s">
         <v>92</v>
@@ -8942,7 +8949,7 @@
         <v>12</v>
       </c>
       <c r="G295" s="4" t="n">
-        <v>16136</v>
+        <v>26510</v>
       </c>
       <c r="H295" s="3" t="s">
         <v>31</v>
@@ -8960,16 +8967,16 @@
         <v>82</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>92</v>
+        <v>208</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G296" s="4" t="n">
-        <v>26510</v>
+        <v>688000</v>
       </c>
       <c r="H296" s="3" t="s">
         <v>31</v>
@@ -8984,19 +8991,19 @@
         <v>65</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E297" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F297" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G297" s="4" t="n">
-        <v>688000</v>
+        <v>48000</v>
       </c>
       <c r="H297" s="3" t="s">
         <v>31</v>
@@ -9014,16 +9021,16 @@
         <v>69</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E298" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G298" s="4" t="n">
-        <v>48000</v>
+        <v>473000</v>
       </c>
       <c r="H298" s="3" t="s">
         <v>31</v>
@@ -9038,19 +9045,19 @@
         <v>65</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F299" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G299" s="4" t="n">
-        <v>473000</v>
+        <v>229200</v>
       </c>
       <c r="H299" s="3" t="s">
         <v>31</v>
@@ -9065,19 +9072,19 @@
         <v>65</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E300" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G300" s="4" t="n">
-        <v>229200</v>
+        <v>190002</v>
       </c>
       <c r="H300" s="3" t="s">
         <v>31</v>
@@ -9086,25 +9093,25 @@
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E301" s="3" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="F301" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G301" s="4" t="n">
-        <v>190002</v>
+        <v>999056</v>
       </c>
       <c r="H301" s="3" t="s">
         <v>31</v>
@@ -9119,19 +9126,19 @@
         <v>65</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="D302" s="3" t="s">
         <v>213</v>
       </c>
       <c r="E302" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F302" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G302" s="4" t="n">
-        <v>999056</v>
+        <v>195000</v>
       </c>
       <c r="H302" s="3" t="s">
         <v>31</v>
@@ -9152,13 +9159,13 @@
         <v>213</v>
       </c>
       <c r="E303" s="3" t="s">
-        <v>215</v>
+        <v>146</v>
       </c>
       <c r="F303" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G303" s="4" t="n">
-        <v>195000</v>
+        <v>70000</v>
       </c>
       <c r="H303" s="3" t="s">
         <v>31</v>
@@ -9170,22 +9177,20 @@
         <v>38</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C304" s="3" t="s">
-        <v>69</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C304" s="3"/>
       <c r="D304" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E304" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F304" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G304" s="4" t="n">
-        <v>70000</v>
+        <v>10381</v>
       </c>
       <c r="H304" s="3" t="s">
         <v>31</v>
@@ -9194,23 +9199,25 @@
     </row>
     <row r="305" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B305" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C305" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C305" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D305" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E305" s="3" t="s">
-        <v>152</v>
+        <v>68</v>
       </c>
       <c r="F305" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G305" s="4" t="n">
-        <v>10381</v>
+        <v>117500</v>
       </c>
       <c r="H305" s="3" t="s">
         <v>31</v>
@@ -9231,13 +9238,13 @@
         <v>217</v>
       </c>
       <c r="E306" s="3" t="s">
-        <v>68</v>
+        <v>218</v>
       </c>
       <c r="F306" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G306" s="4" t="n">
-        <v>117500</v>
+        <v>6000</v>
       </c>
       <c r="H306" s="3" t="s">
         <v>31</v>
@@ -9252,19 +9259,19 @@
         <v>65</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E307" s="3" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="F307" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G307" s="4" t="n">
-        <v>6000</v>
+        <v>80000</v>
       </c>
       <c r="H307" s="3" t="s">
         <v>31</v>
@@ -9282,16 +9289,16 @@
         <v>69</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E308" s="3" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="F308" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G308" s="4" t="n">
-        <v>80000</v>
+        <v>280000</v>
       </c>
       <c r="H308" s="3" t="s">
         <v>31</v>
@@ -9312,13 +9319,13 @@
         <v>220</v>
       </c>
       <c r="E309" s="3" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="F309" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G309" s="4" t="n">
-        <v>280000</v>
+        <v>100000</v>
       </c>
       <c r="H309" s="3" t="s">
         <v>31</v>
@@ -9336,16 +9343,16 @@
         <v>69</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E310" s="3" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="F310" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G310" s="4" t="n">
-        <v>100000</v>
+        <v>140800</v>
       </c>
       <c r="H310" s="3" t="s">
         <v>31</v>
@@ -9354,7 +9361,7 @@
     </row>
     <row r="311" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>65</v>
@@ -9363,16 +9370,16 @@
         <v>69</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E311" s="3" t="s">
-        <v>157</v>
+        <v>223</v>
       </c>
       <c r="F311" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G311" s="4" t="n">
-        <v>140800</v>
+        <v>51200</v>
       </c>
       <c r="H311" s="3" t="s">
         <v>31</v>
@@ -9387,19 +9394,19 @@
         <v>65</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E312" s="3" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="F312" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G312" s="4" t="n">
-        <v>51200</v>
+        <v>564697</v>
       </c>
       <c r="H312" s="3" t="s">
         <v>31</v>
@@ -9420,13 +9427,13 @@
         <v>224</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="F313" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G313" s="4" t="n">
-        <v>564697</v>
+        <v>-112939</v>
       </c>
       <c r="H313" s="3" t="s">
         <v>31</v>
@@ -9438,22 +9445,20 @@
         <v>40</v>
       </c>
       <c r="B314" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C314" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C314" s="3"/>
       <c r="D314" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E314" s="3" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="F314" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G314" s="4" t="n">
-        <v>-112939</v>
+        <v>25752</v>
       </c>
       <c r="H314" s="3" t="s">
         <v>31</v>
@@ -9462,26 +9467,26 @@
     </row>
     <row r="315" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="3" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B315" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C315" s="3"/>
       <c r="D315" s="3" t="s">
-        <v>225</v>
+        <v>90</v>
       </c>
       <c r="E315" s="3" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="F315" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G315" s="4" t="n">
-        <v>25752</v>
+        <v>119526</v>
       </c>
       <c r="H315" s="3" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I315" s="3"/>
     </row>
@@ -9490,20 +9495,22 @@
         <v>9</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C316" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C316" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="D316" s="3" t="s">
-        <v>90</v>
+        <v>226</v>
       </c>
       <c r="E316" s="3" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G316" s="4" t="n">
-        <v>119526</v>
+        <v>25528</v>
       </c>
       <c r="H316" s="3" t="s">
         <v>13</v>
@@ -9521,7 +9528,7 @@
         <v>82</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="E317" s="3" t="s">
         <v>92</v>
@@ -9530,7 +9537,7 @@
         <v>12</v>
       </c>
       <c r="G317" s="4" t="n">
-        <v>25528</v>
+        <v>23457</v>
       </c>
       <c r="H317" s="3" t="s">
         <v>13</v>
@@ -9548,7 +9555,7 @@
         <v>82</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="E318" s="3" t="s">
         <v>92</v>
@@ -9557,7 +9564,7 @@
         <v>12</v>
       </c>
       <c r="G318" s="4" t="n">
-        <v>23457</v>
+        <v>13154</v>
       </c>
       <c r="H318" s="3" t="s">
         <v>13</v>
@@ -9566,25 +9573,25 @@
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="3" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C319" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="E319" s="3" t="s">
-        <v>92</v>
+        <v>155</v>
       </c>
       <c r="F319" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G319" s="4" t="n">
-        <v>13154</v>
+        <v>831231</v>
       </c>
       <c r="H319" s="3" t="s">
         <v>13</v>
@@ -9599,19 +9606,19 @@
         <v>65</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>142</v>
+        <v>227</v>
       </c>
       <c r="E320" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="F320" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G320" s="4" t="n">
-        <v>831231</v>
+        <v>46150</v>
       </c>
       <c r="H320" s="3" t="s">
         <v>13</v>
@@ -9629,16 +9636,16 @@
         <v>79</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E321" s="3" t="s">
-        <v>148</v>
+        <v>229</v>
       </c>
       <c r="F321" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G321" s="4" t="n">
-        <v>46150</v>
+        <v>265505</v>
       </c>
       <c r="H321" s="3" t="s">
         <v>13</v>
@@ -9653,19 +9660,19 @@
         <v>65</v>
       </c>
       <c r="C322" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D322" s="3" t="s">
         <v>228</v>
       </c>
       <c r="E322" s="3" t="s">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="F322" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G322" s="4" t="n">
-        <v>265505</v>
+        <v>193766</v>
       </c>
       <c r="H322" s="3" t="s">
         <v>13</v>
@@ -9680,19 +9687,19 @@
         <v>65</v>
       </c>
       <c r="C323" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D323" s="3" t="s">
         <v>228</v>
       </c>
       <c r="E323" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="F323" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G323" s="4" t="n">
-        <v>193766</v>
+        <v>48350</v>
       </c>
       <c r="H323" s="3" t="s">
         <v>13</v>
@@ -9701,7 +9708,7 @@
     </row>
     <row r="324" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>65</v>
@@ -9710,16 +9717,16 @@
         <v>79</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>228</v>
+        <v>75</v>
       </c>
       <c r="E324" s="3" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="F324" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G324" s="4" t="n">
-        <v>48350</v>
+        <v>29150</v>
       </c>
       <c r="H324" s="3" t="s">
         <v>13</v>
@@ -9734,19 +9741,19 @@
         <v>65</v>
       </c>
       <c r="C325" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="E325" s="3" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
       <c r="F325" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G325" s="4" t="n">
-        <v>29150</v>
+        <v>37600</v>
       </c>
       <c r="H325" s="3" t="s">
         <v>13</v>
@@ -9761,19 +9768,19 @@
         <v>65</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="E326" s="3" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
       <c r="F326" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G326" s="4" t="n">
-        <v>37600</v>
+        <v>74710</v>
       </c>
       <c r="H326" s="3" t="s">
         <v>13</v>
@@ -9791,7 +9798,7 @@
         <v>79</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E327" s="3" t="s">
         <v>191</v>
@@ -9800,7 +9807,7 @@
         <v>12</v>
       </c>
       <c r="G327" s="4" t="n">
-        <v>74710</v>
+        <v>27111</v>
       </c>
       <c r="H327" s="3" t="s">
         <v>13</v>
@@ -9809,7 +9816,7 @@
     </row>
     <row r="328" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>65</v>
@@ -9818,16 +9825,16 @@
         <v>79</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>119</v>
+        <v>228</v>
       </c>
       <c r="E328" s="3" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="F328" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G328" s="4" t="n">
-        <v>27111</v>
+        <v>-53101</v>
       </c>
       <c r="H328" s="3" t="s">
         <v>13</v>
@@ -9836,25 +9843,25 @@
     </row>
     <row r="329" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E329" s="3" t="s">
-        <v>116</v>
+        <v>230</v>
       </c>
       <c r="F329" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G329" s="4" t="n">
-        <v>-53101</v>
+        <v>-7520</v>
       </c>
       <c r="H329" s="3" t="s">
         <v>13</v>
@@ -9866,22 +9873,20 @@
         <v>9</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C330" s="3" t="s">
-        <v>69</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C330" s="3"/>
       <c r="D330" s="3" t="s">
-        <v>226</v>
+        <v>121</v>
       </c>
       <c r="E330" s="3" t="s">
-        <v>230</v>
+        <v>152</v>
       </c>
       <c r="F330" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G330" s="4" t="n">
-        <v>-7520</v>
+        <v>79835</v>
       </c>
       <c r="H330" s="3" t="s">
         <v>13</v>
@@ -9890,32 +9895,34 @@
     </row>
     <row r="331" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="B331" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C331" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C331" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="D331" s="3" t="s">
-        <v>122</v>
+        <v>228</v>
       </c>
       <c r="E331" s="3" t="s">
-        <v>152</v>
+        <v>231</v>
       </c>
       <c r="F331" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G331" s="4" t="n">
-        <v>79835</v>
+        <v>771571</v>
       </c>
       <c r="H331" s="3" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="I331" s="3"/>
     </row>
     <row r="332" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>65</v>
@@ -9924,16 +9931,16 @@
         <v>105</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>228</v>
+        <v>78</v>
       </c>
       <c r="E332" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F332" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G332" s="4" t="n">
-        <v>771571</v>
+        <v>159800</v>
       </c>
       <c r="H332" s="3" t="s">
         <v>64</v>
@@ -9948,19 +9955,19 @@
         <v>65</v>
       </c>
       <c r="C333" s="3" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="D333" s="3" t="s">
         <v>78</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F333" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G333" s="4" t="n">
-        <v>159800</v>
+        <v>142500</v>
       </c>
       <c r="H333" s="3" t="s">
         <v>64</v>
@@ -9978,16 +9985,16 @@
         <v>166</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F334" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G334" s="4" t="n">
-        <v>142500</v>
+        <v>60000</v>
       </c>
       <c r="H334" s="3" t="s">
         <v>64</v>
@@ -10002,19 +10009,19 @@
         <v>65</v>
       </c>
       <c r="C335" s="3" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="F335" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G335" s="4" t="n">
-        <v>60000</v>
+        <v>95339</v>
       </c>
       <c r="H335" s="3" t="s">
         <v>64</v>
@@ -10029,19 +10036,19 @@
         <v>65</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>101</v>
+        <v>235</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>198</v>
+        <v>232</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G336" s="4" t="n">
-        <v>95339</v>
+        <v>174680</v>
       </c>
       <c r="H336" s="3" t="s">
         <v>64</v>
@@ -10062,13 +10069,13 @@
         <v>235</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F337" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G337" s="4" t="n">
-        <v>174680</v>
+        <v>477300</v>
       </c>
       <c r="H337" s="3" t="s">
         <v>64</v>
@@ -10083,46 +10090,44 @@
         <v>65</v>
       </c>
       <c r="C338" s="3" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>235</v>
+        <v>129</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F338" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G338" s="4" t="n">
-        <v>477300</v>
+        <v>116250</v>
       </c>
       <c r="H338" s="3" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="I338" s="3"/>
     </row>
     <row r="339" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="3" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C339" s="3" t="s">
-        <v>79</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C339" s="3"/>
       <c r="D339" s="3" t="s">
-        <v>130</v>
+        <v>237</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="F339" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G339" s="4" t="n">
-        <v>116250</v>
+        <v>356000</v>
       </c>
       <c r="H339" s="3" t="s">
         <v>13</v>
@@ -10134,20 +10139,18 @@
         <v>36</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C340" s="3"/>
-      <c r="D340" s="3" t="s">
-        <v>237</v>
-      </c>
+      <c r="D340" s="3"/>
       <c r="E340" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F340" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G340" s="4" t="n">
-        <v>356000</v>
+        <v>2833</v>
       </c>
       <c r="H340" s="3" t="s">
         <v>13</v>
@@ -10156,7 +10159,7 @@
     </row>
     <row r="341" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>10</v>
@@ -10170,7 +10173,7 @@
         <v>12</v>
       </c>
       <c r="G341" s="4" t="n">
-        <v>2833</v>
+        <v>3425</v>
       </c>
       <c r="H341" s="3" t="s">
         <v>13</v>
@@ -10179,7 +10182,7 @@
     </row>
     <row r="342" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>10</v>
@@ -10193,7 +10196,7 @@
         <v>12</v>
       </c>
       <c r="G342" s="4" t="n">
-        <v>3425</v>
+        <v>3866</v>
       </c>
       <c r="H342" s="3" t="s">
         <v>13</v>
@@ -10202,7 +10205,7 @@
     </row>
     <row r="343" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>10</v>
@@ -10216,7 +10219,7 @@
         <v>12</v>
       </c>
       <c r="G343" s="4" t="n">
-        <v>3866</v>
+        <v>4150</v>
       </c>
       <c r="H343" s="3" t="s">
         <v>13</v>
@@ -10225,7 +10228,7 @@
     </row>
     <row r="344" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>10</v>
@@ -10239,7 +10242,7 @@
         <v>12</v>
       </c>
       <c r="G344" s="4" t="n">
-        <v>4150</v>
+        <v>3625</v>
       </c>
       <c r="H344" s="3" t="s">
         <v>13</v>
@@ -10248,7 +10251,7 @@
     </row>
     <row r="345" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>10</v>
@@ -10262,16 +10265,16 @@
         <v>12</v>
       </c>
       <c r="G345" s="4" t="n">
-        <v>3625</v>
+        <v>2707</v>
       </c>
       <c r="H345" s="3" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="I345" s="3"/>
     </row>
     <row r="346" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>10</v>
@@ -10285,7 +10288,7 @@
         <v>12</v>
       </c>
       <c r="G346" s="4" t="n">
-        <v>2707</v>
+        <v>2697</v>
       </c>
       <c r="H346" s="3" t="s">
         <v>93</v>
@@ -10294,24 +10297,24 @@
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
       <c r="E347" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F347" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G347" s="4" t="n">
-        <v>2697</v>
+        <v>373520</v>
       </c>
       <c r="H347" s="3" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="I347" s="3"/>
     </row>
@@ -10320,18 +10323,18 @@
         <v>36</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>160</v>
+        <v>29</v>
       </c>
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
       <c r="E348" s="3" t="s">
-        <v>240</v>
+        <v>34</v>
       </c>
       <c r="F348" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G348" s="4" t="n">
-        <v>373520</v>
+        <v>60101</v>
       </c>
       <c r="H348" s="3" t="s">
         <v>13</v>
@@ -10343,18 +10346,22 @@
         <v>36</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C349" s="3"/>
-      <c r="D349" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C349" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D349" s="3" t="s">
+        <v>237</v>
+      </c>
       <c r="E349" s="3" t="s">
-        <v>34</v>
+        <v>241</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G349" s="4" t="n">
-        <v>60101</v>
+        <v>294383</v>
       </c>
       <c r="H349" s="3" t="s">
         <v>13</v>
@@ -10369,19 +10376,19 @@
         <v>65</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F350" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G350" s="4" t="n">
-        <v>294383</v>
+        <v>168000</v>
       </c>
       <c r="H350" s="3" t="s">
         <v>13</v>
@@ -10393,22 +10400,18 @@
         <v>36</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C351" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D351" s="3" t="s">
-        <v>242</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C351" s="3"/>
+      <c r="D351" s="3"/>
       <c r="E351" s="3" t="s">
-        <v>243</v>
+        <v>126</v>
       </c>
       <c r="F351" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G351" s="4" t="n">
-        <v>168000</v>
+        <v>134466</v>
       </c>
       <c r="H351" s="3" t="s">
         <v>13</v>
@@ -10420,18 +10423,20 @@
         <v>36</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C352" s="3"/>
-      <c r="D352" s="3"/>
+      <c r="D352" s="3" t="s">
+        <v>175</v>
+      </c>
       <c r="E352" s="3" t="s">
-        <v>127</v>
+        <v>244</v>
       </c>
       <c r="F352" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G352" s="4" t="n">
-        <v>134466</v>
+        <v>50982</v>
       </c>
       <c r="H352" s="3" t="s">
         <v>13</v>
@@ -10443,20 +10448,22 @@
         <v>36</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C353" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D353" s="3" t="s">
         <v>175</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F353" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G353" s="4" t="n">
-        <v>50982</v>
+        <v>936617</v>
       </c>
       <c r="H353" s="3" t="s">
         <v>13</v>
@@ -10474,16 +10481,16 @@
         <v>79</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>245</v>
+        <v>198</v>
       </c>
       <c r="F354" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G354" s="4" t="n">
-        <v>936617</v>
+        <v>207824</v>
       </c>
       <c r="H354" s="3" t="s">
         <v>13</v>
@@ -10498,19 +10505,19 @@
         <v>65</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>176</v>
+        <v>246</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>198</v>
+        <v>243</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G355" s="4" t="n">
-        <v>207824</v>
+        <v>150000</v>
       </c>
       <c r="H355" s="3" t="s">
         <v>13</v>
@@ -10522,22 +10529,18 @@
         <v>36</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C356" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D356" s="3" t="s">
-        <v>246</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C356" s="3"/>
+      <c r="D356" s="3"/>
       <c r="E356" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G356" s="4" t="n">
-        <v>150000</v>
+        <v>5603</v>
       </c>
       <c r="H356" s="3" t="s">
         <v>13</v>
@@ -10549,18 +10552,18 @@
         <v>36</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C357" s="3"/>
       <c r="D357" s="3"/>
       <c r="E357" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F357" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G357" s="4" t="n">
-        <v>5603</v>
+        <v>22727</v>
       </c>
       <c r="H357" s="3" t="s">
         <v>13</v>
@@ -10569,21 +10572,21 @@
     </row>
     <row r="358" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="C358" s="3"/>
       <c r="D358" s="3"/>
       <c r="E358" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F358" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G358" s="4" t="n">
-        <v>22727</v>
+        <v>373520</v>
       </c>
       <c r="H358" s="3" t="s">
         <v>13</v>
@@ -10592,21 +10595,25 @@
     </row>
     <row r="359" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C359" s="3"/>
-      <c r="D359" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C359" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D359" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="E359" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F359" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G359" s="4" t="n">
-        <v>373520</v>
+        <v>137000</v>
       </c>
       <c r="H359" s="3" t="s">
         <v>13</v>
@@ -10621,19 +10628,19 @@
         <v>65</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E360" s="3" t="s">
-        <v>243</v>
+        <v>198</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G360" s="4" t="n">
-        <v>137000</v>
+        <v>395852</v>
       </c>
       <c r="H360" s="3" t="s">
         <v>13</v>
@@ -10648,19 +10655,19 @@
         <v>65</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G361" s="4" t="n">
-        <v>395852</v>
+        <v>273847</v>
       </c>
       <c r="H361" s="3" t="s">
         <v>13</v>
@@ -10675,19 +10682,19 @@
         <v>65</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>250</v>
+        <v>211</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="F362" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G362" s="4" t="n">
-        <v>273847</v>
+        <v>195000</v>
       </c>
       <c r="H362" s="3" t="s">
         <v>13</v>
@@ -10702,19 +10709,19 @@
         <v>65</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G363" s="4" t="n">
-        <v>195000</v>
+        <v>134486</v>
       </c>
       <c r="H363" s="3" t="s">
         <v>13</v>
@@ -10732,16 +10739,16 @@
         <v>79</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G364" s="4" t="n">
-        <v>134486</v>
+        <v>48000</v>
       </c>
       <c r="H364" s="3" t="s">
         <v>13</v>
@@ -10759,16 +10766,16 @@
         <v>79</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>255</v>
+        <v>198</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G365" s="4" t="n">
-        <v>48000</v>
+        <v>517066</v>
       </c>
       <c r="H365" s="3" t="s">
         <v>13</v>
@@ -10780,22 +10787,18 @@
         <v>36</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C366" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D366" s="3" t="s">
-        <v>256</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C366" s="3"/>
+      <c r="D366" s="3"/>
       <c r="E366" s="3" t="s">
-        <v>198</v>
+        <v>34</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G366" s="4" t="n">
-        <v>517066</v>
+        <v>59589</v>
       </c>
       <c r="H366" s="3" t="s">
         <v>13</v>
@@ -10804,21 +10807,25 @@
     </row>
     <row r="367" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C367" s="3"/>
-      <c r="D367" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C367" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D367" s="3" t="s">
+        <v>257</v>
+      </c>
       <c r="E367" s="3" t="s">
-        <v>34</v>
+        <v>243</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G367" s="4" t="n">
-        <v>59589</v>
+        <v>127000</v>
       </c>
       <c r="H367" s="3" t="s">
         <v>13</v>
@@ -10836,7 +10843,7 @@
         <v>66</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E368" s="3" t="s">
         <v>243</v>
@@ -10845,7 +10852,7 @@
         <v>12</v>
       </c>
       <c r="G368" s="4" t="n">
-        <v>127000</v>
+        <v>112000</v>
       </c>
       <c r="H368" s="3" t="s">
         <v>13</v>
@@ -10860,19 +10867,19 @@
         <v>65</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D369" s="3" t="s">
         <v>258</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="F369" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G369" s="4" t="n">
-        <v>112000</v>
+        <v>259730</v>
       </c>
       <c r="H369" s="3" t="s">
         <v>13</v>
@@ -10887,19 +10894,19 @@
         <v>65</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G370" s="4" t="n">
-        <v>259730</v>
+        <v>139453</v>
       </c>
       <c r="H370" s="3" t="s">
         <v>13</v>
@@ -10911,22 +10918,18 @@
         <v>38</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C371" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D371" s="3" t="s">
-        <v>259</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C371" s="3"/>
+      <c r="D371" s="3"/>
       <c r="E371" s="3" t="s">
-        <v>245</v>
+        <v>126</v>
       </c>
       <c r="F371" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G371" s="4" t="n">
-        <v>139453</v>
+        <v>132793</v>
       </c>
       <c r="H371" s="3" t="s">
         <v>13</v>
@@ -10938,18 +10941,22 @@
         <v>38</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C372" s="3"/>
-      <c r="D372" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C372" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D372" s="3" t="s">
+        <v>260</v>
+      </c>
       <c r="E372" s="3" t="s">
-        <v>127</v>
+        <v>243</v>
       </c>
       <c r="F372" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G372" s="4" t="n">
-        <v>132793</v>
+        <v>407000</v>
       </c>
       <c r="H372" s="3" t="s">
         <v>13</v>
@@ -10964,19 +10971,19 @@
         <v>65</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G373" s="4" t="n">
-        <v>407000</v>
+        <v>929706</v>
       </c>
       <c r="H373" s="3" t="s">
         <v>13</v>
@@ -10991,19 +10998,19 @@
         <v>65</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>261</v>
+        <v>216</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G374" s="4" t="n">
-        <v>929706</v>
+        <v>878500</v>
       </c>
       <c r="H374" s="3" t="s">
         <v>13</v>
@@ -11018,19 +11025,19 @@
         <v>65</v>
       </c>
       <c r="C375" s="3" t="s">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="D375" s="3" t="s">
         <v>216</v>
       </c>
       <c r="E375" s="3" t="s">
-        <v>262</v>
+        <v>198</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G375" s="4" t="n">
-        <v>878500</v>
+        <v>328125</v>
       </c>
       <c r="H375" s="3" t="s">
         <v>13</v>
@@ -11045,19 +11052,19 @@
         <v>65</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D376" s="3" t="s">
-        <v>216</v>
+        <v>263</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>198</v>
+        <v>243</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G376" s="4" t="n">
-        <v>328125</v>
+        <v>166000</v>
       </c>
       <c r="H376" s="3" t="s">
         <v>13</v>
@@ -11072,19 +11079,19 @@
         <v>65</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D377" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E377" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G377" s="4" t="n">
-        <v>166000</v>
+        <v>270622</v>
       </c>
       <c r="H377" s="3" t="s">
         <v>13</v>
@@ -11096,22 +11103,18 @@
         <v>38</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C378" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D378" s="3" t="s">
-        <v>264</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C378" s="3"/>
+      <c r="D378" s="3"/>
       <c r="E378" s="3" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G378" s="4" t="n">
-        <v>270622</v>
+        <v>11516</v>
       </c>
       <c r="H378" s="3" t="s">
         <v>13</v>
@@ -11123,18 +11126,18 @@
         <v>38</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
       <c r="E379" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F379" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G379" s="4" t="n">
-        <v>11516</v>
+        <v>22727</v>
       </c>
       <c r="H379" s="3" t="s">
         <v>13</v>
@@ -11143,21 +11146,21 @@
     </row>
     <row r="380" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
       <c r="E380" s="3" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G380" s="4" t="n">
-        <v>22727</v>
+        <v>373520</v>
       </c>
       <c r="H380" s="3" t="s">
         <v>13</v>
@@ -11166,21 +11169,25 @@
     </row>
     <row r="381" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C381" s="3"/>
-      <c r="D381" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C381" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D381" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="E381" s="3" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G381" s="4" t="n">
-        <v>373520</v>
+        <v>181000</v>
       </c>
       <c r="H381" s="3" t="s">
         <v>13</v>
@@ -11195,19 +11202,19 @@
         <v>65</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G382" s="4" t="n">
-        <v>181000</v>
+        <v>78400</v>
       </c>
       <c r="H382" s="3" t="s">
         <v>13</v>
@@ -11222,19 +11229,19 @@
         <v>65</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G383" s="4" t="n">
-        <v>78400</v>
+        <v>440300</v>
       </c>
       <c r="H383" s="3" t="s">
         <v>13</v>
@@ -11249,19 +11256,19 @@
         <v>65</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G384" s="4" t="n">
-        <v>440300</v>
+        <v>265341</v>
       </c>
       <c r="H384" s="3" t="s">
         <v>13</v>
@@ -11282,13 +11289,13 @@
         <v>271</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G385" s="4" t="n">
-        <v>265341</v>
+        <v>243191</v>
       </c>
       <c r="H385" s="3" t="s">
         <v>13</v>
@@ -11303,19 +11310,19 @@
         <v>65</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D386" s="3" t="s">
-        <v>271</v>
+        <v>147</v>
       </c>
       <c r="E386" s="3" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G386" s="4" t="n">
-        <v>243191</v>
+        <v>239000</v>
       </c>
       <c r="H386" s="3" t="s">
         <v>13</v>
@@ -11330,19 +11337,19 @@
         <v>65</v>
       </c>
       <c r="C387" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D387" s="3" t="s">
         <v>147</v>
       </c>
       <c r="E387" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G387" s="4" t="n">
-        <v>239000</v>
+        <v>261384</v>
       </c>
       <c r="H387" s="3" t="s">
         <v>13</v>
@@ -11357,19 +11364,19 @@
         <v>65</v>
       </c>
       <c r="C388" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E388" s="3" t="s">
-        <v>251</v>
+        <v>198</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G388" s="4" t="n">
-        <v>261384</v>
+        <v>387502</v>
       </c>
       <c r="H388" s="3" t="s">
         <v>13</v>
@@ -11378,7 +11385,7 @@
     </row>
     <row r="389" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>65</v>
@@ -11387,16 +11394,16 @@
         <v>79</v>
       </c>
       <c r="D389" s="3" t="s">
-        <v>150</v>
+        <v>274</v>
       </c>
       <c r="E389" s="3" t="s">
-        <v>198</v>
+        <v>272</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G389" s="4" t="n">
-        <v>387502</v>
+        <v>260955</v>
       </c>
       <c r="H389" s="3" t="s">
         <v>13</v>
@@ -11408,22 +11415,18 @@
         <v>39</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C390" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D390" s="3" t="s">
-        <v>274</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C390" s="3"/>
+      <c r="D390" s="3"/>
       <c r="E390" s="3" t="s">
-        <v>272</v>
+        <v>34</v>
       </c>
       <c r="F390" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G390" s="4" t="n">
-        <v>260955</v>
+        <v>57831</v>
       </c>
       <c r="H390" s="3" t="s">
         <v>13</v>
@@ -11435,18 +11438,22 @@
         <v>39</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C391" s="3"/>
-      <c r="D391" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C391" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D391" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E391" s="3" t="s">
-        <v>34</v>
+        <v>275</v>
       </c>
       <c r="F391" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G391" s="4" t="n">
-        <v>57831</v>
+        <v>178000</v>
       </c>
       <c r="H391" s="3" t="s">
         <v>13</v>
@@ -11467,13 +11474,13 @@
         <v>274</v>
       </c>
       <c r="E392" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G392" s="4" t="n">
-        <v>178000</v>
+        <v>122000</v>
       </c>
       <c r="H392" s="3" t="s">
         <v>13</v>
@@ -11488,19 +11495,19 @@
         <v>65</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D393" s="3" t="s">
         <v>274</v>
       </c>
       <c r="E393" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G393" s="4" t="n">
-        <v>122000</v>
+        <v>233052</v>
       </c>
       <c r="H393" s="3" t="s">
         <v>13</v>
@@ -11515,19 +11522,19 @@
         <v>65</v>
       </c>
       <c r="C394" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D394" s="3" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E394" s="3" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G394" s="4" t="n">
-        <v>233052</v>
+        <v>535511</v>
       </c>
       <c r="H394" s="3" t="s">
         <v>13</v>
@@ -11539,22 +11546,18 @@
         <v>39</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C395" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D395" s="3" t="s">
-        <v>278</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C395" s="3"/>
+      <c r="D395" s="3"/>
       <c r="E395" s="3" t="s">
-        <v>245</v>
+        <v>126</v>
       </c>
       <c r="F395" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G395" s="4" t="n">
-        <v>535511</v>
+        <v>131201</v>
       </c>
       <c r="H395" s="3" t="s">
         <v>13</v>
@@ -11566,18 +11569,20 @@
         <v>39</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C396" s="3"/>
-      <c r="D396" s="3"/>
+      <c r="D396" s="3" t="s">
+        <v>279</v>
+      </c>
       <c r="E396" s="3" t="s">
-        <v>127</v>
+        <v>280</v>
       </c>
       <c r="F396" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G396" s="4" t="n">
-        <v>131201</v>
+        <v>41329</v>
       </c>
       <c r="H396" s="3" t="s">
         <v>13</v>
@@ -11602,7 +11607,7 @@
         <v>12</v>
       </c>
       <c r="G397" s="4" t="n">
-        <v>41329</v>
+        <v>111000</v>
       </c>
       <c r="H397" s="3" t="s">
         <v>13</v>
@@ -11614,20 +11619,22 @@
         <v>39</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C398" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C398" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D398" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="F398" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G398" s="4" t="n">
-        <v>111000</v>
+        <v>183000</v>
       </c>
       <c r="H398" s="3" t="s">
         <v>13</v>
@@ -11642,19 +11649,19 @@
         <v>65</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>281</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="F399" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G399" s="4" t="n">
-        <v>183000</v>
+        <v>274095</v>
       </c>
       <c r="H399" s="3" t="s">
         <v>13</v>
@@ -11669,19 +11676,19 @@
         <v>65</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="F400" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G400" s="4" t="n">
-        <v>274095</v>
+        <v>67482</v>
       </c>
       <c r="H400" s="3" t="s">
         <v>13</v>
@@ -11696,19 +11703,19 @@
         <v>65</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D401" s="3" t="s">
         <v>282</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="F401" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G401" s="4" t="n">
-        <v>67482</v>
+        <v>135896</v>
       </c>
       <c r="H401" s="3" t="s">
         <v>13</v>
@@ -11723,19 +11730,19 @@
         <v>65</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="D402" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E402" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F402" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G402" s="4" t="n">
-        <v>135896</v>
+        <v>172000</v>
       </c>
       <c r="H402" s="3" t="s">
         <v>13</v>
@@ -11750,19 +11757,19 @@
         <v>65</v>
       </c>
       <c r="C403" s="3" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E403" s="3" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="F403" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G403" s="4" t="n">
-        <v>172000</v>
+        <v>216568</v>
       </c>
       <c r="H403" s="3" t="s">
         <v>13</v>
@@ -11777,19 +11784,19 @@
         <v>65</v>
       </c>
       <c r="C404" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E404" s="3" t="s">
-        <v>273</v>
+        <v>243</v>
       </c>
       <c r="F404" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G404" s="4" t="n">
-        <v>216568</v>
+        <v>252000</v>
       </c>
       <c r="H404" s="3" t="s">
         <v>13</v>
@@ -11804,19 +11811,19 @@
         <v>65</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D405" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E405" s="3" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="F405" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G405" s="4" t="n">
-        <v>252000</v>
+        <v>200000</v>
       </c>
       <c r="H405" s="3" t="s">
         <v>13</v>
@@ -11831,19 +11838,19 @@
         <v>65</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D406" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E406" s="3" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="F406" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G406" s="4" t="n">
-        <v>200000</v>
+        <v>307699</v>
       </c>
       <c r="H406" s="3" t="s">
         <v>13</v>
@@ -11858,19 +11865,19 @@
         <v>65</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="D407" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E407" s="3" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="F407" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G407" s="4" t="n">
-        <v>307699</v>
+        <v>70384</v>
       </c>
       <c r="H407" s="3" t="s">
         <v>13</v>
@@ -11885,19 +11892,19 @@
         <v>65</v>
       </c>
       <c r="C408" s="3" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D408" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E408" s="3" t="s">
-        <v>291</v>
+        <v>245</v>
       </c>
       <c r="F408" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G408" s="4" t="n">
-        <v>70384</v>
+        <v>815782</v>
       </c>
       <c r="H408" s="3" t="s">
         <v>13</v>
@@ -11912,19 +11919,19 @@
         <v>65</v>
       </c>
       <c r="C409" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>289</v>
+        <v>151</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F409" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G409" s="4" t="n">
-        <v>815782</v>
+        <v>291772</v>
       </c>
       <c r="H409" s="3" t="s">
         <v>13</v>
@@ -11939,19 +11946,19 @@
         <v>65</v>
       </c>
       <c r="C410" s="3" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>151</v>
+        <v>292</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>251</v>
+        <v>293</v>
       </c>
       <c r="F410" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G410" s="4" t="n">
-        <v>291772</v>
+        <v>103000</v>
       </c>
       <c r="H410" s="3" t="s">
         <v>13</v>
@@ -11966,19 +11973,19 @@
         <v>65</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D411" s="3" t="s">
         <v>292</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>293</v>
+        <v>243</v>
       </c>
       <c r="F411" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G411" s="4" t="n">
-        <v>103000</v>
+        <v>175000</v>
       </c>
       <c r="H411" s="3" t="s">
         <v>13</v>
@@ -11990,22 +11997,18 @@
         <v>39</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C412" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D412" s="3" t="s">
-        <v>292</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C412" s="3"/>
+      <c r="D412" s="3"/>
       <c r="E412" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F412" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G412" s="4" t="n">
-        <v>175000</v>
+        <v>22727</v>
       </c>
       <c r="H412" s="3" t="s">
         <v>13</v>
@@ -12017,18 +12020,22 @@
         <v>39</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C413" s="3"/>
-      <c r="D413" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C413" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D413" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="E413" s="3" t="s">
-        <v>248</v>
+        <v>294</v>
       </c>
       <c r="F413" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G413" s="4" t="n">
-        <v>22727</v>
+        <v>115276</v>
       </c>
       <c r="H413" s="3" t="s">
         <v>13</v>
@@ -12040,22 +12047,18 @@
         <v>39</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C414" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D414" s="3" t="s">
-        <v>217</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C414" s="3"/>
+      <c r="D414" s="3"/>
       <c r="E414" s="3" t="s">
-        <v>294</v>
+        <v>247</v>
       </c>
       <c r="F414" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G414" s="4" t="n">
-        <v>115276</v>
+        <v>15928</v>
       </c>
       <c r="H414" s="3" t="s">
         <v>13</v>
@@ -12067,18 +12070,20 @@
         <v>39</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C415" s="3"/>
-      <c r="D415" s="3"/>
+      <c r="D415" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="E415" s="3" t="s">
-        <v>247</v>
+        <v>280</v>
       </c>
       <c r="F415" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G415" s="4" t="n">
-        <v>15928</v>
+        <v>139920</v>
       </c>
       <c r="H415" s="3" t="s">
         <v>13</v>
@@ -12087,23 +12092,25 @@
     </row>
     <row r="416" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B416" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C416" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C416" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="D416" s="3" t="s">
-        <v>217</v>
+        <v>295</v>
       </c>
       <c r="E416" s="3" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="F416" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G416" s="4" t="n">
-        <v>139920</v>
+        <v>440300</v>
       </c>
       <c r="H416" s="3" t="s">
         <v>13</v>
@@ -12118,19 +12125,19 @@
         <v>65</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F417" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G417" s="4" t="n">
-        <v>440300</v>
+        <v>172000</v>
       </c>
       <c r="H417" s="3" t="s">
         <v>13</v>
@@ -12139,25 +12146,25 @@
     </row>
     <row r="418" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C418" s="3" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="D418" s="3" t="s">
-        <v>297</v>
+        <v>220</v>
       </c>
       <c r="E418" s="3" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="F418" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G418" s="4" t="n">
-        <v>172000</v>
+        <v>65806</v>
       </c>
       <c r="H418" s="3" t="s">
         <v>13</v>
@@ -12175,16 +12182,16 @@
         <v>95</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>220</v>
+        <v>299</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="F419" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G419" s="4" t="n">
-        <v>65806</v>
+        <v>-65860</v>
       </c>
       <c r="H419" s="3" t="s">
         <v>13</v>
@@ -12199,19 +12206,19 @@
         <v>65</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>299</v>
+        <v>134</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F420" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G420" s="4" t="n">
-        <v>-65860</v>
+        <v>305000</v>
       </c>
       <c r="H420" s="3" t="s">
         <v>13</v>
@@ -12223,22 +12230,18 @@
         <v>39</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C421" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D421" s="3" t="s">
-        <v>135</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C421" s="3"/>
+      <c r="D421" s="3"/>
       <c r="E421" s="3" t="s">
-        <v>301</v>
+        <v>34</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G421" s="4" t="n">
-        <v>305000</v>
+        <v>58534</v>
       </c>
       <c r="H421" s="3" t="s">
         <v>13</v>
@@ -12250,18 +12253,22 @@
         <v>39</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C422" s="3"/>
-      <c r="D422" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C422" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D422" s="3" t="s">
+        <v>302</v>
+      </c>
       <c r="E422" s="3" t="s">
-        <v>34</v>
+        <v>291</v>
       </c>
       <c r="F422" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G422" s="4" t="n">
-        <v>58534</v>
+        <v>93993</v>
       </c>
       <c r="H422" s="3" t="s">
         <v>13</v>
@@ -12270,25 +12277,25 @@
     </row>
     <row r="423" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C423" s="3" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D423" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>291</v>
+        <v>245</v>
       </c>
       <c r="F423" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G423" s="4" t="n">
-        <v>93993</v>
+        <v>163150</v>
       </c>
       <c r="H423" s="3" t="s">
         <v>13</v>
@@ -12303,19 +12310,19 @@
         <v>65</v>
       </c>
       <c r="C424" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D424" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>245</v>
+        <v>171</v>
       </c>
       <c r="F424" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G424" s="4" t="n">
-        <v>163150</v>
+        <v>360000</v>
       </c>
       <c r="H424" s="3" t="s">
         <v>13</v>
@@ -12330,19 +12337,19 @@
         <v>65</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D425" s="3" t="s">
         <v>304</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>171</v>
+        <v>294</v>
       </c>
       <c r="F425" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G425" s="4" t="n">
-        <v>360000</v>
+        <v>52150</v>
       </c>
       <c r="H425" s="3" t="s">
         <v>13</v>
@@ -12363,13 +12370,13 @@
         <v>304</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="F426" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G426" s="4" t="n">
-        <v>52150</v>
+        <v>84900</v>
       </c>
       <c r="H426" s="3" t="s">
         <v>13</v>
@@ -12390,13 +12397,13 @@
         <v>304</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F427" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G427" s="4" t="n">
-        <v>84900</v>
+        <v>648804</v>
       </c>
       <c r="H427" s="3" t="s">
         <v>13</v>
@@ -12417,13 +12424,13 @@
         <v>304</v>
       </c>
       <c r="E428" s="3" t="s">
-        <v>306</v>
+        <v>245</v>
       </c>
       <c r="F428" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G428" s="4" t="n">
-        <v>648804</v>
+        <v>781672</v>
       </c>
       <c r="H428" s="3" t="s">
         <v>13</v>
@@ -12435,22 +12442,18 @@
         <v>40</v>
       </c>
       <c r="B429" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C429" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D429" s="3" t="s">
-        <v>304</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C429" s="3"/>
+      <c r="D429" s="3"/>
       <c r="E429" s="3" t="s">
-        <v>245</v>
+        <v>126</v>
       </c>
       <c r="F429" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G429" s="4" t="n">
-        <v>781672</v>
+        <v>132190</v>
       </c>
       <c r="H429" s="3" t="s">
         <v>13</v>
@@ -12462,18 +12465,22 @@
         <v>40</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C430" s="3"/>
-      <c r="D430" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C430" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D430" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="E430" s="3" t="s">
-        <v>127</v>
+        <v>308</v>
       </c>
       <c r="F430" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G430" s="4" t="n">
-        <v>132190</v>
+        <v>140000</v>
       </c>
       <c r="H430" s="3" t="s">
         <v>13</v>
@@ -12494,13 +12501,13 @@
         <v>307</v>
       </c>
       <c r="E431" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F431" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G431" s="4" t="n">
-        <v>140000</v>
+        <v>30000</v>
       </c>
       <c r="H431" s="3" t="s">
         <v>13</v>
@@ -12515,19 +12522,19 @@
         <v>65</v>
       </c>
       <c r="C432" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D432" s="3" t="s">
-        <v>307</v>
+        <v>224</v>
       </c>
       <c r="E432" s="3" t="s">
-        <v>309</v>
+        <v>243</v>
       </c>
       <c r="F432" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G432" s="4" t="n">
-        <v>30000</v>
+        <v>82000</v>
       </c>
       <c r="H432" s="3" t="s">
         <v>13</v>
@@ -12542,19 +12549,19 @@
         <v>65</v>
       </c>
       <c r="C433" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>224</v>
+        <v>310</v>
       </c>
       <c r="E433" s="3" t="s">
-        <v>243</v>
+        <v>301</v>
       </c>
       <c r="F433" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G433" s="4" t="n">
-        <v>82000</v>
+        <v>312133</v>
       </c>
       <c r="H433" s="3" t="s">
         <v>13</v>
@@ -12569,19 +12576,19 @@
         <v>65</v>
       </c>
       <c r="C434" s="3" t="s">
-        <v>94</v>
+        <v>166</v>
       </c>
       <c r="D434" s="3" t="s">
         <v>310</v>
       </c>
       <c r="E434" s="3" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="F434" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G434" s="4" t="n">
-        <v>312133</v>
+        <v>261000</v>
       </c>
       <c r="H434" s="3" t="s">
         <v>13</v>
@@ -12593,22 +12600,20 @@
         <v>40</v>
       </c>
       <c r="B435" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C435" s="3" t="s">
-        <v>166</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C435" s="3"/>
       <c r="D435" s="3" t="s">
-        <v>310</v>
+        <v>225</v>
       </c>
       <c r="E435" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F435" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G435" s="4" t="n">
-        <v>261000</v>
+        <v>2392425</v>
       </c>
       <c r="H435" s="3" t="s">
         <v>13</v>
@@ -12620,20 +12625,22 @@
         <v>40</v>
       </c>
       <c r="B436" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C436" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C436" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D436" s="3" t="s">
-        <v>225</v>
+        <v>313</v>
       </c>
       <c r="E436" s="3" t="s">
-        <v>312</v>
+        <v>243</v>
       </c>
       <c r="F436" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G436" s="4" t="n">
-        <v>2392425</v>
+        <v>143000</v>
       </c>
       <c r="H436" s="3" t="s">
         <v>13</v>
@@ -12648,19 +12655,19 @@
         <v>65</v>
       </c>
       <c r="C437" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="E437" s="3" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="F437" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G437" s="4" t="n">
-        <v>143000</v>
+        <v>364400</v>
       </c>
       <c r="H437" s="3" t="s">
         <v>13</v>
@@ -12681,13 +12688,13 @@
         <v>295</v>
       </c>
       <c r="E438" s="3" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="F438" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G438" s="4" t="n">
-        <v>364400</v>
+        <v>74761</v>
       </c>
       <c r="H438" s="3" t="s">
         <v>13</v>
@@ -12699,22 +12706,18 @@
         <v>40</v>
       </c>
       <c r="B439" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C439" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D439" s="3" t="s">
-        <v>295</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C439" s="3"/>
+      <c r="D439" s="3"/>
       <c r="E439" s="3" t="s">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G439" s="4" t="n">
-        <v>74761</v>
+        <v>22727</v>
       </c>
       <c r="H439" s="3" t="s">
         <v>13</v>
@@ -12726,18 +12729,18 @@
         <v>40</v>
       </c>
       <c r="B440" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C440" s="3"/>
       <c r="D440" s="3"/>
       <c r="E440" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G440" s="4" t="n">
-        <v>22727</v>
+        <v>18773</v>
       </c>
       <c r="H440" s="3" t="s">
         <v>13</v>
@@ -12746,21 +12749,25 @@
     </row>
     <row r="441" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B441" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C441" s="3"/>
-      <c r="D441" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C441" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D441" s="3" t="s">
+        <v>314</v>
+      </c>
       <c r="E441" s="3" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="F441" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G441" s="4" t="n">
-        <v>18773</v>
+        <v>440300</v>
       </c>
       <c r="H441" s="3" t="s">
         <v>13</v>
@@ -12772,22 +12779,20 @@
         <v>41</v>
       </c>
       <c r="B442" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C442" s="3" t="s">
-        <v>74</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C442" s="3"/>
       <c r="D442" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E442" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F442" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G442" s="4" t="n">
-        <v>440300</v>
+        <v>2392425</v>
       </c>
       <c r="H442" s="3" t="s">
         <v>13</v>
@@ -12796,23 +12801,25 @@
     </row>
     <row r="443" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B443" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C443" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C443" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D443" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E443" s="3" t="s">
-        <v>317</v>
+        <v>243</v>
       </c>
       <c r="F443" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G443" s="4" t="n">
-        <v>2392425</v>
+        <v>243000</v>
       </c>
       <c r="H443" s="3" t="s">
         <v>13</v>
@@ -12824,22 +12831,18 @@
         <v>40</v>
       </c>
       <c r="B444" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C444" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D444" s="3" t="s">
-        <v>318</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C444" s="3"/>
+      <c r="D444" s="3"/>
       <c r="E444" s="3" t="s">
-        <v>243</v>
+        <v>34</v>
       </c>
       <c r="F444" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G444" s="4" t="n">
-        <v>243000</v>
+        <v>55994</v>
       </c>
       <c r="H444" s="3" t="s">
         <v>13</v>
@@ -12848,21 +12851,25 @@
     </row>
     <row r="445" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B445" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C445" s="3"/>
-      <c r="D445" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C445" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D445" s="3" t="s">
+        <v>319</v>
+      </c>
       <c r="E445" s="3" t="s">
-        <v>34</v>
+        <v>251</v>
       </c>
       <c r="F445" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G445" s="4" t="n">
-        <v>55994</v>
+        <v>308968</v>
       </c>
       <c r="H445" s="3" t="s">
         <v>13</v>
@@ -12877,19 +12884,19 @@
         <v>65</v>
       </c>
       <c r="C446" s="3" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D446" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E446" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="F446" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G446" s="4" t="n">
-        <v>308968</v>
+        <v>107000</v>
       </c>
       <c r="H446" s="3" t="s">
         <v>13</v>
@@ -12901,22 +12908,20 @@
         <v>41</v>
       </c>
       <c r="B447" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C447" s="3" t="s">
-        <v>66</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C447" s="3"/>
       <c r="D447" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E447" s="3" t="s">
-        <v>243</v>
+        <v>322</v>
       </c>
       <c r="F447" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G447" s="4" t="n">
-        <v>107000</v>
+        <v>50000</v>
       </c>
       <c r="H447" s="3" t="s">
         <v>13</v>
@@ -12928,20 +12933,22 @@
         <v>41</v>
       </c>
       <c r="B448" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C448" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C448" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D448" s="3" t="s">
         <v>321</v>
       </c>
       <c r="E448" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F448" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G448" s="4" t="n">
-        <v>50000</v>
+        <v>435994</v>
       </c>
       <c r="H448" s="3" t="s">
         <v>13</v>
@@ -12953,22 +12960,18 @@
         <v>41</v>
       </c>
       <c r="B449" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C449" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D449" s="3" t="s">
-        <v>321</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C449" s="3"/>
+      <c r="D449" s="3"/>
       <c r="E449" s="3" t="s">
-        <v>323</v>
+        <v>126</v>
       </c>
       <c r="F449" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G449" s="4" t="n">
-        <v>435994</v>
+        <v>121469</v>
       </c>
       <c r="H449" s="3" t="s">
         <v>13</v>
@@ -12980,18 +12983,22 @@
         <v>41</v>
       </c>
       <c r="B450" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C450" s="3"/>
-      <c r="D450" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C450" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D450" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="E450" s="3" t="s">
-        <v>127</v>
+        <v>291</v>
       </c>
       <c r="F450" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G450" s="4" t="n">
-        <v>121469</v>
+        <v>73327</v>
       </c>
       <c r="H450" s="3" t="s">
         <v>13</v>
@@ -13006,19 +13013,19 @@
         <v>65</v>
       </c>
       <c r="C451" s="3" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="D451" s="3" t="s">
-        <v>201</v>
+        <v>324</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="F451" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G451" s="4" t="n">
-        <v>73327</v>
+        <v>214000</v>
       </c>
       <c r="H451" s="3" t="s">
         <v>13</v>
@@ -13033,19 +13040,19 @@
         <v>65</v>
       </c>
       <c r="C452" s="3" t="s">
-        <v>66</v>
+        <v>166</v>
       </c>
       <c r="D452" s="3" t="s">
         <v>324</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>243</v>
+        <v>325</v>
       </c>
       <c r="F452" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G452" s="4" t="n">
-        <v>214000</v>
+        <v>56000</v>
       </c>
       <c r="H452" s="3" t="s">
         <v>13</v>
@@ -13057,22 +13064,20 @@
         <v>41</v>
       </c>
       <c r="B453" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C453" s="3" t="s">
-        <v>166</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C453" s="3"/>
       <c r="D453" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F453" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G453" s="4" t="n">
-        <v>56000</v>
+        <v>425242</v>
       </c>
       <c r="H453" s="3" t="s">
         <v>13</v>
@@ -13088,16 +13093,16 @@
       </c>
       <c r="C454" s="3"/>
       <c r="D454" s="3" t="s">
-        <v>326</v>
+        <v>203</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F454" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G454" s="4" t="n">
-        <v>425242</v>
+        <v>296076</v>
       </c>
       <c r="H454" s="3" t="s">
         <v>13</v>
@@ -13109,20 +13114,22 @@
         <v>41</v>
       </c>
       <c r="B455" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C455" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C455" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="D455" s="3" t="s">
-        <v>203</v>
+        <v>329</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>328</v>
+        <v>245</v>
       </c>
       <c r="F455" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G455" s="4" t="n">
-        <v>296076</v>
+        <v>619681</v>
       </c>
       <c r="H455" s="3" t="s">
         <v>13</v>
@@ -13137,19 +13144,19 @@
         <v>65</v>
       </c>
       <c r="C456" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>245</v>
+        <v>301</v>
       </c>
       <c r="F456" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G456" s="4" t="n">
-        <v>619681</v>
+        <v>295000</v>
       </c>
       <c r="H456" s="3" t="s">
         <v>13</v>
@@ -13164,19 +13171,19 @@
         <v>65</v>
       </c>
       <c r="C457" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D457" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="F457" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G457" s="4" t="n">
-        <v>295000</v>
+        <v>61717</v>
       </c>
       <c r="H457" s="3" t="s">
         <v>13</v>
@@ -13188,22 +13195,20 @@
         <v>41</v>
       </c>
       <c r="B458" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C458" s="3" t="s">
-        <v>95</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C458" s="3"/>
       <c r="D458" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>291</v>
+        <v>333</v>
       </c>
       <c r="F458" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G458" s="4" t="n">
-        <v>61717</v>
+        <v>277650</v>
       </c>
       <c r="H458" s="3" t="s">
         <v>13</v>
@@ -13215,20 +13220,22 @@
         <v>41</v>
       </c>
       <c r="B459" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C459" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C459" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="D459" s="3" t="s">
         <v>332</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F459" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G459" s="4" t="n">
-        <v>277650</v>
+        <v>450185</v>
       </c>
       <c r="H459" s="3" t="s">
         <v>13</v>
@@ -13243,19 +13250,19 @@
         <v>65</v>
       </c>
       <c r="C460" s="3" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="D460" s="3" t="s">
-        <v>332</v>
+        <v>180</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>334</v>
+        <v>243</v>
       </c>
       <c r="F460" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G460" s="4" t="n">
-        <v>450185</v>
+        <v>112000</v>
       </c>
       <c r="H460" s="3" t="s">
         <v>13</v>
@@ -13270,19 +13277,19 @@
         <v>65</v>
       </c>
       <c r="C461" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D461" s="3" t="s">
-        <v>180</v>
+        <v>335</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>243</v>
+        <v>272</v>
       </c>
       <c r="F461" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G461" s="4" t="n">
-        <v>112000</v>
+        <v>332275</v>
       </c>
       <c r="H461" s="3" t="s">
         <v>13</v>
@@ -13294,22 +13301,18 @@
         <v>41</v>
       </c>
       <c r="B462" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C462" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D462" s="3" t="s">
-        <v>335</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="C462" s="3"/>
+      <c r="D462" s="3"/>
       <c r="E462" s="3" t="s">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="F462" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G462" s="4" t="n">
-        <v>332275</v>
+        <v>13525</v>
       </c>
       <c r="H462" s="3" t="s">
         <v>13</v>
@@ -13321,18 +13324,18 @@
         <v>41</v>
       </c>
       <c r="B463" s="3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C463" s="3"/>
       <c r="D463" s="3"/>
       <c r="E463" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G463" s="4" t="n">
-        <v>13525</v>
+        <v>22727</v>
       </c>
       <c r="H463" s="3" t="s">
         <v>13</v>
@@ -13344,18 +13347,22 @@
         <v>41</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C464" s="3"/>
-      <c r="D464" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C464" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D464" s="3" t="s">
+        <v>184</v>
+      </c>
       <c r="E464" s="3" t="s">
-        <v>248</v>
+        <v>336</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G464" s="4" t="n">
-        <v>22727</v>
+        <v>32700</v>
       </c>
       <c r="H464" s="3" t="s">
         <v>13</v>
@@ -13367,22 +13374,18 @@
         <v>41</v>
       </c>
       <c r="B465" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C465" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D465" s="3" t="s">
-        <v>184</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C465" s="3"/>
+      <c r="D465" s="3"/>
       <c r="E465" s="3" t="s">
-        <v>336</v>
+        <v>34</v>
       </c>
       <c r="F465" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G465" s="4" t="n">
-        <v>32700</v>
+        <v>53965</v>
       </c>
       <c r="H465" s="3" t="s">
         <v>13</v>
@@ -13391,24 +13394,28 @@
     </row>
     <row r="466" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B466" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C466" s="3"/>
-      <c r="D466" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C466" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D466" s="3" t="s">
+        <v>337</v>
+      </c>
       <c r="E466" s="3" t="s">
-        <v>34</v>
+        <v>301</v>
       </c>
       <c r="F466" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G466" s="4" t="n">
-        <v>53965</v>
+        <v>280600</v>
       </c>
       <c r="H466" s="3" t="s">
-        <v>13</v>
+        <v>93</v>
       </c>
       <c r="I466" s="3"/>
     </row>
@@ -13420,19 +13427,19 @@
         <v>65</v>
       </c>
       <c r="C467" s="3" t="s">
-        <v>94</v>
+        <v>166</v>
       </c>
       <c r="D467" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E467" s="3" t="s">
-        <v>301</v>
+        <v>339</v>
       </c>
       <c r="F467" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G467" s="4" t="n">
-        <v>280600</v>
+        <v>892735</v>
       </c>
       <c r="H467" s="3" t="s">
         <v>93</v>
@@ -13447,19 +13454,19 @@
         <v>65</v>
       </c>
       <c r="C468" s="3" t="s">
-        <v>166</v>
+        <v>66</v>
       </c>
       <c r="D468" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E468" s="3" t="s">
-        <v>339</v>
+        <v>243</v>
       </c>
       <c r="F468" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G468" s="4" t="n">
-        <v>892735</v>
+        <v>149000</v>
       </c>
       <c r="H468" s="3" t="s">
         <v>93</v>
@@ -13474,19 +13481,19 @@
         <v>65</v>
       </c>
       <c r="C469" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D469" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E469" s="3" t="s">
-        <v>243</v>
+        <v>301</v>
       </c>
       <c r="F469" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G469" s="4" t="n">
-        <v>149000</v>
+        <v>252000</v>
       </c>
       <c r="H469" s="3" t="s">
         <v>93</v>
@@ -13501,19 +13508,19 @@
         <v>65</v>
       </c>
       <c r="C470" s="3" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D470" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E470" s="3" t="s">
-        <v>301</v>
+        <v>243</v>
       </c>
       <c r="F470" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G470" s="4" t="n">
-        <v>252000</v>
+        <v>198000</v>
       </c>
       <c r="H470" s="3" t="s">
         <v>93</v>
@@ -13528,19 +13535,19 @@
         <v>65</v>
       </c>
       <c r="C471" s="3" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D471" s="3" t="s">
-        <v>342</v>
+        <v>167</v>
       </c>
       <c r="E471" s="3" t="s">
-        <v>243</v>
+        <v>343</v>
       </c>
       <c r="F471" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G471" s="4" t="n">
-        <v>198000</v>
+        <v>20000</v>
       </c>
       <c r="H471" s="3" t="s">
         <v>93</v>
@@ -13555,19 +13562,19 @@
         <v>65</v>
       </c>
       <c r="C472" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D472" s="3" t="s">
-        <v>167</v>
+        <v>344</v>
       </c>
       <c r="E472" s="3" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F472" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G472" s="4" t="n">
-        <v>20000</v>
+        <v>65000</v>
       </c>
       <c r="H472" s="3" t="s">
         <v>93</v>
@@ -13582,19 +13589,19 @@
         <v>65</v>
       </c>
       <c r="C473" s="3" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="D473" s="3" t="s">
         <v>344</v>
       </c>
       <c r="E473" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F473" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G473" s="4" t="n">
-        <v>65000</v>
+        <v>267128</v>
       </c>
       <c r="H473" s="3" t="s">
         <v>93</v>
@@ -13609,19 +13616,19 @@
         <v>65</v>
       </c>
       <c r="C474" s="3" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="D474" s="3" t="s">
-        <v>344</v>
+        <v>162</v>
       </c>
       <c r="E474" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F474" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G474" s="4" t="n">
-        <v>267128</v>
+        <v>30000</v>
       </c>
       <c r="H474" s="3" t="s">
         <v>93</v>
@@ -13633,22 +13640,18 @@
         <v>42</v>
       </c>
       <c r="B475" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C475" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D475" s="3" t="s">
-        <v>162</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C475" s="3"/>
+      <c r="D475" s="3"/>
       <c r="E475" s="3" t="s">
-        <v>347</v>
+        <v>248</v>
       </c>
       <c r="F475" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G475" s="4" t="n">
-        <v>30000</v>
+        <v>22727</v>
       </c>
       <c r="H475" s="3" t="s">
         <v>93</v>
@@ -13660,18 +13663,18 @@
         <v>42</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C476" s="3"/>
       <c r="D476" s="3"/>
       <c r="E476" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G476" s="4" t="n">
-        <v>22727</v>
+        <v>4338</v>
       </c>
       <c r="H476" s="3" t="s">
         <v>93</v>
@@ -13683,18 +13686,22 @@
         <v>42</v>
       </c>
       <c r="B477" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C477" s="3"/>
-      <c r="D477" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C477" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D477" s="3" t="s">
+        <v>348</v>
+      </c>
       <c r="E477" s="3" t="s">
-        <v>247</v>
+        <v>349</v>
       </c>
       <c r="F477" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G477" s="4" t="n">
-        <v>4338</v>
+        <v>15165</v>
       </c>
       <c r="H477" s="3" t="s">
         <v>93</v>
@@ -13709,19 +13716,19 @@
         <v>65</v>
       </c>
       <c r="C478" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D478" s="3" t="s">
         <v>348</v>
       </c>
       <c r="E478" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F478" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G478" s="4" t="n">
-        <v>15165</v>
+        <v>513392</v>
       </c>
       <c r="H478" s="3" t="s">
         <v>93</v>
@@ -13736,19 +13743,19 @@
         <v>65</v>
       </c>
       <c r="C479" s="3" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D479" s="3" t="s">
         <v>348</v>
       </c>
       <c r="E479" s="3" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="F479" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G479" s="4" t="n">
-        <v>513392</v>
+        <v>320000</v>
       </c>
       <c r="H479" s="3" t="s">
         <v>93</v>
@@ -13757,25 +13764,25 @@
     </row>
     <row r="480" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B480" s="3" t="s">
         <v>65</v>
       </c>
       <c r="C480" s="3" t="s">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D480" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E480" s="3" t="s">
-        <v>301</v>
+        <v>243</v>
       </c>
       <c r="F480" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G480" s="4" t="n">
-        <v>320000</v>
+        <v>201000</v>
       </c>
       <c r="H480" s="3" t="s">
         <v>93</v>
@@ -13793,7 +13800,7 @@
         <v>66</v>
       </c>
       <c r="D481" s="3" t="s">
-        <v>351</v>
+        <v>158</v>
       </c>
       <c r="E481" s="3" t="s">
         <v>243</v>
@@ -13802,7 +13809,7 @@
         <v>12</v>
       </c>
       <c r="G481" s="4" t="n">
-        <v>201000</v>
+        <v>253000</v>
       </c>
       <c r="H481" s="3" t="s">
         <v>93</v>
@@ -13820,7 +13827,7 @@
         <v>66</v>
       </c>
       <c r="D482" s="3" t="s">
-        <v>158</v>
+        <v>352</v>
       </c>
       <c r="E482" s="3" t="s">
         <v>243</v>
@@ -13829,7 +13836,7 @@
         <v>12</v>
       </c>
       <c r="G482" s="4" t="n">
-        <v>253000</v>
+        <v>198000</v>
       </c>
       <c r="H482" s="3" t="s">
         <v>93</v>
@@ -13847,7 +13854,7 @@
         <v>66</v>
       </c>
       <c r="D483" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E483" s="3" t="s">
         <v>243</v>
@@ -13856,7 +13863,7 @@
         <v>12</v>
       </c>
       <c r="G483" s="4" t="n">
-        <v>198000</v>
+        <v>351000</v>
       </c>
       <c r="H483" s="3" t="s">
         <v>93</v>
@@ -13871,19 +13878,19 @@
         <v>65</v>
       </c>
       <c r="C484" s="3" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="D484" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E484" s="3" t="s">
-        <v>243</v>
+        <v>355</v>
       </c>
       <c r="F484" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G484" s="4" t="n">
-        <v>351000</v>
+        <v>328834</v>
       </c>
       <c r="H484" s="3" t="s">
         <v>93</v>
@@ -13895,22 +13902,18 @@
         <v>32</v>
       </c>
       <c r="B485" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C485" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D485" s="3" t="s">
-        <v>354</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C485" s="3"/>
+      <c r="D485" s="3"/>
       <c r="E485" s="3" t="s">
-        <v>355</v>
+        <v>248</v>
       </c>
       <c r="F485" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G485" s="4" t="n">
-        <v>328834</v>
+        <v>22727</v>
       </c>
       <c r="H485" s="3" t="s">
         <v>93</v>
@@ -13922,18 +13925,18 @@
         <v>32</v>
       </c>
       <c r="B486" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C486" s="3"/>
       <c r="D486" s="3"/>
       <c r="E486" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F486" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G486" s="4" t="n">
-        <v>22727</v>
+        <v>4238</v>
       </c>
       <c r="H486" s="3" t="s">
         <v>93</v>
@@ -13942,24 +13945,28 @@
     </row>
     <row r="487" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="3" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B487" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C487" s="3"/>
-      <c r="D487" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C487" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D487" s="3" t="s">
+        <v>133</v>
+      </c>
       <c r="E487" s="3" t="s">
-        <v>247</v>
+        <v>356</v>
       </c>
       <c r="F487" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G487" s="4" t="n">
-        <v>4238</v>
+        <v>385000</v>
       </c>
       <c r="H487" s="3" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="I487" s="3"/>
     </row>
@@ -13971,19 +13978,19 @@
         <v>65</v>
       </c>
       <c r="C488" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D488" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E488" s="3" t="s">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="F488" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G488" s="4" t="n">
-        <v>385000</v>
+        <v>67000</v>
       </c>
       <c r="H488" s="3" t="s">
         <v>13</v>
@@ -14001,7 +14008,7 @@
         <v>79</v>
       </c>
       <c r="D489" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E489" s="3" t="s">
         <v>79</v>
@@ -14010,7 +14017,7 @@
         <v>12</v>
       </c>
       <c r="G489" s="4" t="n">
-        <v>67000</v>
+        <v>830000</v>
       </c>
       <c r="H489" s="3" t="s">
         <v>13</v>
@@ -14028,16 +14035,16 @@
         <v>79</v>
       </c>
       <c r="D490" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E490" s="3" t="s">
-        <v>79</v>
+        <v>357</v>
       </c>
       <c r="F490" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G490" s="4" t="n">
-        <v>830000</v>
+        <v>-166000</v>
       </c>
       <c r="H490" s="3" t="s">
         <v>13</v>
@@ -14052,19 +14059,19 @@
         <v>65</v>
       </c>
       <c r="C491" s="3" t="s">
-        <v>79</v>
+        <v>166</v>
       </c>
       <c r="D491" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E491" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F491" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G491" s="4" t="n">
-        <v>-166000</v>
+        <v>210000</v>
       </c>
       <c r="H491" s="3" t="s">
         <v>13</v>
@@ -14079,19 +14086,19 @@
         <v>65</v>
       </c>
       <c r="C492" s="3" t="s">
-        <v>166</v>
+        <v>69</v>
       </c>
       <c r="D492" s="3" t="s">
-        <v>134</v>
+        <v>359</v>
       </c>
       <c r="E492" s="3" t="s">
-        <v>358</v>
+        <v>69</v>
       </c>
       <c r="F492" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G492" s="4" t="n">
-        <v>210000</v>
+        <v>308000</v>
       </c>
       <c r="H492" s="3" t="s">
         <v>13</v>
@@ -14106,22 +14113,22 @@
         <v>65</v>
       </c>
       <c r="C493" s="3" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="D493" s="3" t="s">
         <v>359</v>
       </c>
       <c r="E493" s="3" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="F493" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G493" s="4" t="n">
-        <v>308000</v>
+        <v>20000</v>
       </c>
       <c r="H493" s="3" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="I493" s="3"/>
     </row>
@@ -14133,22 +14140,22 @@
         <v>65</v>
       </c>
       <c r="C494" s="3" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="D494" s="3" t="s">
         <v>359</v>
       </c>
       <c r="E494" s="3" t="s">
-        <v>83</v>
+        <v>360</v>
       </c>
       <c r="F494" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G494" s="4" t="n">
-        <v>20000</v>
+        <v>35000</v>
       </c>
       <c r="H494" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I494" s="3"/>
     </row>
@@ -14160,22 +14167,22 @@
         <v>65</v>
       </c>
       <c r="C495" s="3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D495" s="3" t="s">
         <v>359</v>
       </c>
       <c r="E495" s="3" t="s">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="F495" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G495" s="4" t="n">
-        <v>35000</v>
+        <v>120000</v>
       </c>
       <c r="H495" s="3" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="I495" s="3"/>
     </row>
@@ -14187,19 +14194,19 @@
         <v>65</v>
       </c>
       <c r="C496" s="3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D496" s="3" t="s">
         <v>359</v>
       </c>
       <c r="E496" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F496" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G496" s="4" t="n">
-        <v>120000</v>
+        <v>45000</v>
       </c>
       <c r="H496" s="3" t="s">
         <v>25</v>
@@ -14217,19 +14224,19 @@
         <v>74</v>
       </c>
       <c r="D497" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E497" s="3" t="s">
-        <v>76</v>
+        <v>362</v>
       </c>
       <c r="F497" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G497" s="4" t="n">
-        <v>45000</v>
+        <v>22000</v>
       </c>
       <c r="H497" s="3" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I497" s="3"/>
     </row>
@@ -14241,19 +14248,19 @@
         <v>65</v>
       </c>
       <c r="C498" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D498" s="3" t="s">
         <v>361</v>
       </c>
       <c r="E498" s="3" t="s">
-        <v>362</v>
+        <v>66</v>
       </c>
       <c r="F498" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G498" s="4" t="n">
-        <v>22000</v>
+        <v>197000</v>
       </c>
       <c r="H498" s="3" t="s">
         <v>13</v>
@@ -14265,22 +14272,20 @@
         <v>9</v>
       </c>
       <c r="B499" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C499" s="3" t="s">
-        <v>66</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C499" s="3"/>
       <c r="D499" s="3" t="s">
         <v>361</v>
       </c>
       <c r="E499" s="3" t="s">
-        <v>66</v>
+        <v>173</v>
       </c>
       <c r="F499" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G499" s="4" t="n">
-        <v>197000</v>
+        <v>248714</v>
       </c>
       <c r="H499" s="3" t="s">
         <v>13</v>
@@ -14299,16 +14304,16 @@
         <v>361</v>
       </c>
       <c r="E500" s="3" t="s">
-        <v>173</v>
+        <v>363</v>
       </c>
       <c r="F500" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G500" s="4" t="n">
-        <v>248714</v>
+        <v>330000</v>
       </c>
       <c r="H500" s="3" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I500" s="3"/>
     </row>
@@ -14317,23 +14322,25 @@
         <v>9</v>
       </c>
       <c r="B501" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C501" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C501" s="3" t="s">
+        <v>82</v>
+      </c>
       <c r="D501" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E501" s="3" t="s">
-        <v>363</v>
+        <v>83</v>
       </c>
       <c r="F501" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G501" s="4" t="n">
-        <v>330000</v>
+        <v>20000</v>
       </c>
       <c r="H501" s="3" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="I501" s="3"/>
     </row>
@@ -14345,19 +14352,19 @@
         <v>65</v>
       </c>
       <c r="C502" s="3" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D502" s="3" t="s">
         <v>364</v>
       </c>
       <c r="E502" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F502" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G502" s="4" t="n">
-        <v>20000</v>
+        <v>319235</v>
       </c>
       <c r="H502" s="3" t="s">
         <v>93</v>
@@ -14378,13 +14385,13 @@
         <v>364</v>
       </c>
       <c r="E503" s="3" t="s">
-        <v>94</v>
+        <v>365</v>
       </c>
       <c r="F503" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G503" s="4" t="n">
-        <v>319235</v>
+        <v>-18750</v>
       </c>
       <c r="H503" s="3" t="s">
         <v>93</v>
@@ -14396,22 +14403,18 @@
         <v>9</v>
       </c>
       <c r="B504" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C504" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D504" s="3" t="s">
-        <v>364</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C504" s="3"/>
+      <c r="D504" s="3"/>
       <c r="E504" s="3" t="s">
-        <v>365</v>
+        <v>248</v>
       </c>
       <c r="F504" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G504" s="4" t="n">
-        <v>-18750</v>
+        <v>25000</v>
       </c>
       <c r="H504" s="3" t="s">
         <v>93</v>
@@ -14423,18 +14426,18 @@
         <v>9</v>
       </c>
       <c r="B505" s="3" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="C505" s="3"/>
       <c r="D505" s="3"/>
       <c r="E505" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F505" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G505" s="4" t="n">
-        <v>25000</v>
+        <v>4675</v>
       </c>
       <c r="H505" s="3" t="s">
         <v>93</v>
@@ -14446,18 +14449,22 @@
         <v>9</v>
       </c>
       <c r="B506" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C506" s="3"/>
-      <c r="D506" s="3"/>
+        <v>65</v>
+      </c>
+      <c r="C506" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D506" s="3" t="s">
+        <v>364</v>
+      </c>
       <c r="E506" s="3" t="s">
-        <v>247</v>
+        <v>366</v>
       </c>
       <c r="F506" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G506" s="4" t="n">
-        <v>4675</v>
+        <v>159000</v>
       </c>
       <c r="H506" s="3" t="s">
         <v>93</v>
@@ -14472,22 +14479,22 @@
         <v>65</v>
       </c>
       <c r="C507" s="3" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="D507" s="3" t="s">
         <v>364</v>
       </c>
       <c r="E507" s="3" t="s">
-        <v>366</v>
+        <v>79</v>
       </c>
       <c r="F507" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G507" s="4" t="n">
-        <v>159000</v>
+        <v>145600</v>
       </c>
       <c r="H507" s="3" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="I507" s="3"/>
     </row>
@@ -14499,22 +14506,22 @@
         <v>65</v>
       </c>
       <c r="C508" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D508" s="3" t="s">
         <v>364</v>
       </c>
       <c r="E508" s="3" t="s">
-        <v>79</v>
+        <v>360</v>
       </c>
       <c r="F508" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G508" s="4" t="n">
-        <v>145600</v>
+        <v>48500</v>
       </c>
       <c r="H508" s="3" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="I508" s="3"/>
     </row>
@@ -14532,34 +14539,86 @@
         <v>364</v>
       </c>
       <c r="E509" s="3" t="s">
-        <v>360</v>
+        <v>69</v>
       </c>
       <c r="F509" s="3" t="s">
         <v>12</v>
       </c>
       <c r="G509" s="4" t="n">
-        <v>48500</v>
+        <v>66000</v>
       </c>
       <c r="H509" s="3" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="I509" s="3"/>
     </row>
     <row r="510" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A510" s="3"/>
-      <c r="B510" s="3"/>
+      <c r="A510" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B510" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="C510" s="3"/>
-      <c r="D510" s="3"/>
+      <c r="D510" s="3" t="s">
+        <v>361</v>
+      </c>
       <c r="E510" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F510" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G510" s="4" t="n">
+        <v>133540</v>
+      </c>
+      <c r="H510" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I510" s="3"/>
+    </row>
+    <row r="511" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A511" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B511" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C511" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D511" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E511" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="F510" s="3"/>
-      <c r="G510" s="4" t="n">
-        <f aca="false">SUM(G2:G509)</f>
-        <v>175693157</v>
-      </c>
-      <c r="H510" s="3"/>
-      <c r="I510" s="3"/>
+      <c r="F511" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G511" s="4" t="n">
+        <v>59294</v>
+      </c>
+      <c r="H511" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I511" s="3"/>
+    </row>
+    <row r="512" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A512" s="3"/>
+      <c r="B512" s="3"/>
+      <c r="C512" s="3"/>
+      <c r="D512" s="3"/>
+      <c r="E512" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="F512" s="3"/>
+      <c r="G512" s="4" t="n">
+        <f aca="false">SUM(G2:G511)</f>
+        <v>175139464</v>
+      </c>
+      <c r="H512" s="3"/>
+      <c r="I512" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -14585,7 +14644,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14593,32 +14652,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14626,32 +14685,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14659,27 +14718,27 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14687,22 +14746,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14710,17 +14769,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -14748,7 +14807,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14798,153 +14857,153 @@
         <v>60</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$F$2:$F$509,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$F$2:$F$511,"Fijo")</f>
         <v>3247828</v>
       </c>
       <c r="C4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$F$2:$F$509,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$F$2:$F$511,"Fijo")</f>
         <v>5318465</v>
       </c>
       <c r="D4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$F$2:$F$509,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$F$2:$F$511,"Fijo")</f>
         <v>5936170</v>
       </c>
       <c r="E4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$F$2:$F$509,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$F$2:$F$511,"Fijo")</f>
         <v>5876788</v>
       </c>
       <c r="F4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$F$2:$F$509,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$F$2:$F$511,"Fijo")</f>
         <v>6035363</v>
       </c>
       <c r="G4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$F$2:$F$509,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$F$2:$F$511,"Fijo")</f>
         <v>5949233</v>
       </c>
       <c r="H4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$F$2:$F$509,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$F$2:$F$511,"Fijo")</f>
         <v>6977171</v>
       </c>
       <c r="I4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$F$2:$F$509,"Fijo")</f>
-        <v>8822758</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$F$2:$F$511,"Fijo")</f>
+        <v>8010231</v>
       </c>
       <c r="J4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$F$2:$F$509,"Fijo")</f>
-        <v>6459977</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$F$2:$F$511,"Fijo")</f>
+        <v>6593517</v>
       </c>
       <c r="K4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$F$2:$F$509,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$F$2:$F$511,"Fijo")</f>
         <v>5665877</v>
       </c>
       <c r="L4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$F$2:$F$509,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$F$2:$F$511,"Fijo")</f>
         <v>5665877</v>
       </c>
       <c r="M4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$F$2:$F$509,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$F$2:$F$511,"Fijo")</f>
         <v>3320877</v>
       </c>
       <c r="N4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$F$2:$F$509,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$F$2:$F$511,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="O4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$F$2:$F$509,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$F$2:$F$511,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="P4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$F$2:$F$509,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$F$2:$F$511,"Fijo")</f>
         <v>0</v>
       </c>
       <c r="Q4" s="10" t="n">
         <f aca="false">SUM(B4:P4)</f>
-        <v>70288248</v>
+        <v>69609261</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$F$2:$F$511,"Variable")</f>
         <v>6304755</v>
       </c>
       <c r="C5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$F$2:$F$511,"Variable")</f>
         <v>9626002</v>
       </c>
       <c r="D5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$F$2:$F$511,"Variable")</f>
         <v>8177007</v>
       </c>
       <c r="E5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$F$2:$F$511,"Variable")</f>
         <v>9970945</v>
       </c>
       <c r="F5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$F$2:$F$511,"Variable")</f>
         <v>10299475</v>
       </c>
       <c r="G5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$F$2:$F$511,"Variable")</f>
         <v>30893365</v>
       </c>
       <c r="H5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$F$2:$F$511,"Variable")</f>
         <v>6757280</v>
       </c>
       <c r="I5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$F$2:$F$509,"Variable")</f>
-        <v>19216080</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$F$2:$F$511,"Variable")</f>
+        <v>19341374</v>
       </c>
       <c r="J5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$F$2:$F$511,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="K5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$F$2:$F$511,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="L5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$F$2:$F$511,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="M5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$F$2:$F$511,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="N5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$F$2:$F$511,"Variable")</f>
         <v>0</v>
       </c>
       <c r="O5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$F$2:$F$511,"Variable")</f>
         <v>0</v>
       </c>
       <c r="P5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$F$2:$F$509,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$F$2:$F$511,"Variable")</f>
         <v>0</v>
       </c>
       <c r="Q5" s="10" t="n">
         <f aca="false">SUM(B5:P5)</f>
-        <v>105404909</v>
+        <v>105530203</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">B4+B5</f>
@@ -14976,11 +15035,11 @@
       </c>
       <c r="I6" s="9" t="n">
         <f aca="false">I4+I5</f>
-        <v>28038838</v>
+        <v>27351605</v>
       </c>
       <c r="J6" s="9" t="n">
         <f aca="false">J4+J5</f>
-        <v>7499977</v>
+        <v>7633517</v>
       </c>
       <c r="K6" s="9" t="n">
         <f aca="false">K4+K5</f>
@@ -15008,12 +15067,12 @@
       </c>
       <c r="Q6" s="10" t="n">
         <f aca="false">Q4+Q5</f>
-        <v>175693157</v>
+        <v>175139464</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15021,63 +15080,63 @@
         <v>10</v>
       </c>
       <c r="B9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>286542</v>
       </c>
       <c r="C9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>883152</v>
       </c>
       <c r="D9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>1048593</v>
       </c>
       <c r="E9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>783677</v>
       </c>
       <c r="F9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>826352</v>
       </c>
       <c r="G9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>624134</v>
       </c>
       <c r="H9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>633304</v>
       </c>
       <c r="I9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>680440</v>
       </c>
       <c r="J9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="K9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="L9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="M9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="N9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="O9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="Q9" s="9" t="n">
@@ -15090,63 +15149,63 @@
         <v>16</v>
       </c>
       <c r="B10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="E10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="F10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="G10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>262000</v>
       </c>
       <c r="H10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="I10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="J10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="K10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="L10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="M10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="N10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="O10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="P10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="9" t="n">
@@ -15159,63 +15218,63 @@
         <v>19</v>
       </c>
       <c r="B11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Educación")</f>
         <v>0</v>
       </c>
       <c r="C11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Educación")</f>
         <v>2345000</v>
       </c>
       <c r="D11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="E11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="F11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="G11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="H11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="I11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="J11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="K11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="L11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="M11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Educación")</f>
         <v>1040000</v>
       </c>
       <c r="N11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Educación")</f>
         <v>0</v>
       </c>
       <c r="O11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Educación")</f>
         <v>0</v>
       </c>
       <c r="P11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Educación")</f>
         <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
@@ -15228,63 +15287,63 @@
         <v>21</v>
       </c>
       <c r="B12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="C12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="D12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Salud")</f>
         <v>1548449</v>
       </c>
       <c r="E12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="F12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Salud")</f>
         <v>1306200</v>
       </c>
       <c r="G12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="H12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="I12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Salud")</f>
         <v>1834914</v>
       </c>
       <c r="J12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="K12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="L12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="M12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="N12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Salud")</f>
         <v>0</v>
       </c>
       <c r="O12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Salud")</f>
         <v>0</v>
       </c>
       <c r="P12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Salud")</f>
         <v>0</v>
       </c>
       <c r="Q12" s="9" t="n">
@@ -15297,63 +15356,63 @@
         <v>27</v>
       </c>
       <c r="B13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>1057700</v>
       </c>
       <c r="C13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>710897</v>
       </c>
       <c r="D13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>708661</v>
       </c>
       <c r="E13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>730525</v>
       </c>
       <c r="F13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>728410</v>
       </c>
       <c r="G13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>1086789</v>
       </c>
       <c r="H13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>814937</v>
       </c>
       <c r="I13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>770510</v>
       </c>
       <c r="J13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="K13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="L13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="M13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="N13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="O13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="P13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="Q13" s="9" t="n">
@@ -15366,68 +15425,68 @@
         <v>29</v>
       </c>
       <c r="B14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>456901</v>
       </c>
       <c r="C14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>335538</v>
       </c>
       <c r="D14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>450311</v>
       </c>
       <c r="E14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>390929</v>
       </c>
       <c r="F14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>549504</v>
       </c>
       <c r="G14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>461374</v>
       </c>
       <c r="H14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>620062</v>
       </c>
       <c r="I14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>451349</v>
       </c>
       <c r="J14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <v>336285</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>202745</v>
       </c>
-      <c r="K14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Suscripciones")</f>
+      <c r="L14" s="9" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>202745</v>
       </c>
-      <c r="L14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Suscripciones")</f>
+      <c r="M14" s="9" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>202745</v>
       </c>
-      <c r="M14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Suscripciones")</f>
-        <v>202745</v>
-      </c>
       <c r="N14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="O14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="P14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="Q14" s="9" t="n">
         <f aca="false">SUM(B14:P14)</f>
-        <v>4526948</v>
+        <v>4660488</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15435,68 +15494,68 @@
         <v>47</v>
       </c>
       <c r="B15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="C15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="D15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="E15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>470932</v>
       </c>
       <c r="F15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="G15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="H15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>1507182</v>
       </c>
       <c r="I15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Compras adicionales")</f>
-        <v>3131099</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <v>2318572</v>
       </c>
       <c r="J15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>1300032</v>
       </c>
       <c r="K15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="L15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="M15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="N15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="O15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="P15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="Q15" s="9" t="n">
         <f aca="false">SUM(B15:P15)</f>
-        <v>10456701</v>
+        <v>9644174</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15504,68 +15563,68 @@
         <v>65</v>
       </c>
       <c r="B16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>5861720</v>
       </c>
       <c r="C16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>8780160</v>
       </c>
       <c r="D16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>5832711</v>
       </c>
       <c r="E16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>6178045</v>
       </c>
       <c r="F16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>5382047</v>
       </c>
       <c r="G16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>5089768</v>
       </c>
       <c r="H16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>5387766</v>
       </c>
       <c r="I16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Día a día")</f>
-        <v>17267416</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Día a día")</f>
+        <v>17392710</v>
       </c>
       <c r="J16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="K16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="M16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="N16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="O16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="P16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="Q16" s="9" t="n">
         <f aca="false">SUM(B16:P16)</f>
-        <v>59779633</v>
+        <v>59904927</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15573,63 +15632,63 @@
         <v>109</v>
       </c>
       <c r="B17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="C17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="F17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="G17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="I17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"IPS")</f>
         <v>388110</v>
       </c>
       <c r="J17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="K17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="M17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="N17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="O17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-02",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="P17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-03",Gastos!$B$2:$B$509,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"IPS")</f>
         <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
@@ -15642,55 +15701,55 @@
         <v>160</v>
       </c>
       <c r="B18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-01",Gastos!$B$2:$B$509,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="C18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-02",Gastos!$B$2:$B$509,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="D18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-03",Gastos!$B$2:$B$509,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="E18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-04",Gastos!$B$2:$B$509,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Viajes")</f>
         <v>2392425</v>
       </c>
       <c r="F18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-05",Gastos!$B$2:$B$509,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Viajes")</f>
         <v>3391393</v>
       </c>
       <c r="G18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-06",Gastos!$B$2:$B$509,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Viajes")</f>
         <v>24171401</v>
       </c>
       <c r="H18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-07",Gastos!$B$2:$B$509,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-08",Gastos!$B$2:$B$509,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-09",Gastos!$B$2:$B$509,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="K18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-10",Gastos!$B$2:$B$509,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-11",Gastos!$B$2:$B$509,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="M18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2026-12",Gastos!$B$2:$B$509,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="N18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$509,Gastos!$A$2:$A$509,"2027-01",Gastos!$B$2:$B$509,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Viajes")</f>
         <v>0</v>
       </c>
     </row>

--- a/Gastos_Mensuales.xlsx
+++ b/Gastos_Mensuales.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3201" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3216" uniqueCount="401">
   <si>
     <t xml:space="preserve">Mes</t>
   </si>
@@ -1664,7 +1664,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I512"/>
+  <dimension ref="A1:I515"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -14605,20 +14605,89 @@
       <c r="I511" s="3"/>
     </row>
     <row r="512" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A512" s="3"/>
-      <c r="B512" s="3"/>
+      <c r="A512" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B512" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="C512" s="3"/>
       <c r="D512" s="3"/>
       <c r="E512" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F512" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G512" s="4" t="n">
+        <v>130000</v>
+      </c>
+      <c r="H512" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I512" s="3"/>
+    </row>
+    <row r="513" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A513" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B513" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C513" s="3"/>
+      <c r="D513" s="3"/>
+      <c r="E513" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F513" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G513" s="4" t="n">
+        <v>53174</v>
+      </c>
+      <c r="H513" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I513" s="3"/>
+    </row>
+    <row r="514" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A514" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B514" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C514" s="3"/>
+      <c r="D514" s="3"/>
+      <c r="E514" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F514" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G514" s="4" t="n">
+        <v>134420</v>
+      </c>
+      <c r="H514" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I514" s="3"/>
+    </row>
+    <row r="515" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A515" s="3"/>
+      <c r="B515" s="3"/>
+      <c r="C515" s="3"/>
+      <c r="D515" s="3"/>
+      <c r="E515" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="F512" s="3"/>
-      <c r="G512" s="4" t="n">
-        <f aca="false">SUM(G2:G511)</f>
-        <v>175139464</v>
-      </c>
-      <c r="H512" s="3"/>
-      <c r="I512" s="3"/>
+      <c r="F515" s="3"/>
+      <c r="G515" s="4" t="n">
+        <f aca="false">SUM(G2:G514)</f>
+        <v>175457058</v>
+      </c>
+      <c r="H515" s="3"/>
+      <c r="I515" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -14868,68 +14937,68 @@
         <v>397</v>
       </c>
       <c r="B4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-01",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>3247828</v>
       </c>
       <c r="C4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-02",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>5318465</v>
       </c>
       <c r="D4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-03",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>5936170</v>
       </c>
       <c r="E4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-04",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>5876788</v>
       </c>
       <c r="F4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-05",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>6035363</v>
       </c>
       <c r="G4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-06",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>5949233</v>
       </c>
       <c r="H4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-07",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>6977171</v>
       </c>
       <c r="I4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$F$2:$F$511,"Fijo")</f>
-        <v>8010231</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-08",Gastos!$F$2:$F$514,"Fijo")</f>
+        <v>8327825</v>
       </c>
       <c r="J4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-09",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>6593517</v>
       </c>
       <c r="K4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-10",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>5665877</v>
       </c>
       <c r="L4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-11",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>5665877</v>
       </c>
       <c r="M4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-12",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>3320877</v>
       </c>
       <c r="N4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-01",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="O4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-02",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="P4" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$F$2:$F$511,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-03",Gastos!$F$2:$F$514,"Fijo")</f>
         <v>0</v>
       </c>
       <c r="Q4" s="10" t="n">
         <f aca="false">SUM(B4:P4)</f>
-        <v>69609261</v>
+        <v>69926855</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14937,63 +15006,63 @@
         <v>398</v>
       </c>
       <c r="B5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-01",Gastos!$F$2:$F$514,"Variable")</f>
         <v>6304755</v>
       </c>
       <c r="C5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-02",Gastos!$F$2:$F$514,"Variable")</f>
         <v>9626002</v>
       </c>
       <c r="D5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-03",Gastos!$F$2:$F$514,"Variable")</f>
         <v>8177007</v>
       </c>
       <c r="E5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-04",Gastos!$F$2:$F$514,"Variable")</f>
         <v>9970945</v>
       </c>
       <c r="F5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-05",Gastos!$F$2:$F$514,"Variable")</f>
         <v>10299475</v>
       </c>
       <c r="G5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-06",Gastos!$F$2:$F$514,"Variable")</f>
         <v>30893365</v>
       </c>
       <c r="H5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-07",Gastos!$F$2:$F$514,"Variable")</f>
         <v>6757280</v>
       </c>
       <c r="I5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-08",Gastos!$F$2:$F$514,"Variable")</f>
         <v>19341374</v>
       </c>
       <c r="J5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-09",Gastos!$F$2:$F$514,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="K5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-10",Gastos!$F$2:$F$514,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="L5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-11",Gastos!$F$2:$F$514,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="M5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-12",Gastos!$F$2:$F$514,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="N5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-01",Gastos!$F$2:$F$514,"Variable")</f>
         <v>0</v>
       </c>
       <c r="O5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-02",Gastos!$F$2:$F$514,"Variable")</f>
         <v>0</v>
       </c>
       <c r="P5" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$F$2:$F$511,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-03",Gastos!$F$2:$F$514,"Variable")</f>
         <v>0</v>
       </c>
       <c r="Q5" s="10" t="n">
@@ -15035,7 +15104,7 @@
       </c>
       <c r="I6" s="9" t="n">
         <f aca="false">I4+I5</f>
-        <v>27351605</v>
+        <v>27669199</v>
       </c>
       <c r="J6" s="9" t="n">
         <f aca="false">J4+J5</f>
@@ -15067,7 +15136,7 @@
       </c>
       <c r="Q6" s="10" t="n">
         <f aca="false">Q4+Q5</f>
-        <v>175139464</v>
+        <v>175457058</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15080,63 +15149,63 @@
         <v>10</v>
       </c>
       <c r="B9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-01",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>286542</v>
       </c>
       <c r="C9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-02",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>883152</v>
       </c>
       <c r="D9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-03",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>1048593</v>
       </c>
       <c r="E9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-04",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>783677</v>
       </c>
       <c r="F9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-05",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>826352</v>
       </c>
       <c r="G9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-06",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>624134</v>
       </c>
       <c r="H9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-07",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>633304</v>
       </c>
       <c r="I9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-08",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>680440</v>
       </c>
       <c r="J9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-09",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="K9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-10",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="L9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-11",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="M9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-12",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="N9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-01",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="O9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-02",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="P9" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-03",Gastos!$B$2:$B$514,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="Q9" s="9" t="n">
@@ -15149,68 +15218,68 @@
         <v>16</v>
       </c>
       <c r="B10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-01",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="C10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-02",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-03",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="E10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-04",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="F10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-05",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="G10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-06",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>262000</v>
       </c>
       <c r="H10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-07",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="I10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
-        <v>130000</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-08",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
+        <v>260000</v>
       </c>
       <c r="J10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-09",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="K10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-10",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="L10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-11",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="M10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-12",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="N10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-01",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="O10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-02",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="P10" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-03",Gastos!$B$2:$B$514,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="9" t="n">
         <f aca="false">SUM(B10:P10)</f>
-        <v>2862000</v>
+        <v>2992000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15218,63 +15287,63 @@
         <v>19</v>
       </c>
       <c r="B11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-01",Gastos!$B$2:$B$514,"Educación")</f>
         <v>0</v>
       </c>
       <c r="C11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-02",Gastos!$B$2:$B$514,"Educación")</f>
         <v>2345000</v>
       </c>
       <c r="D11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-03",Gastos!$B$2:$B$514,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="E11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-04",Gastos!$B$2:$B$514,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="F11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-05",Gastos!$B$2:$B$514,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="G11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-06",Gastos!$B$2:$B$514,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="H11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-07",Gastos!$B$2:$B$514,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="I11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-08",Gastos!$B$2:$B$514,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="J11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-09",Gastos!$B$2:$B$514,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="K11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-10",Gastos!$B$2:$B$514,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="L11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-11",Gastos!$B$2:$B$514,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="M11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-12",Gastos!$B$2:$B$514,"Educación")</f>
         <v>1040000</v>
       </c>
       <c r="N11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-01",Gastos!$B$2:$B$514,"Educación")</f>
         <v>0</v>
       </c>
       <c r="O11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-02",Gastos!$B$2:$B$514,"Educación")</f>
         <v>0</v>
       </c>
       <c r="P11" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-03",Gastos!$B$2:$B$514,"Educación")</f>
         <v>0</v>
       </c>
       <c r="Q11" s="9" t="n">
@@ -15287,63 +15356,63 @@
         <v>21</v>
       </c>
       <c r="B12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-01",Gastos!$B$2:$B$514,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="C12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-02",Gastos!$B$2:$B$514,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="D12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-03",Gastos!$B$2:$B$514,"Salud")</f>
         <v>1548449</v>
       </c>
       <c r="E12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-04",Gastos!$B$2:$B$514,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="F12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-05",Gastos!$B$2:$B$514,"Salud")</f>
         <v>1306200</v>
       </c>
       <c r="G12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-06",Gastos!$B$2:$B$514,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="H12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-07",Gastos!$B$2:$B$514,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="I12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-08",Gastos!$B$2:$B$514,"Salud")</f>
         <v>1834914</v>
       </c>
       <c r="J12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-09",Gastos!$B$2:$B$514,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="K12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-10",Gastos!$B$2:$B$514,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="L12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-11",Gastos!$B$2:$B$514,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="M12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-12",Gastos!$B$2:$B$514,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="N12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-01",Gastos!$B$2:$B$514,"Salud")</f>
         <v>0</v>
       </c>
       <c r="O12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-02",Gastos!$B$2:$B$514,"Salud")</f>
         <v>0</v>
       </c>
       <c r="P12" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-03",Gastos!$B$2:$B$514,"Salud")</f>
         <v>0</v>
       </c>
       <c r="Q12" s="9" t="n">
@@ -15356,63 +15425,63 @@
         <v>27</v>
       </c>
       <c r="B13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-01",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>1057700</v>
       </c>
       <c r="C13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-02",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>710897</v>
       </c>
       <c r="D13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-03",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>708661</v>
       </c>
       <c r="E13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-04",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>730525</v>
       </c>
       <c r="F13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-05",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>728410</v>
       </c>
       <c r="G13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-06",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>1086789</v>
       </c>
       <c r="H13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-07",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>814937</v>
       </c>
       <c r="I13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-08",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>770510</v>
       </c>
       <c r="J13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-09",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="K13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-10",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="L13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-11",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="M13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-12",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="N13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-01",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="O13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-02",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="P13" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-03",Gastos!$B$2:$B$514,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="Q13" s="9" t="n">
@@ -15425,68 +15494,68 @@
         <v>29</v>
       </c>
       <c r="B14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-01",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>456901</v>
       </c>
       <c r="C14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-02",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>335538</v>
       </c>
       <c r="D14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-03",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>450311</v>
       </c>
       <c r="E14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-04",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>390929</v>
       </c>
       <c r="F14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-05",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>549504</v>
       </c>
       <c r="G14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-06",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>461374</v>
       </c>
       <c r="H14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-07",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>620062</v>
       </c>
       <c r="I14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Suscripciones")</f>
-        <v>451349</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-08",Gastos!$B$2:$B$514,"Suscripciones")</f>
+        <v>638943</v>
       </c>
       <c r="J14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-09",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>336285</v>
       </c>
       <c r="K14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-10",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="L14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-11",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="M14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-12",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="N14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-01",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="O14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-02",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="P14" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-03",Gastos!$B$2:$B$514,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="Q14" s="9" t="n">
         <f aca="false">SUM(B14:P14)</f>
-        <v>4660488</v>
+        <v>4848082</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15494,63 +15563,63 @@
         <v>47</v>
       </c>
       <c r="B15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-01",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="C15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-02",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="D15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-03",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="E15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-04",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>470932</v>
       </c>
       <c r="F15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-05",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="G15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-06",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="H15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-07",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>1507182</v>
       </c>
       <c r="I15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-08",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>2318572</v>
       </c>
       <c r="J15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-09",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>1300032</v>
       </c>
       <c r="K15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-10",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="L15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-11",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="M15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-12",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="N15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-01",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="O15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-02",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="P15" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-03",Gastos!$B$2:$B$514,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="Q15" s="9" t="n">
@@ -15563,63 +15632,63 @@
         <v>65</v>
       </c>
       <c r="B16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-01",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>5861720</v>
       </c>
       <c r="C16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-02",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>8780160</v>
       </c>
       <c r="D16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-03",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>5832711</v>
       </c>
       <c r="E16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-04",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>6178045</v>
       </c>
       <c r="F16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-05",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>5382047</v>
       </c>
       <c r="G16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-06",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>5089768</v>
       </c>
       <c r="H16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-07",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>5387766</v>
       </c>
       <c r="I16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-08",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>17392710</v>
       </c>
       <c r="J16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-09",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="K16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-10",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-11",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="M16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-12",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="N16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-01",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="O16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-02",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="P16" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-03",Gastos!$B$2:$B$514,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="Q16" s="9" t="n">
@@ -15632,63 +15701,63 @@
         <v>109</v>
       </c>
       <c r="B17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-01",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="C17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-02",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-03",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-04",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="F17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-05",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="G17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-06",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-07",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="I17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-08",Gastos!$B$2:$B$514,"IPS")</f>
         <v>388110</v>
       </c>
       <c r="J17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-09",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="K17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-10",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-11",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="M17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-12",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="N17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-01",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="O17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-02",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-02",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="P17" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-03",Gastos!$B$2:$B$511,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-03",Gastos!$B$2:$B$514,"IPS")</f>
         <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
@@ -15701,55 +15770,55 @@
         <v>160</v>
       </c>
       <c r="B18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-01",Gastos!$B$2:$B$511,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-01",Gastos!$B$2:$B$514,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="C18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-02",Gastos!$B$2:$B$511,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-02",Gastos!$B$2:$B$514,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="D18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-03",Gastos!$B$2:$B$511,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-03",Gastos!$B$2:$B$514,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="E18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-04",Gastos!$B$2:$B$511,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-04",Gastos!$B$2:$B$514,"Viajes")</f>
         <v>2392425</v>
       </c>
       <c r="F18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-05",Gastos!$B$2:$B$511,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-05",Gastos!$B$2:$B$514,"Viajes")</f>
         <v>3391393</v>
       </c>
       <c r="G18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-06",Gastos!$B$2:$B$511,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-06",Gastos!$B$2:$B$514,"Viajes")</f>
         <v>24171401</v>
       </c>
       <c r="H18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-07",Gastos!$B$2:$B$511,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-07",Gastos!$B$2:$B$514,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-08",Gastos!$B$2:$B$511,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-08",Gastos!$B$2:$B$514,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-09",Gastos!$B$2:$B$511,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-09",Gastos!$B$2:$B$514,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="K18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-10",Gastos!$B$2:$B$511,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-10",Gastos!$B$2:$B$514,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-11",Gastos!$B$2:$B$511,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-11",Gastos!$B$2:$B$514,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="M18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2026-12",Gastos!$B$2:$B$511,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2026-12",Gastos!$B$2:$B$514,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="N18" s="9" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$511,Gastos!$A$2:$A$511,"2027-01",Gastos!$B$2:$B$511,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$514,Gastos!$A$2:$A$514,"2027-01",Gastos!$B$2:$B$514,"Viajes")</f>
         <v>0</v>
       </c>
     </row>

--- a/Gastos_Mensuales.xlsx
+++ b/Gastos_Mensuales.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3238" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3257" uniqueCount="408">
   <si>
     <t xml:space="preserve">Mes</t>
   </si>
@@ -2878,7 +2878,7 @@
         <v>18</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>130000</v>
+        <v>140000</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>13</v>
@@ -4404,7 +4404,7 @@
         <v>697200</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4424,7 +4424,7 @@
         <v>330000</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>65</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13788,17 +13788,86 @@
       </c>
     </row>
     <row r="516" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A516" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B516" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C516" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D516" s="1" t="s">
+        <v>371</v>
+      </c>
       <c r="E516" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F516" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G516" s="1" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H516" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="517" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A517" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C517" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D517" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="E517" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F517" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G517" s="1" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H517" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="518" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A518" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B518" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E518" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F518" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G518" s="1" t="n">
+        <v>262140</v>
+      </c>
+      <c r="H518" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="519" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E519" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="G516" s="1" t="n">
-        <f aca="false">SUM(G2:G515)</f>
-        <v>176023603</v>
-      </c>
-    </row>
-    <row r="517" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="518" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="519" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="G519" s="1" t="n">
+        <f aca="false">SUM(G2:G518)</f>
+        <v>176440743</v>
+      </c>
+    </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
@@ -14049,68 +14118,68 @@
         <v>404</v>
       </c>
       <c r="B4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-01",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>3133982</v>
       </c>
       <c r="C4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-02",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>5264720</v>
       </c>
       <c r="D4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-03",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>5882425</v>
       </c>
       <c r="E4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-04",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>5823043</v>
       </c>
       <c r="F4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-05",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>5981618</v>
       </c>
       <c r="G4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-06",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>5949233</v>
       </c>
       <c r="H4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-07",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>6977171</v>
       </c>
       <c r="I4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-08",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>7634299</v>
       </c>
       <c r="J4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-09",Gastos!$F$2:$F$515,"Fijo")</f>
-        <v>7153214</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$F$2:$F$518,"Fijo")</f>
+        <v>7163214</v>
       </c>
       <c r="K4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-10",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>5665877</v>
       </c>
       <c r="L4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-11",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>5665877</v>
       </c>
       <c r="M4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-12",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>3320877</v>
       </c>
       <c r="N4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-01",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="O4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-02",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="P4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-03",Gastos!$F$2:$F$515,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$F$2:$F$518,"Fijo")</f>
         <v>0</v>
       </c>
       <c r="Q4" s="8" t="n">
         <f aca="false">SUM(B4:P4)</f>
-        <v>69464200</v>
+        <v>69474200</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14118,68 +14187,68 @@
         <v>405</v>
       </c>
       <c r="B5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-01",Gastos!$F$2:$F$515,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$F$2:$F$518,"Variable")</f>
         <v>6304755</v>
       </c>
       <c r="C5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-02",Gastos!$F$2:$F$515,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$F$2:$F$518,"Variable")</f>
         <v>9626002</v>
       </c>
       <c r="D5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-03",Gastos!$F$2:$F$515,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$F$2:$F$518,"Variable")</f>
         <v>8177007</v>
       </c>
       <c r="E5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-04",Gastos!$F$2:$F$515,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$F$2:$F$518,"Variable")</f>
         <v>9970945</v>
       </c>
       <c r="F5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-05",Gastos!$F$2:$F$515,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$F$2:$F$518,"Variable")</f>
         <v>10299475</v>
       </c>
       <c r="G5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-06",Gastos!$F$2:$F$515,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$F$2:$F$518,"Variable")</f>
         <v>30893365</v>
       </c>
       <c r="H5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-07",Gastos!$F$2:$F$515,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$F$2:$F$518,"Variable")</f>
         <v>6757280</v>
       </c>
       <c r="I5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-08",Gastos!$F$2:$F$515,"Variable")</f>
-        <v>20370574</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$F$2:$F$518,"Variable")</f>
+        <v>20515574</v>
       </c>
       <c r="J5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-09",Gastos!$F$2:$F$515,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$F$2:$F$518,"Variable")</f>
+        <v>1302140</v>
+      </c>
+      <c r="K5" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$F$2:$F$518,"Variable")</f>
         <v>1040000</v>
       </c>
-      <c r="K5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-10",Gastos!$F$2:$F$515,"Variable")</f>
+      <c r="L5" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$F$2:$F$518,"Variable")</f>
         <v>1040000</v>
       </c>
-      <c r="L5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-11",Gastos!$F$2:$F$515,"Variable")</f>
+      <c r="M5" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$F$2:$F$518,"Variable")</f>
         <v>1040000</v>
       </c>
-      <c r="M5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-12",Gastos!$F$2:$F$515,"Variable")</f>
-        <v>1040000</v>
-      </c>
       <c r="N5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-01",Gastos!$F$2:$F$515,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$F$2:$F$518,"Variable")</f>
         <v>0</v>
       </c>
       <c r="O5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-02",Gastos!$F$2:$F$515,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$F$2:$F$518,"Variable")</f>
         <v>0</v>
       </c>
       <c r="P5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-03",Gastos!$F$2:$F$515,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$F$2:$F$518,"Variable")</f>
         <v>0</v>
       </c>
       <c r="Q5" s="8" t="n">
         <f aca="false">SUM(B5:P5)</f>
-        <v>106559403</v>
+        <v>106966543</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14216,11 +14285,11 @@
       </c>
       <c r="I6" s="7" t="n">
         <f aca="false">I4+I5</f>
-        <v>28004873</v>
+        <v>28149873</v>
       </c>
       <c r="J6" s="7" t="n">
         <f aca="false">J4+J5</f>
-        <v>8193214</v>
+        <v>8465354</v>
       </c>
       <c r="K6" s="7" t="n">
         <f aca="false">K4+K5</f>
@@ -14248,7 +14317,7 @@
       </c>
       <c r="Q6" s="8" t="n">
         <f aca="false">Q4+Q5</f>
-        <v>176023603</v>
+        <v>176440743</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14261,68 +14330,68 @@
         <v>10</v>
       </c>
       <c r="B9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-01",Gastos!$B$2:$B$515,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>286542</v>
       </c>
       <c r="C9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-02",Gastos!$B$2:$B$515,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>883152</v>
       </c>
       <c r="D9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-03",Gastos!$B$2:$B$515,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>1048593</v>
       </c>
       <c r="E9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-04",Gastos!$B$2:$B$515,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>783677</v>
       </c>
       <c r="F9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-05",Gastos!$B$2:$B$515,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>826352</v>
       </c>
       <c r="G9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-06",Gastos!$B$2:$B$515,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>624134</v>
       </c>
       <c r="H9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-07",Gastos!$B$2:$B$515,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>633304</v>
       </c>
       <c r="I9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-08",Gastos!$B$2:$B$515,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>680440</v>
       </c>
       <c r="J9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-09",Gastos!$B$2:$B$515,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Servicios")</f>
+        <v>672140</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>410000</v>
       </c>
-      <c r="K9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-10",Gastos!$B$2:$B$515,"Servicios")</f>
+      <c r="L9" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>410000</v>
       </c>
-      <c r="L9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-11",Gastos!$B$2:$B$515,"Servicios")</f>
+      <c r="M9" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>410000</v>
       </c>
-      <c r="M9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-12",Gastos!$B$2:$B$515,"Servicios")</f>
-        <v>410000</v>
-      </c>
       <c r="N9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-01",Gastos!$B$2:$B$515,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="O9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-02",Gastos!$B$2:$B$515,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="P9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-03",Gastos!$B$2:$B$515,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="Q9" s="7" t="n">
         <f aca="false">SUM(B9:P9)</f>
-        <v>7406194</v>
+        <v>7668334</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14330,68 +14399,68 @@
         <v>16</v>
       </c>
       <c r="B10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-01",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="C10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-02",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="D10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-03",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="E10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-04",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="F10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-05",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="G10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-06",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>262000</v>
       </c>
       <c r="H10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-07",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="I10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-08",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="J10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-09",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <v>270000</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
-      <c r="K10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-10",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+      <c r="L10" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
-      <c r="L10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-11",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+      <c r="M10" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
-      <c r="M10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-12",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
-        <v>260000</v>
-      </c>
       <c r="N10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-01",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="O10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-02",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="P10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-03",Gastos!$B$2:$B$515,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="7" t="n">
         <f aca="false">SUM(B10:P10)</f>
-        <v>2992000</v>
+        <v>3002000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14399,63 +14468,63 @@
         <v>19</v>
       </c>
       <c r="B11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-01",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Educación")</f>
         <v>0</v>
       </c>
       <c r="C11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-02",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Educación")</f>
         <v>2345000</v>
       </c>
       <c r="D11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-03",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="E11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-04",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="F11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-05",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="G11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-06",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="H11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-07",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="I11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-08",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="J11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-09",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="K11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-10",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="L11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-11",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="M11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-12",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Educación")</f>
         <v>1040000</v>
       </c>
       <c r="N11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-01",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Educación")</f>
         <v>0</v>
       </c>
       <c r="O11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-02",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Educación")</f>
         <v>0</v>
       </c>
       <c r="P11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-03",Gastos!$B$2:$B$515,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Educación")</f>
         <v>0</v>
       </c>
       <c r="Q11" s="7" t="n">
@@ -14468,63 +14537,63 @@
         <v>21</v>
       </c>
       <c r="B12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-01",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-02",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="D12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-03",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Salud")</f>
         <v>1548449</v>
       </c>
       <c r="E12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-04",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="F12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-05",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Salud")</f>
         <v>1306200</v>
       </c>
       <c r="G12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-06",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="H12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-07",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="I12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-08",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Salud")</f>
         <v>1834914</v>
       </c>
       <c r="J12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-09",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="K12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-10",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="L12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-11",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="M12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-12",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="N12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-01",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Salud")</f>
         <v>0</v>
       </c>
       <c r="O12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-02",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Salud")</f>
         <v>0</v>
       </c>
       <c r="P12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-03",Gastos!$B$2:$B$515,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Salud")</f>
         <v>0</v>
       </c>
       <c r="Q12" s="7" t="n">
@@ -14537,63 +14606,63 @@
         <v>27</v>
       </c>
       <c r="B13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-01",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>1057700</v>
       </c>
       <c r="C13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-02",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>710897</v>
       </c>
       <c r="D13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-03",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>708661</v>
       </c>
       <c r="E13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-04",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>730525</v>
       </c>
       <c r="F13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-05",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>728410</v>
       </c>
       <c r="G13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-06",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>1086789</v>
       </c>
       <c r="H13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-07",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>814937</v>
       </c>
       <c r="I13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-08",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>770510</v>
       </c>
       <c r="J13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-09",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="K13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-10",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="L13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-11",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="M13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-12",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="N13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-01",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="O13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-02",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="P13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-03",Gastos!$B$2:$B$515,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="Q13" s="7" t="n">
@@ -14606,63 +14675,63 @@
         <v>29</v>
       </c>
       <c r="B14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-01",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>343055</v>
       </c>
       <c r="C14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-02",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>281793</v>
       </c>
       <c r="D14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-03",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>396566</v>
       </c>
       <c r="E14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-04",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>337184</v>
       </c>
       <c r="F14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-05",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>495759</v>
       </c>
       <c r="G14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-06",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>461374</v>
       </c>
       <c r="H14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-07",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>620062</v>
       </c>
       <c r="I14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-08",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>825549</v>
       </c>
       <c r="J14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-09",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>390050</v>
       </c>
       <c r="K14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-10",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="L14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-11",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="M14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-12",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>202745</v>
       </c>
       <c r="N14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-01",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="O14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-02",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="P14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-03",Gastos!$B$2:$B$515,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="Q14" s="7" t="n">
@@ -14675,63 +14744,63 @@
         <v>47</v>
       </c>
       <c r="B15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-01",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="C15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-02",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-03",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="E15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-04",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>470932</v>
       </c>
       <c r="F15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-05",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="G15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-06",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="H15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-07",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>1507182</v>
       </c>
       <c r="I15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-08",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>1812640</v>
       </c>
       <c r="J15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-09",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>1805964</v>
       </c>
       <c r="K15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-10",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="L15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-11",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="M15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-12",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="N15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-01",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="O15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-02",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="P15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-03",Gastos!$B$2:$B$515,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="Q15" s="7" t="n">
@@ -14744,68 +14813,68 @@
         <v>66</v>
       </c>
       <c r="B16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-01",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>5861720</v>
       </c>
       <c r="C16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-02",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>8780160</v>
       </c>
       <c r="D16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-03",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>5832711</v>
       </c>
       <c r="E16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-04",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>6178045</v>
       </c>
       <c r="F16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-05",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>5382047</v>
       </c>
       <c r="G16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-06",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>5089768</v>
       </c>
       <c r="H16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-07",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>5387766</v>
       </c>
       <c r="I16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-08",Gastos!$B$2:$B$515,"Día a día")</f>
-        <v>18047710</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Día a día")</f>
+        <v>18192710</v>
       </c>
       <c r="J16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-09",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="K16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-10",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="L16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-11",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="M16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-12",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="N16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-01",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="O16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-02",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="P16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-03",Gastos!$B$2:$B$515,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="Q16" s="7" t="n">
         <f aca="false">SUM(B16:P16)</f>
-        <v>60559927</v>
+        <v>60704927</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14813,63 +14882,63 @@
         <v>110</v>
       </c>
       <c r="B17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-01",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="C17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-02",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-03",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-04",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-05",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-06",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="H17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-07",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-08",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"IPS")</f>
         <v>388110</v>
       </c>
       <c r="J17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-09",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="K17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-10",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="L17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-11",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="M17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-12",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="N17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-01",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="O17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-02",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="P17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-03",Gastos!$B$2:$B$515,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"IPS")</f>
         <v>0</v>
       </c>
       <c r="Q17" s="7" t="n">
@@ -14882,55 +14951,55 @@
         <v>161</v>
       </c>
       <c r="B18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-01",Gastos!$B$2:$B$515,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="C18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-02",Gastos!$B$2:$B$515,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="D18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-03",Gastos!$B$2:$B$515,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="E18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-04",Gastos!$B$2:$B$515,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Viajes")</f>
         <v>2392425</v>
       </c>
       <c r="F18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-05",Gastos!$B$2:$B$515,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Viajes")</f>
         <v>3391393</v>
       </c>
       <c r="G18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-06",Gastos!$B$2:$B$515,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Viajes")</f>
         <v>24171401</v>
       </c>
       <c r="H18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-07",Gastos!$B$2:$B$515,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="I18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-08",Gastos!$B$2:$B$515,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="J18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-09",Gastos!$B$2:$B$515,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="K18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-10",Gastos!$B$2:$B$515,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="L18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-11",Gastos!$B$2:$B$515,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="M18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2026-12",Gastos!$B$2:$B$515,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="N18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$515,Gastos!$A$2:$A$515,"2027-01",Gastos!$B$2:$B$515,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Viajes")</f>
         <v>0</v>
       </c>
     </row>

--- a/Gastos_Mensuales.xlsx
+++ b/Gastos_Mensuales.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3257" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3263" uniqueCount="409">
   <si>
     <t xml:space="preserve">Mes</t>
   </si>
@@ -417,7 +417,7 @@
     <t xml:space="preserve">2026-08-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Max Dominios (gestión web marca)</t>
+    <t xml:space="preserve">GTM Paraguay (gestión web marca)</t>
   </si>
   <si>
     <t xml:space="preserve">Transferencia (personal)</t>
@@ -1147,6 +1147,9 @@
   </si>
   <si>
     <t xml:space="preserve">Asado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -2938,7 +2941,7 @@
         <v>18</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>149000</v>
+        <v>0</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>31</v>
@@ -3058,7 +3061,7 @@
         <v>18</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>149000</v>
+        <v>0</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>31</v>
@@ -3178,7 +3181,7 @@
         <v>18</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>149000</v>
+        <v>0</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>31</v>
@@ -3298,7 +3301,7 @@
         <v>18</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>149000</v>
+        <v>0</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>31</v>
@@ -4701,7 +4704,7 @@
         <v>18</v>
       </c>
       <c r="G151" s="1" t="n">
-        <v>53745</v>
+        <v>0</v>
       </c>
       <c r="H151" s="1" t="s">
         <v>13</v>
@@ -4721,7 +4724,7 @@
         <v>18</v>
       </c>
       <c r="G152" s="1" t="n">
-        <v>53745</v>
+        <v>0</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>13</v>
@@ -4741,7 +4744,7 @@
         <v>18</v>
       </c>
       <c r="G153" s="1" t="n">
-        <v>53745</v>
+        <v>0</v>
       </c>
       <c r="H153" s="1" t="s">
         <v>13</v>
@@ -4761,7 +4764,7 @@
         <v>18</v>
       </c>
       <c r="G154" s="1" t="n">
-        <v>53745</v>
+        <v>0</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>13</v>
@@ -13507,7 +13510,7 @@
         <v>18</v>
       </c>
       <c r="G504" s="1" t="n">
-        <v>133540</v>
+        <v>0</v>
       </c>
       <c r="H504" s="1" t="s">
         <v>13</v>
@@ -13714,25 +13717,28 @@
     </row>
     <row r="513" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="1" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>29</v>
+        <v>66</v>
+      </c>
+      <c r="C513" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>53</v>
+        <v>371</v>
       </c>
       <c r="E513" s="1" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F513" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G513" s="1" t="n">
-        <v>53765</v>
+        <v>45000</v>
       </c>
       <c r="H513" s="1" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
     </row>
     <row r="514" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13743,22 +13749,22 @@
         <v>66</v>
       </c>
       <c r="C514" s="1" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="D514" s="1" t="s">
         <v>371</v>
       </c>
       <c r="E514" s="1" t="s">
-        <v>77</v>
+        <v>374</v>
       </c>
       <c r="F514" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G514" s="1" t="n">
-        <v>45000</v>
+        <v>75000</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
     </row>
     <row r="515" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13769,19 +13775,19 @@
         <v>66</v>
       </c>
       <c r="C515" s="1" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D515" s="1" t="s">
         <v>371</v>
       </c>
       <c r="E515" s="1" t="s">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="F515" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G515" s="1" t="n">
-        <v>75000</v>
+        <v>120000</v>
       </c>
       <c r="H515" s="1" t="s">
         <v>25</v>
@@ -13795,48 +13801,42 @@
         <v>66</v>
       </c>
       <c r="C516" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D516" s="1" t="s">
         <v>371</v>
       </c>
       <c r="E516" s="1" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F516" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G516" s="1" t="n">
-        <v>120000</v>
+        <v>25000</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>25</v>
+        <v>132</v>
       </c>
     </row>
     <row r="517" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B517" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C517" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D517" s="1" t="s">
-        <v>371</v>
+        <v>10</v>
       </c>
       <c r="E517" s="1" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="F517" s="1" t="s">
         <v>12</v>
       </c>
       <c r="G517" s="1" t="n">
-        <v>25000</v>
+        <v>262140</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
     </row>
     <row r="518" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13844,31 +13844,56 @@
         <v>43</v>
       </c>
       <c r="B518" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="E518" s="1" t="s">
-        <v>11</v>
+        <v>131</v>
       </c>
       <c r="F518" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G518" s="1" t="n">
-        <v>262140</v>
+        <v>0</v>
       </c>
       <c r="H518" s="1" t="s">
-        <v>13</v>
+        <v>132</v>
       </c>
     </row>
     <row r="519" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A519" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B519" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C519" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D519" s="1" t="s">
+        <v>375</v>
+      </c>
       <c r="E519" s="1" t="s">
-        <v>375</v>
+        <v>78</v>
+      </c>
+      <c r="F519" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G519" s="1" t="n">
-        <f aca="false">SUM(G2:G518)</f>
-        <v>176440743</v>
-      </c>
-    </row>
-    <row r="520" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+        <v>120000</v>
+      </c>
+      <c r="H519" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="520" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E520" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="G520" s="1" t="n">
+        <f aca="false">SUM(G2:G519)</f>
+        <v>175562458</v>
+      </c>
+    </row>
     <row r="521" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -13894,7 +13919,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13902,32 +13927,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13935,32 +13960,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13968,27 +13993,27 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13996,22 +14021,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14019,17 +14044,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
   </sheetData>
@@ -14057,7 +14082,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14107,153 +14132,153 @@
         <v>61</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$F$2:$F$518,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$F$2:$F$519,"Fijo")</f>
         <v>3133982</v>
       </c>
       <c r="C4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$F$2:$F$518,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$F$2:$F$519,"Fijo")</f>
         <v>5264720</v>
       </c>
       <c r="D4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$F$2:$F$518,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$F$2:$F$519,"Fijo")</f>
         <v>5882425</v>
       </c>
       <c r="E4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$F$2:$F$518,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$F$2:$F$519,"Fijo")</f>
         <v>5823043</v>
       </c>
       <c r="F4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$F$2:$F$518,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$F$2:$F$519,"Fijo")</f>
         <v>5981618</v>
       </c>
       <c r="G4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$F$2:$F$518,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$F$2:$F$519,"Fijo")</f>
         <v>5949233</v>
       </c>
       <c r="H4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$F$2:$F$518,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$F$2:$F$519,"Fijo")</f>
         <v>6977171</v>
       </c>
       <c r="I4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$F$2:$F$518,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$F$2:$F$519,"Fijo")</f>
         <v>7634299</v>
       </c>
       <c r="J4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$F$2:$F$518,"Fijo")</f>
-        <v>7163214</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$F$2:$F$519,"Fijo")</f>
+        <v>6773164</v>
       </c>
       <c r="K4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$F$2:$F$518,"Fijo")</f>
-        <v>5665877</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$F$2:$F$519,"Fijo")</f>
+        <v>5463132</v>
       </c>
       <c r="L4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$F$2:$F$518,"Fijo")</f>
-        <v>5665877</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$F$2:$F$519,"Fijo")</f>
+        <v>5463132</v>
       </c>
       <c r="M4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$F$2:$F$518,"Fijo")</f>
-        <v>3320877</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$F$2:$F$519,"Fijo")</f>
+        <v>3118132</v>
       </c>
       <c r="N4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$F$2:$F$518,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$F$2:$F$519,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="O4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$F$2:$F$518,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$F$2:$F$519,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="P4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$F$2:$F$518,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$F$2:$F$519,"Fijo")</f>
         <v>0</v>
       </c>
       <c r="Q4" s="8" t="n">
         <f aca="false">SUM(B4:P4)</f>
-        <v>69474200</v>
+        <v>68475915</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$F$2:$F$519,"Variable")</f>
         <v>6304755</v>
       </c>
       <c r="C5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$F$2:$F$519,"Variable")</f>
         <v>9626002</v>
       </c>
       <c r="D5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$F$2:$F$519,"Variable")</f>
         <v>8177007</v>
       </c>
       <c r="E5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$F$2:$F$519,"Variable")</f>
         <v>9970945</v>
       </c>
       <c r="F5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$F$2:$F$519,"Variable")</f>
         <v>10299475</v>
       </c>
       <c r="G5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$F$2:$F$519,"Variable")</f>
         <v>30893365</v>
       </c>
       <c r="H5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$F$2:$F$519,"Variable")</f>
         <v>6757280</v>
       </c>
       <c r="I5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$F$2:$F$519,"Variable")</f>
         <v>20515574</v>
       </c>
       <c r="J5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$F$2:$F$518,"Variable")</f>
-        <v>1302140</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$F$2:$F$519,"Variable")</f>
+        <v>1422140</v>
       </c>
       <c r="K5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$F$2:$F$519,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="L5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$F$2:$F$519,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="M5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$F$2:$F$519,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="N5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$F$2:$F$519,"Variable")</f>
         <v>0</v>
       </c>
       <c r="O5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$F$2:$F$519,"Variable")</f>
         <v>0</v>
       </c>
       <c r="P5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$F$2:$F$518,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$F$2:$F$519,"Variable")</f>
         <v>0</v>
       </c>
       <c r="Q5" s="8" t="n">
         <f aca="false">SUM(B5:P5)</f>
-        <v>106966543</v>
+        <v>107086543</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">B4+B5</f>
@@ -14289,19 +14314,19 @@
       </c>
       <c r="J6" s="7" t="n">
         <f aca="false">J4+J5</f>
-        <v>8465354</v>
+        <v>8195304</v>
       </c>
       <c r="K6" s="7" t="n">
         <f aca="false">K4+K5</f>
-        <v>6705877</v>
+        <v>6503132</v>
       </c>
       <c r="L6" s="7" t="n">
         <f aca="false">L4+L5</f>
-        <v>6705877</v>
+        <v>6503132</v>
       </c>
       <c r="M6" s="7" t="n">
         <f aca="false">M4+M5</f>
-        <v>4360877</v>
+        <v>4158132</v>
       </c>
       <c r="N6" s="7" t="n">
         <f aca="false">N4+N5</f>
@@ -14317,12 +14342,12 @@
       </c>
       <c r="Q6" s="8" t="n">
         <f aca="false">Q4+Q5</f>
-        <v>176440743</v>
+        <v>175562458</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14330,63 +14355,63 @@
         <v>10</v>
       </c>
       <c r="B9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>286542</v>
       </c>
       <c r="C9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>883152</v>
       </c>
       <c r="D9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>1048593</v>
       </c>
       <c r="E9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>783677</v>
       </c>
       <c r="F9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>826352</v>
       </c>
       <c r="G9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>624134</v>
       </c>
       <c r="H9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>633304</v>
       </c>
       <c r="I9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>680440</v>
       </c>
       <c r="J9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>672140</v>
       </c>
       <c r="K9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="L9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="M9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="N9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="O9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="P9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="Q9" s="7" t="n">
@@ -14399,63 +14424,63 @@
         <v>16</v>
       </c>
       <c r="B10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="C10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="D10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="E10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="F10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="G10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>262000</v>
       </c>
       <c r="H10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="I10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="J10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>270000</v>
       </c>
       <c r="K10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="L10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="M10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="N10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="O10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="P10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="7" t="n">
@@ -14468,63 +14493,63 @@
         <v>19</v>
       </c>
       <c r="B11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Educación")</f>
         <v>0</v>
       </c>
       <c r="C11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Educación")</f>
         <v>2345000</v>
       </c>
       <c r="D11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="E11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="F11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="G11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="H11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="I11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="J11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="K11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="L11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="M11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Educación")</f>
         <v>1040000</v>
       </c>
       <c r="N11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Educación")</f>
         <v>0</v>
       </c>
       <c r="O11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Educación")</f>
         <v>0</v>
       </c>
       <c r="P11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Educación")</f>
         <v>0</v>
       </c>
       <c r="Q11" s="7" t="n">
@@ -14537,63 +14562,63 @@
         <v>21</v>
       </c>
       <c r="B12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="D12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Salud")</f>
         <v>1548449</v>
       </c>
       <c r="E12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="F12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Salud")</f>
         <v>1306200</v>
       </c>
       <c r="G12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="H12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="I12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Salud")</f>
         <v>1834914</v>
       </c>
       <c r="J12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="K12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="L12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="M12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="N12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Salud")</f>
         <v>0</v>
       </c>
       <c r="O12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Salud")</f>
         <v>0</v>
       </c>
       <c r="P12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Salud")</f>
         <v>0</v>
       </c>
       <c r="Q12" s="7" t="n">
@@ -14606,63 +14631,63 @@
         <v>27</v>
       </c>
       <c r="B13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>1057700</v>
       </c>
       <c r="C13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>710897</v>
       </c>
       <c r="D13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>708661</v>
       </c>
       <c r="E13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>730525</v>
       </c>
       <c r="F13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>728410</v>
       </c>
       <c r="G13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>1086789</v>
       </c>
       <c r="H13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>814937</v>
       </c>
       <c r="I13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>770510</v>
       </c>
       <c r="J13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="K13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="L13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="M13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="N13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="O13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="P13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="Q13" s="7" t="n">
@@ -14675,68 +14700,68 @@
         <v>29</v>
       </c>
       <c r="B14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Suscripciones")</f>
         <v>343055</v>
       </c>
       <c r="C14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Suscripciones")</f>
         <v>281793</v>
       </c>
       <c r="D14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Suscripciones")</f>
         <v>396566</v>
       </c>
       <c r="E14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Suscripciones")</f>
         <v>337184</v>
       </c>
       <c r="F14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Suscripciones")</f>
         <v>495759</v>
       </c>
       <c r="G14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Suscripciones")</f>
         <v>461374</v>
       </c>
       <c r="H14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Suscripciones")</f>
         <v>620062</v>
       </c>
       <c r="I14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Suscripciones")</f>
         <v>825549</v>
       </c>
       <c r="J14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Suscripciones")</f>
-        <v>390050</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <v>0</v>
       </c>
       <c r="K14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Suscripciones")</f>
-        <v>202745</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <v>0</v>
       </c>
       <c r="L14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Suscripciones")</f>
-        <v>202745</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <v>0</v>
       </c>
       <c r="M14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Suscripciones")</f>
-        <v>202745</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <v>0</v>
       </c>
       <c r="N14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="O14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="P14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="Q14" s="7" t="n">
         <f aca="false">SUM(B14:P14)</f>
-        <v>4759627</v>
+        <v>3761342</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14744,63 +14769,63 @@
         <v>47</v>
       </c>
       <c r="B15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="C15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="E15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>470932</v>
       </c>
       <c r="F15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="G15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="H15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>1507182</v>
       </c>
       <c r="I15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>1812640</v>
       </c>
       <c r="J15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>1805964</v>
       </c>
       <c r="K15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="L15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="M15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="N15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="O15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="P15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="Q15" s="7" t="n">
@@ -14813,68 +14838,68 @@
         <v>66</v>
       </c>
       <c r="B16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>5861720</v>
       </c>
       <c r="C16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>8780160</v>
       </c>
       <c r="D16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>5832711</v>
       </c>
       <c r="E16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>6178045</v>
       </c>
       <c r="F16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>5382047</v>
       </c>
       <c r="G16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>5089768</v>
       </c>
       <c r="H16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>5387766</v>
       </c>
       <c r="I16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>18192710</v>
       </c>
       <c r="J16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Día a día")</f>
+        <v>120000</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>0</v>
       </c>
-      <c r="K16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Día a día")</f>
+      <c r="L16" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>0</v>
       </c>
-      <c r="L16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Día a día")</f>
+      <c r="M16" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>0</v>
       </c>
-      <c r="M16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Día a día")</f>
+      <c r="N16" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>0</v>
       </c>
-      <c r="N16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Día a día")</f>
+      <c r="O16" s="7" t="n">
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>0</v>
       </c>
-      <c r="O16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"Día a día")</f>
-        <v>0</v>
-      </c>
       <c r="P16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="Q16" s="7" t="n">
         <f aca="false">SUM(B16:P16)</f>
-        <v>60704927</v>
+        <v>60824927</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14882,63 +14907,63 @@
         <v>110</v>
       </c>
       <c r="B17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="C17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="H17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"IPS")</f>
         <v>388110</v>
       </c>
       <c r="J17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="K17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="L17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="M17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="N17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="O17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-02",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="P17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-03",Gastos!$B$2:$B$518,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"IPS")</f>
         <v>0</v>
       </c>
       <c r="Q17" s="7" t="n">
@@ -14951,55 +14976,55 @@
         <v>161</v>
       </c>
       <c r="B18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-01",Gastos!$B$2:$B$518,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="C18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-02",Gastos!$B$2:$B$518,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="D18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-03",Gastos!$B$2:$B$518,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="E18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-04",Gastos!$B$2:$B$518,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Viajes")</f>
         <v>2392425</v>
       </c>
       <c r="F18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-05",Gastos!$B$2:$B$518,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Viajes")</f>
         <v>3391393</v>
       </c>
       <c r="G18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-06",Gastos!$B$2:$B$518,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Viajes")</f>
         <v>24171401</v>
       </c>
       <c r="H18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-07",Gastos!$B$2:$B$518,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="I18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-08",Gastos!$B$2:$B$518,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="J18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-09",Gastos!$B$2:$B$518,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="K18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-10",Gastos!$B$2:$B$518,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="L18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-11",Gastos!$B$2:$B$518,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="M18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2026-12",Gastos!$B$2:$B$518,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="N18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$518,Gastos!$A$2:$A$518,"2027-01",Gastos!$B$2:$B$518,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Viajes")</f>
         <v>0</v>
       </c>
     </row>

--- a/Gastos_Mensuales.xlsx
+++ b/Gastos_Mensuales.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3263" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3277" uniqueCount="410">
   <si>
     <t xml:space="preserve">Mes</t>
   </si>
@@ -1150,6 +1150,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oficina</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -1665,7 +1668,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I521"/>
+  <dimension ref="A1:I522"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -13886,15 +13889,66 @@
       </c>
     </row>
     <row r="520" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A520" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C520" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D520" s="1" t="s">
+        <v>375</v>
+      </c>
       <c r="E520" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F520" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G520" s="1" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H520" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="521" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A521" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B521" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C521" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="G520" s="1" t="n">
-        <f aca="false">SUM(G2:G519)</f>
-        <v>175562458</v>
-      </c>
-    </row>
-    <row r="521" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="D521" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E521" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F521" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G521" s="1" t="n">
+        <v>32400</v>
+      </c>
+      <c r="H521" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E522" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G522" s="1" t="n">
+        <f aca="false">SUM(G2:G521)</f>
+        <v>175604858</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13919,7 +13973,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13927,32 +13981,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13960,32 +14014,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13993,27 +14047,27 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14021,22 +14075,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14044,17 +14098,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -14082,7 +14136,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14132,74 +14186,74 @@
         <v>61</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>3133982</v>
       </c>
       <c r="C4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>5264720</v>
       </c>
       <c r="D4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>5882425</v>
       </c>
       <c r="E4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>5823043</v>
       </c>
       <c r="F4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>5981618</v>
       </c>
       <c r="G4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>5949233</v>
       </c>
       <c r="H4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>6977171</v>
       </c>
       <c r="I4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>7634299</v>
       </c>
       <c r="J4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>6773164</v>
       </c>
       <c r="K4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>5463132</v>
       </c>
       <c r="L4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>5463132</v>
       </c>
       <c r="M4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>3118132</v>
       </c>
       <c r="N4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="O4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="P4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$F$2:$F$519,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$F$2:$F$521,"Fijo")</f>
         <v>0</v>
       </c>
       <c r="Q4" s="8" t="n">
@@ -14209,76 +14263,76 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$F$2:$F$521,"Variable")</f>
         <v>6304755</v>
       </c>
       <c r="C5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$F$2:$F$521,"Variable")</f>
         <v>9626002</v>
       </c>
       <c r="D5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$F$2:$F$521,"Variable")</f>
         <v>8177007</v>
       </c>
       <c r="E5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$F$2:$F$521,"Variable")</f>
         <v>9970945</v>
       </c>
       <c r="F5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$F$2:$F$521,"Variable")</f>
         <v>10299475</v>
       </c>
       <c r="G5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$F$2:$F$521,"Variable")</f>
         <v>30893365</v>
       </c>
       <c r="H5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$F$2:$F$521,"Variable")</f>
         <v>6757280</v>
       </c>
       <c r="I5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$F$2:$F$521,"Variable")</f>
         <v>20515574</v>
       </c>
       <c r="J5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$F$2:$F$519,"Variable")</f>
-        <v>1422140</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$F$2:$F$521,"Variable")</f>
+        <v>1464540</v>
       </c>
       <c r="K5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$F$2:$F$521,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="L5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$F$2:$F$521,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="M5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$F$2:$F$521,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="N5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$F$2:$F$521,"Variable")</f>
         <v>0</v>
       </c>
       <c r="O5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$F$2:$F$521,"Variable")</f>
         <v>0</v>
       </c>
       <c r="P5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$F$2:$F$519,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$F$2:$F$521,"Variable")</f>
         <v>0</v>
       </c>
       <c r="Q5" s="8" t="n">
         <f aca="false">SUM(B5:P5)</f>
-        <v>107086543</v>
+        <v>107128943</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">B4+B5</f>
@@ -14314,7 +14368,7 @@
       </c>
       <c r="J6" s="7" t="n">
         <f aca="false">J4+J5</f>
-        <v>8195304</v>
+        <v>8237704</v>
       </c>
       <c r="K6" s="7" t="n">
         <f aca="false">K4+K5</f>
@@ -14342,12 +14396,12 @@
       </c>
       <c r="Q6" s="8" t="n">
         <f aca="false">Q4+Q5</f>
-        <v>175562458</v>
+        <v>175604858</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14355,63 +14409,63 @@
         <v>10</v>
       </c>
       <c r="B9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>286542</v>
       </c>
       <c r="C9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>883152</v>
       </c>
       <c r="D9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>1048593</v>
       </c>
       <c r="E9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>783677</v>
       </c>
       <c r="F9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>826352</v>
       </c>
       <c r="G9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>624134</v>
       </c>
       <c r="H9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>633304</v>
       </c>
       <c r="I9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>680440</v>
       </c>
       <c r="J9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>672140</v>
       </c>
       <c r="K9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="L9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="M9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="N9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="O9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="P9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="Q9" s="7" t="n">
@@ -14424,63 +14478,63 @@
         <v>16</v>
       </c>
       <c r="B10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="C10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="D10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="E10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="F10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="G10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>262000</v>
       </c>
       <c r="H10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="I10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="J10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>270000</v>
       </c>
       <c r="K10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="L10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="M10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="N10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="O10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="P10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="7" t="n">
@@ -14493,63 +14547,63 @@
         <v>19</v>
       </c>
       <c r="B11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Educación")</f>
         <v>0</v>
       </c>
       <c r="C11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Educación")</f>
         <v>2345000</v>
       </c>
       <c r="D11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="E11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="F11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="G11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="H11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="I11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="J11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="K11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="L11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="M11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Educación")</f>
         <v>1040000</v>
       </c>
       <c r="N11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Educación")</f>
         <v>0</v>
       </c>
       <c r="O11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Educación")</f>
         <v>0</v>
       </c>
       <c r="P11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Educación")</f>
         <v>0</v>
       </c>
       <c r="Q11" s="7" t="n">
@@ -14562,63 +14616,63 @@
         <v>21</v>
       </c>
       <c r="B12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="D12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Salud")</f>
         <v>1548449</v>
       </c>
       <c r="E12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="F12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Salud")</f>
         <v>1306200</v>
       </c>
       <c r="G12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="H12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="I12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Salud")</f>
         <v>1834914</v>
       </c>
       <c r="J12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="K12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="L12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="M12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="N12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Salud")</f>
         <v>0</v>
       </c>
       <c r="O12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Salud")</f>
         <v>0</v>
       </c>
       <c r="P12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Salud")</f>
         <v>0</v>
       </c>
       <c r="Q12" s="7" t="n">
@@ -14631,63 +14685,63 @@
         <v>27</v>
       </c>
       <c r="B13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>1057700</v>
       </c>
       <c r="C13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>710897</v>
       </c>
       <c r="D13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>708661</v>
       </c>
       <c r="E13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>730525</v>
       </c>
       <c r="F13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>728410</v>
       </c>
       <c r="G13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>1086789</v>
       </c>
       <c r="H13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>814937</v>
       </c>
       <c r="I13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>770510</v>
       </c>
       <c r="J13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="K13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="L13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="M13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="N13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="O13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="P13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="Q13" s="7" t="n">
@@ -14700,63 +14754,63 @@
         <v>29</v>
       </c>
       <c r="B14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>343055</v>
       </c>
       <c r="C14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>281793</v>
       </c>
       <c r="D14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>396566</v>
       </c>
       <c r="E14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>337184</v>
       </c>
       <c r="F14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>495759</v>
       </c>
       <c r="G14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>461374</v>
       </c>
       <c r="H14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>620062</v>
       </c>
       <c r="I14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>825549</v>
       </c>
       <c r="J14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="K14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="L14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="M14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="N14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="O14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="P14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="Q14" s="7" t="n">
@@ -14769,63 +14823,63 @@
         <v>47</v>
       </c>
       <c r="B15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="C15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="E15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>470932</v>
       </c>
       <c r="F15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="G15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="H15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>1507182</v>
       </c>
       <c r="I15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>1812640</v>
       </c>
       <c r="J15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>1805964</v>
       </c>
       <c r="K15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="L15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="M15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="N15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="O15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="P15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="Q15" s="7" t="n">
@@ -14838,68 +14892,68 @@
         <v>66</v>
       </c>
       <c r="B16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>5861720</v>
       </c>
       <c r="C16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>8780160</v>
       </c>
       <c r="D16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>5832711</v>
       </c>
       <c r="E16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>6178045</v>
       </c>
       <c r="F16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>5382047</v>
       </c>
       <c r="G16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>5089768</v>
       </c>
       <c r="H16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>5387766</v>
       </c>
       <c r="I16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>18192710</v>
       </c>
       <c r="J16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Día a día")</f>
-        <v>120000</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Día a día")</f>
+        <v>162400</v>
       </c>
       <c r="K16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="L16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="M16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="N16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="O16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="P16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="Q16" s="7" t="n">
         <f aca="false">SUM(B16:P16)</f>
-        <v>60824927</v>
+        <v>60867327</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14907,63 +14961,63 @@
         <v>110</v>
       </c>
       <c r="B17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="C17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="H17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"IPS")</f>
         <v>388110</v>
       </c>
       <c r="J17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="K17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="L17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="M17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="N17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="O17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-02",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="P17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-03",Gastos!$B$2:$B$519,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"IPS")</f>
         <v>0</v>
       </c>
       <c r="Q17" s="7" t="n">
@@ -14976,55 +15030,55 @@
         <v>161</v>
       </c>
       <c r="B18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-01",Gastos!$B$2:$B$519,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="C18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-02",Gastos!$B$2:$B$519,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="D18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-03",Gastos!$B$2:$B$519,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="E18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-04",Gastos!$B$2:$B$519,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Viajes")</f>
         <v>2392425</v>
       </c>
       <c r="F18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-05",Gastos!$B$2:$B$519,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Viajes")</f>
         <v>3391393</v>
       </c>
       <c r="G18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-06",Gastos!$B$2:$B$519,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Viajes")</f>
         <v>24171401</v>
       </c>
       <c r="H18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-07",Gastos!$B$2:$B$519,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="I18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-08",Gastos!$B$2:$B$519,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="J18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-09",Gastos!$B$2:$B$519,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="K18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-10",Gastos!$B$2:$B$519,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="L18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-11",Gastos!$B$2:$B$519,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="M18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2026-12",Gastos!$B$2:$B$519,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="N18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$519,Gastos!$A$2:$A$519,"2027-01",Gastos!$B$2:$B$519,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Viajes")</f>
         <v>0</v>
       </c>
     </row>

--- a/Gastos_Mensuales.xlsx
+++ b/Gastos_Mensuales.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3277" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3305" uniqueCount="412">
   <si>
     <t xml:space="preserve">Mes</t>
   </si>
@@ -1153,6 +1153,12 @@
   </si>
   <si>
     <t xml:space="preserve">Oficina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ropa Rufi</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -1668,7 +1674,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I522"/>
+  <dimension ref="A1:I526"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -13940,13 +13946,117 @@
         <v>132</v>
       </c>
     </row>
-    <row r="522" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="522" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A522" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C522" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D522" s="1" t="s">
+        <v>377</v>
+      </c>
       <c r="E522" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F522" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G522" s="1" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H522" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="523" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A523" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B523" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C523" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D523" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="G522" s="1" t="n">
-        <f aca="false">SUM(G2:G521)</f>
-        <v>175604858</v>
+      <c r="E523" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F523" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G523" s="1" t="n">
+        <v>30200</v>
+      </c>
+      <c r="H523" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="524" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A524" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B524" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C524" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D524" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E524" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="F524" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G524" s="1" t="n">
+        <v>135700</v>
+      </c>
+      <c r="H524" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="525" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A525" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B525" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C525" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D525" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E525" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F525" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G525" s="1" t="n">
+        <v>79350</v>
+      </c>
+      <c r="H525" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E526" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="G526" s="1" t="n">
+        <f aca="false">SUM(G2:G525)</f>
+        <v>175890108</v>
       </c>
     </row>
   </sheetData>
@@ -13973,7 +14083,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13981,32 +14091,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14014,32 +14124,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14047,27 +14157,27 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14075,22 +14185,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14098,17 +14208,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -14136,7 +14246,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14186,74 +14296,74 @@
         <v>61</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>3133982</v>
       </c>
       <c r="C4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>5264720</v>
       </c>
       <c r="D4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>5882425</v>
       </c>
       <c r="E4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>5823043</v>
       </c>
       <c r="F4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>5981618</v>
       </c>
       <c r="G4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>5949233</v>
       </c>
       <c r="H4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>6977171</v>
       </c>
       <c r="I4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>7634299</v>
       </c>
       <c r="J4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>6773164</v>
       </c>
       <c r="K4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>5463132</v>
       </c>
       <c r="L4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>5463132</v>
       </c>
       <c r="M4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>3118132</v>
       </c>
       <c r="N4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="O4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="P4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$F$2:$F$521,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$F$2:$F$525,"Fijo")</f>
         <v>0</v>
       </c>
       <c r="Q4" s="8" t="n">
@@ -14263,76 +14373,76 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$F$2:$F$525,"Variable")</f>
         <v>6304755</v>
       </c>
       <c r="C5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$F$2:$F$525,"Variable")</f>
         <v>9626002</v>
       </c>
       <c r="D5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$F$2:$F$525,"Variable")</f>
         <v>8177007</v>
       </c>
       <c r="E5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$F$2:$F$525,"Variable")</f>
         <v>9970945</v>
       </c>
       <c r="F5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$F$2:$F$525,"Variable")</f>
         <v>10299475</v>
       </c>
       <c r="G5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$F$2:$F$525,"Variable")</f>
         <v>30893365</v>
       </c>
       <c r="H5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$F$2:$F$525,"Variable")</f>
         <v>6757280</v>
       </c>
       <c r="I5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$F$2:$F$525,"Variable")</f>
         <v>20515574</v>
       </c>
       <c r="J5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$F$2:$F$521,"Variable")</f>
-        <v>1464540</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$F$2:$F$525,"Variable")</f>
+        <v>1749790</v>
       </c>
       <c r="K5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$F$2:$F$525,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="L5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$F$2:$F$525,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="M5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$F$2:$F$525,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="N5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$F$2:$F$525,"Variable")</f>
         <v>0</v>
       </c>
       <c r="O5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$F$2:$F$525,"Variable")</f>
         <v>0</v>
       </c>
       <c r="P5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$F$2:$F$521,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$F$2:$F$525,"Variable")</f>
         <v>0</v>
       </c>
       <c r="Q5" s="8" t="n">
         <f aca="false">SUM(B5:P5)</f>
-        <v>107128943</v>
+        <v>107414193</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">B4+B5</f>
@@ -14368,7 +14478,7 @@
       </c>
       <c r="J6" s="7" t="n">
         <f aca="false">J4+J5</f>
-        <v>8237704</v>
+        <v>8522954</v>
       </c>
       <c r="K6" s="7" t="n">
         <f aca="false">K4+K5</f>
@@ -14396,12 +14506,12 @@
       </c>
       <c r="Q6" s="8" t="n">
         <f aca="false">Q4+Q5</f>
-        <v>175604858</v>
+        <v>175890108</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14409,63 +14519,63 @@
         <v>10</v>
       </c>
       <c r="B9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>286542</v>
       </c>
       <c r="C9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>883152</v>
       </c>
       <c r="D9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>1048593</v>
       </c>
       <c r="E9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>783677</v>
       </c>
       <c r="F9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>826352</v>
       </c>
       <c r="G9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>624134</v>
       </c>
       <c r="H9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>633304</v>
       </c>
       <c r="I9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>680440</v>
       </c>
       <c r="J9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>672140</v>
       </c>
       <c r="K9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="L9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="M9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="N9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="O9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="P9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="Q9" s="7" t="n">
@@ -14478,63 +14588,63 @@
         <v>16</v>
       </c>
       <c r="B10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="C10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="D10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="E10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="F10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="G10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>262000</v>
       </c>
       <c r="H10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="I10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="J10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>270000</v>
       </c>
       <c r="K10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="L10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="M10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="N10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="O10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="P10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="7" t="n">
@@ -14547,63 +14657,63 @@
         <v>19</v>
       </c>
       <c r="B11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Educación")</f>
         <v>0</v>
       </c>
       <c r="C11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Educación")</f>
         <v>2345000</v>
       </c>
       <c r="D11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="E11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="F11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="G11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="H11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="I11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="J11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="K11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="L11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="M11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Educación")</f>
         <v>1040000</v>
       </c>
       <c r="N11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Educación")</f>
         <v>0</v>
       </c>
       <c r="O11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Educación")</f>
         <v>0</v>
       </c>
       <c r="P11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Educación")</f>
         <v>0</v>
       </c>
       <c r="Q11" s="7" t="n">
@@ -14616,63 +14726,63 @@
         <v>21</v>
       </c>
       <c r="B12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="D12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Salud")</f>
         <v>1548449</v>
       </c>
       <c r="E12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="F12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Salud")</f>
         <v>1306200</v>
       </c>
       <c r="G12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="H12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="I12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Salud")</f>
         <v>1834914</v>
       </c>
       <c r="J12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="K12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="L12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="M12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="N12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Salud")</f>
         <v>0</v>
       </c>
       <c r="O12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Salud")</f>
         <v>0</v>
       </c>
       <c r="P12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Salud")</f>
         <v>0</v>
       </c>
       <c r="Q12" s="7" t="n">
@@ -14685,63 +14795,63 @@
         <v>27</v>
       </c>
       <c r="B13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>1057700</v>
       </c>
       <c r="C13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>710897</v>
       </c>
       <c r="D13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>708661</v>
       </c>
       <c r="E13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>730525</v>
       </c>
       <c r="F13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>728410</v>
       </c>
       <c r="G13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>1086789</v>
       </c>
       <c r="H13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>814937</v>
       </c>
       <c r="I13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>770510</v>
       </c>
       <c r="J13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="K13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="L13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="M13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="N13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="O13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="P13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="Q13" s="7" t="n">
@@ -14754,63 +14864,63 @@
         <v>29</v>
       </c>
       <c r="B14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>343055</v>
       </c>
       <c r="C14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>281793</v>
       </c>
       <c r="D14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>396566</v>
       </c>
       <c r="E14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>337184</v>
       </c>
       <c r="F14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>495759</v>
       </c>
       <c r="G14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>461374</v>
       </c>
       <c r="H14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>620062</v>
       </c>
       <c r="I14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>825549</v>
       </c>
       <c r="J14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="K14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="L14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="M14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="N14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="O14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="P14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="Q14" s="7" t="n">
@@ -14823,63 +14933,63 @@
         <v>47</v>
       </c>
       <c r="B15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="C15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="E15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>470932</v>
       </c>
       <c r="F15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="G15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="H15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>1507182</v>
       </c>
       <c r="I15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>1812640</v>
       </c>
       <c r="J15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>1805964</v>
       </c>
       <c r="K15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="L15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="M15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="N15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="O15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="P15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="Q15" s="7" t="n">
@@ -14892,68 +15002,68 @@
         <v>66</v>
       </c>
       <c r="B16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>5861720</v>
       </c>
       <c r="C16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>8780160</v>
       </c>
       <c r="D16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>5832711</v>
       </c>
       <c r="E16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>6178045</v>
       </c>
       <c r="F16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>5382047</v>
       </c>
       <c r="G16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>5089768</v>
       </c>
       <c r="H16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>5387766</v>
       </c>
       <c r="I16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>18192710</v>
       </c>
       <c r="J16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Día a día")</f>
-        <v>162400</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Día a día")</f>
+        <v>447650</v>
       </c>
       <c r="K16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="L16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="M16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="N16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="O16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="P16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="Q16" s="7" t="n">
         <f aca="false">SUM(B16:P16)</f>
-        <v>60867327</v>
+        <v>61152577</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14961,63 +15071,63 @@
         <v>110</v>
       </c>
       <c r="B17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="C17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="H17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"IPS")</f>
         <v>388110</v>
       </c>
       <c r="J17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="K17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="L17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="M17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="N17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="O17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-02",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="P17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-03",Gastos!$B$2:$B$521,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"IPS")</f>
         <v>0</v>
       </c>
       <c r="Q17" s="7" t="n">
@@ -15030,55 +15140,55 @@
         <v>161</v>
       </c>
       <c r="B18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-01",Gastos!$B$2:$B$521,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="C18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-02",Gastos!$B$2:$B$521,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="D18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-03",Gastos!$B$2:$B$521,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="E18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-04",Gastos!$B$2:$B$521,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Viajes")</f>
         <v>2392425</v>
       </c>
       <c r="F18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-05",Gastos!$B$2:$B$521,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Viajes")</f>
         <v>3391393</v>
       </c>
       <c r="G18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-06",Gastos!$B$2:$B$521,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Viajes")</f>
         <v>24171401</v>
       </c>
       <c r="H18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-07",Gastos!$B$2:$B$521,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="I18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-08",Gastos!$B$2:$B$521,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="J18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-09",Gastos!$B$2:$B$521,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="K18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-10",Gastos!$B$2:$B$521,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="L18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-11",Gastos!$B$2:$B$521,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="M18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2026-12",Gastos!$B$2:$B$521,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="N18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$521,Gastos!$A$2:$A$521,"2027-01",Gastos!$B$2:$B$521,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Viajes")</f>
         <v>0</v>
       </c>
     </row>

--- a/Gastos_Mensuales.xlsx
+++ b/Gastos_Mensuales.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3305" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3333" uniqueCount="415">
   <si>
     <t xml:space="preserve">Mes</t>
   </si>
@@ -1159,6 +1159,15 @@
   </si>
   <si>
     <t xml:space="preserve">Ropa Rufi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery (cena invitada en casa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limpieza (adelanto, se descuenta 50.000 en próximos 2 pagos)</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -1674,7 +1683,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I526"/>
+  <dimension ref="A1:I530"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -14050,13 +14059,117 @@
         <v>13</v>
       </c>
     </row>
-    <row r="526" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="526" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A526" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B526" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C526" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D526" s="1" t="s">
+        <v>377</v>
+      </c>
       <c r="E526" s="1" t="s">
         <v>379</v>
       </c>
+      <c r="F526" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="G526" s="1" t="n">
-        <f aca="false">SUM(G2:G525)</f>
-        <v>175890108</v>
+        <v>304000</v>
+      </c>
+      <c r="H526" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="527" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A527" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B527" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C527" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D527" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E527" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F527" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G527" s="1" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H527" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="528" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A528" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B528" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C528" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D528" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E528" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F528" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G528" s="1" t="n">
+        <v>165000</v>
+      </c>
+      <c r="H528" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="529" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A529" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B529" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C529" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D529" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="E529" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="F529" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G529" s="1" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H529" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="530" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F530" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G530" s="1" t="n">
+        <f aca="false">SUM(G2:G529)</f>
+        <v>176579108</v>
       </c>
     </row>
   </sheetData>
@@ -14083,7 +14196,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14091,32 +14204,32 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14124,32 +14237,32 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14157,27 +14270,27 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14185,22 +14298,22 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14208,17 +14321,17 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -14246,7 +14359,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14296,74 +14409,74 @@
         <v>61</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-01",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>3133982</v>
       </c>
       <c r="C4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-02",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>5264720</v>
       </c>
       <c r="D4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-03",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>5882425</v>
       </c>
       <c r="E4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-04",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>5823043</v>
       </c>
       <c r="F4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-05",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>5981618</v>
       </c>
       <c r="G4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-06",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>5949233</v>
       </c>
       <c r="H4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-07",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>6977171</v>
       </c>
       <c r="I4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-08",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>7634299</v>
       </c>
       <c r="J4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-09",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>6773164</v>
       </c>
       <c r="K4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-10",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>5463132</v>
       </c>
       <c r="L4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-11",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>5463132</v>
       </c>
       <c r="M4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-12",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>3118132</v>
       </c>
       <c r="N4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-01",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="O4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-02",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>505932</v>
       </c>
       <c r="P4" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$F$2:$F$525,"Fijo")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-03",Gastos!$F$2:$F$529,"Fijo")</f>
         <v>0</v>
       </c>
       <c r="Q4" s="8" t="n">
@@ -14373,76 +14486,76 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-01",Gastos!$F$2:$F$529,"Variable")</f>
         <v>6304755</v>
       </c>
       <c r="C5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-02",Gastos!$F$2:$F$529,"Variable")</f>
         <v>9626002</v>
       </c>
       <c r="D5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-03",Gastos!$F$2:$F$529,"Variable")</f>
         <v>8177007</v>
       </c>
       <c r="E5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-04",Gastos!$F$2:$F$529,"Variable")</f>
         <v>9970945</v>
       </c>
       <c r="F5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-05",Gastos!$F$2:$F$529,"Variable")</f>
         <v>10299475</v>
       </c>
       <c r="G5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-06",Gastos!$F$2:$F$529,"Variable")</f>
         <v>30893365</v>
       </c>
       <c r="H5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-07",Gastos!$F$2:$F$529,"Variable")</f>
         <v>6757280</v>
       </c>
       <c r="I5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-08",Gastos!$F$2:$F$529,"Variable")</f>
         <v>20515574</v>
       </c>
       <c r="J5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$F$2:$F$525,"Variable")</f>
-        <v>1749790</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-09",Gastos!$F$2:$F$529,"Variable")</f>
+        <v>2438790</v>
       </c>
       <c r="K5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-10",Gastos!$F$2:$F$529,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="L5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-11",Gastos!$F$2:$F$529,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="M5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-12",Gastos!$F$2:$F$529,"Variable")</f>
         <v>1040000</v>
       </c>
       <c r="N5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-01",Gastos!$F$2:$F$529,"Variable")</f>
         <v>0</v>
       </c>
       <c r="O5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-02",Gastos!$F$2:$F$529,"Variable")</f>
         <v>0</v>
       </c>
       <c r="P5" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$F$2:$F$525,"Variable")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-03",Gastos!$F$2:$F$529,"Variable")</f>
         <v>0</v>
       </c>
       <c r="Q5" s="8" t="n">
         <f aca="false">SUM(B5:P5)</f>
-        <v>107414193</v>
+        <v>108103193</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">B4+B5</f>
@@ -14478,7 +14591,7 @@
       </c>
       <c r="J6" s="7" t="n">
         <f aca="false">J4+J5</f>
-        <v>8522954</v>
+        <v>9211954</v>
       </c>
       <c r="K6" s="7" t="n">
         <f aca="false">K4+K5</f>
@@ -14506,12 +14619,12 @@
       </c>
       <c r="Q6" s="8" t="n">
         <f aca="false">Q4+Q5</f>
-        <v>175890108</v>
+        <v>176579108</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14519,63 +14632,63 @@
         <v>10</v>
       </c>
       <c r="B9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-01",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>286542</v>
       </c>
       <c r="C9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-02",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>883152</v>
       </c>
       <c r="D9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-03",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>1048593</v>
       </c>
       <c r="E9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-04",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>783677</v>
       </c>
       <c r="F9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-05",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>826352</v>
       </c>
       <c r="G9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-06",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>624134</v>
       </c>
       <c r="H9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-07",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>633304</v>
       </c>
       <c r="I9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-08",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>680440</v>
       </c>
       <c r="J9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-09",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>672140</v>
       </c>
       <c r="K9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-10",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="L9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-11",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="M9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-12",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>410000</v>
       </c>
       <c r="N9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-01",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="O9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-02",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="P9" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Servicios")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-03",Gastos!$B$2:$B$529,"Servicios")</f>
         <v>0</v>
       </c>
       <c r="Q9" s="7" t="n">
@@ -14588,63 +14701,63 @@
         <v>16</v>
       </c>
       <c r="B10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-01",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="C10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-02",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="D10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-03",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="E10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-04",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="F10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-05",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="G10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-06",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>262000</v>
       </c>
       <c r="H10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-07",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>130000</v>
       </c>
       <c r="I10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-08",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="J10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-09",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>270000</v>
       </c>
       <c r="K10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-10",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="L10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-11",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="M10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-12",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>260000</v>
       </c>
       <c r="N10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-01",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="O10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-02",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="P10" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Telecomunicaciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-03",Gastos!$B$2:$B$529,"Telecomunicaciones")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="7" t="n">
@@ -14657,63 +14770,63 @@
         <v>19</v>
       </c>
       <c r="B11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-01",Gastos!$B$2:$B$529,"Educación")</f>
         <v>0</v>
       </c>
       <c r="C11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-02",Gastos!$B$2:$B$529,"Educación")</f>
         <v>2345000</v>
       </c>
       <c r="D11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-03",Gastos!$B$2:$B$529,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="E11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-04",Gastos!$B$2:$B$529,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="F11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-05",Gastos!$B$2:$B$529,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="G11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-06",Gastos!$B$2:$B$529,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="H11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-07",Gastos!$B$2:$B$529,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="I11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-08",Gastos!$B$2:$B$529,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="J11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-09",Gastos!$B$2:$B$529,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="K11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-10",Gastos!$B$2:$B$529,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="L11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-11",Gastos!$B$2:$B$529,"Educación")</f>
         <v>3385000</v>
       </c>
       <c r="M11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-12",Gastos!$B$2:$B$529,"Educación")</f>
         <v>1040000</v>
       </c>
       <c r="N11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-01",Gastos!$B$2:$B$529,"Educación")</f>
         <v>0</v>
       </c>
       <c r="O11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-02",Gastos!$B$2:$B$529,"Educación")</f>
         <v>0</v>
       </c>
       <c r="P11" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Educación")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-03",Gastos!$B$2:$B$529,"Educación")</f>
         <v>0</v>
       </c>
       <c r="Q11" s="7" t="n">
@@ -14726,63 +14839,63 @@
         <v>21</v>
       </c>
       <c r="B12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-01",Gastos!$B$2:$B$529,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-02",Gastos!$B$2:$B$529,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="D12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-03",Gastos!$B$2:$B$529,"Salud")</f>
         <v>1548449</v>
       </c>
       <c r="E12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-04",Gastos!$B$2:$B$529,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="F12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-05",Gastos!$B$2:$B$529,"Salud")</f>
         <v>1306200</v>
       </c>
       <c r="G12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-06",Gastos!$B$2:$B$529,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="H12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-07",Gastos!$B$2:$B$529,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="I12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-08",Gastos!$B$2:$B$529,"Salud")</f>
         <v>1834914</v>
       </c>
       <c r="J12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-09",Gastos!$B$2:$B$529,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="K12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-10",Gastos!$B$2:$B$529,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="L12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-11",Gastos!$B$2:$B$529,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="M12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-12",Gastos!$B$2:$B$529,"Salud")</f>
         <v>1256200</v>
       </c>
       <c r="N12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-01",Gastos!$B$2:$B$529,"Salud")</f>
         <v>0</v>
       </c>
       <c r="O12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-02",Gastos!$B$2:$B$529,"Salud")</f>
         <v>0</v>
       </c>
       <c r="P12" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Salud")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-03",Gastos!$B$2:$B$529,"Salud")</f>
         <v>0</v>
       </c>
       <c r="Q12" s="7" t="n">
@@ -14795,63 +14908,63 @@
         <v>27</v>
       </c>
       <c r="B13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-01",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>1057700</v>
       </c>
       <c r="C13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-02",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>710897</v>
       </c>
       <c r="D13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-03",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>708661</v>
       </c>
       <c r="E13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-04",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>730525</v>
       </c>
       <c r="F13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-05",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>728410</v>
       </c>
       <c r="G13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-06",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>1086789</v>
       </c>
       <c r="H13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-07",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>814937</v>
       </c>
       <c r="I13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-08",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>770510</v>
       </c>
       <c r="J13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-09",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="K13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-10",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="L13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-11",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="M13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-12",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>686000</v>
       </c>
       <c r="N13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-01",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="O13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-02",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="P13" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Seguros")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-03",Gastos!$B$2:$B$529,"Seguros")</f>
         <v>0</v>
       </c>
       <c r="Q13" s="7" t="n">
@@ -14864,63 +14977,63 @@
         <v>29</v>
       </c>
       <c r="B14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-01",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>343055</v>
       </c>
       <c r="C14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-02",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>281793</v>
       </c>
       <c r="D14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-03",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>396566</v>
       </c>
       <c r="E14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-04",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>337184</v>
       </c>
       <c r="F14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-05",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>495759</v>
       </c>
       <c r="G14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-06",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>461374</v>
       </c>
       <c r="H14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-07",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>620062</v>
       </c>
       <c r="I14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-08",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>825549</v>
       </c>
       <c r="J14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-09",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="K14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-10",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="L14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-11",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="M14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-12",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="N14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-01",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="O14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-02",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="P14" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Suscripciones")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-03",Gastos!$B$2:$B$529,"Suscripciones")</f>
         <v>0</v>
       </c>
       <c r="Q14" s="7" t="n">
@@ -14933,63 +15046,63 @@
         <v>47</v>
       </c>
       <c r="B15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-01",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="C15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-02",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="D15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-03",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="E15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-04",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>470932</v>
       </c>
       <c r="F15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-05",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="G15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-06",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="H15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-07",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>1507182</v>
       </c>
       <c r="I15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-08",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>1812640</v>
       </c>
       <c r="J15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-09",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>1805964</v>
       </c>
       <c r="K15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-10",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="L15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-11",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="M15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-12",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="N15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-01",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="O15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-02",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>505932</v>
       </c>
       <c r="P15" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Compras adicionales")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-03",Gastos!$B$2:$B$529,"Compras adicionales")</f>
         <v>0</v>
       </c>
       <c r="Q15" s="7" t="n">
@@ -15002,68 +15115,68 @@
         <v>66</v>
       </c>
       <c r="B16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-01",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>5861720</v>
       </c>
       <c r="C16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-02",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>8780160</v>
       </c>
       <c r="D16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-03",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>5832711</v>
       </c>
       <c r="E16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-04",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>6178045</v>
       </c>
       <c r="F16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-05",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>5382047</v>
       </c>
       <c r="G16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-06",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>5089768</v>
       </c>
       <c r="H16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-07",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>5387766</v>
       </c>
       <c r="I16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-08",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>18192710</v>
       </c>
       <c r="J16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Día a día")</f>
-        <v>447650</v>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-09",Gastos!$B$2:$B$529,"Día a día")</f>
+        <v>1136650</v>
       </c>
       <c r="K16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-10",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="L16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-11",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="M16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-12",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="N16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-01",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="O16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-02",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="P16" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"Día a día")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-03",Gastos!$B$2:$B$529,"Día a día")</f>
         <v>0</v>
       </c>
       <c r="Q16" s="7" t="n">
         <f aca="false">SUM(B16:P16)</f>
-        <v>61152577</v>
+        <v>61841577</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15071,63 +15184,63 @@
         <v>110</v>
       </c>
       <c r="B17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-01",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="C17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-02",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="D17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-03",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-04",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-05",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-06",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="H17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-07",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="I17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-08",Gastos!$B$2:$B$529,"IPS")</f>
         <v>388110</v>
       </c>
       <c r="J17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-09",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="K17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-10",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="L17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-11",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="M17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-12",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="N17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-01",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="O17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-02",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-02",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="P17" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-03",Gastos!$B$2:$B$525,"IPS")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-03",Gastos!$B$2:$B$529,"IPS")</f>
         <v>0</v>
       </c>
       <c r="Q17" s="7" t="n">
@@ -15140,55 +15253,55 @@
         <v>161</v>
       </c>
       <c r="B18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-01",Gastos!$B$2:$B$525,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-01",Gastos!$B$2:$B$529,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="C18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-02",Gastos!$B$2:$B$525,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-02",Gastos!$B$2:$B$529,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="D18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-03",Gastos!$B$2:$B$525,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-03",Gastos!$B$2:$B$529,"Viajes")</f>
         <v>373520</v>
       </c>
       <c r="E18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-04",Gastos!$B$2:$B$525,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-04",Gastos!$B$2:$B$529,"Viajes")</f>
         <v>2392425</v>
       </c>
       <c r="F18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-05",Gastos!$B$2:$B$525,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-05",Gastos!$B$2:$B$529,"Viajes")</f>
         <v>3391393</v>
       </c>
       <c r="G18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-06",Gastos!$B$2:$B$525,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-06",Gastos!$B$2:$B$529,"Viajes")</f>
         <v>24171401</v>
       </c>
       <c r="H18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-07",Gastos!$B$2:$B$525,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-07",Gastos!$B$2:$B$529,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="I18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-08",Gastos!$B$2:$B$525,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-08",Gastos!$B$2:$B$529,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="J18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-09",Gastos!$B$2:$B$525,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-09",Gastos!$B$2:$B$529,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="K18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-10",Gastos!$B$2:$B$525,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-10",Gastos!$B$2:$B$529,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="L18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-11",Gastos!$B$2:$B$525,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-11",Gastos!$B$2:$B$529,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="M18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2026-12",Gastos!$B$2:$B$525,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2026-12",Gastos!$B$2:$B$529,"Viajes")</f>
         <v>0</v>
       </c>
       <c r="N18" s="7" t="n">
-        <f aca="false">SUMIFS(Gastos!$G$2:$G$525,Gastos!$A$2:$A$525,"2027-01",Gastos!$B$2:$B$525,"Viajes")</f>
+        <f aca="false">SUMIFS(Gastos!$G$2:$G$529,Gastos!$A$2:$A$529,"2027-01",Gastos!$B$2:$B$529,"Viajes")</f>
         <v>0</v>
       </c>
     </row>
